--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,31 +446,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1789045649533</v>
+        <v>1789701749272</v>
       </c>
       <c r="B2" t="str">
-        <v>ENCE Academy</v>
+        <v>MOUZ</v>
       </c>
       <c r="C2" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F2" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v>Fourth</v>
       </c>
       <c r="H2">
-        <v>10000</v>
+        <v>700</v>
       </c>
       <c r="I2">
-        <v>700</v>
+        <v>420</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -487,31 +487,31 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>1789045609684</v>
+        <v>1789701744555</v>
       </c>
       <c r="B3" t="str">
-        <v>SKYFURY</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="C3" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F3" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v>Fourth</v>
       </c>
       <c r="H3">
-        <v>10000</v>
+        <v>700</v>
       </c>
       <c r="I3">
-        <v>700</v>
+        <v>420</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -528,31 +528,31 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1789045581410</v>
+        <v>1789701734985</v>
       </c>
       <c r="B4" t="str">
-        <v>BIG Academy</v>
+        <v>Envy</v>
       </c>
       <c r="C4" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F4" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v>Fourth</v>
       </c>
       <c r="H4">
-        <v>10000</v>
+        <v>700</v>
       </c>
       <c r="I4">
-        <v>700</v>
+        <v>420</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -569,31 +569,31 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1789045560109</v>
+        <v>1789701723266</v>
       </c>
       <c r="B5" t="str">
-        <v>Wildcard Academy</v>
+        <v>Enemy</v>
       </c>
       <c r="C5" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F5" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v>Fourth</v>
       </c>
       <c r="H5">
-        <v>10000</v>
+        <v>700</v>
       </c>
       <c r="I5">
-        <v>700</v>
+        <v>420</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -610,31 +610,31 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>1789045530768</v>
+        <v>1789701676668</v>
       </c>
       <c r="B6" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Astralis</v>
       </c>
       <c r="C6" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F6" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v>Fourth</v>
       </c>
       <c r="H6">
-        <v>10000</v>
+        <v>700</v>
       </c>
       <c r="I6">
-        <v>700</v>
+        <v>420</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -651,31 +651,31 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1789045299584</v>
+        <v>1789701668422</v>
       </c>
       <c r="B7" t="str">
-        <v>Mythic</v>
+        <v>BC.Game</v>
       </c>
       <c r="C7" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F7" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>Fourth</v>
+        <v>Third</v>
       </c>
       <c r="H7">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="I7">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -692,31 +692,31 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>1789045274106</v>
+        <v>1789701649080</v>
       </c>
       <c r="B8" t="str">
-        <v>paiN Academy</v>
+        <v>Imperial</v>
       </c>
       <c r="C8" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F8" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>Fourth</v>
+        <v>Second</v>
       </c>
       <c r="H8">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="I8">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -733,31 +733,31 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>1789045224902</v>
+        <v>1789701627337</v>
       </c>
       <c r="B9" t="str">
-        <v>Legacy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="C9" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F9" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="H9">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I9">
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -774,13 +774,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>1789045150461</v>
+        <v>1789045649533</v>
       </c>
       <c r="B10" t="str">
-        <v>Into the Beach</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="C10" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -789,7 +789,7 @@
         <v>Regional</v>
       </c>
       <c r="F10" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="G10" t="str">
         <v>Fourth</v>
@@ -815,13 +815,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>1789045118610</v>
+        <v>1789045609684</v>
       </c>
       <c r="B11" t="str">
-        <v>Take Flyte</v>
+        <v>SKYFURY</v>
       </c>
       <c r="C11" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -830,7 +830,7 @@
         <v>Regional</v>
       </c>
       <c r="F11" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="G11" t="str">
         <v>Fourth</v>
@@ -856,31 +856,31 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>1789044307262</v>
+        <v>1789045581410</v>
       </c>
       <c r="B12" t="str">
-        <v>Nemiga</v>
+        <v>BIG Academy</v>
       </c>
       <c r="C12" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E12" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="G12" t="str">
         <v>Fourth</v>
       </c>
       <c r="H12">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I12">
-        <v>45000</v>
+        <v>700</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -897,31 +897,31 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>1789044244253</v>
+        <v>1789045560109</v>
       </c>
       <c r="B13" t="str">
-        <v>Natus Vincere</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="C13" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="G13" t="str">
         <v>Fourth</v>
       </c>
       <c r="H13">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I13">
-        <v>45000</v>
+        <v>700</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -938,31 +938,31 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>1789044197304</v>
+        <v>1789045530768</v>
       </c>
       <c r="B14" t="str">
-        <v>Copenhagen Flames</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="C14" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E14" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="G14" t="str">
         <v>Fourth</v>
       </c>
       <c r="H14">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I14">
-        <v>45000</v>
+        <v>700</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -979,31 +979,31 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>1789044064380</v>
+        <v>1789045299584</v>
       </c>
       <c r="B15" t="str">
-        <v>The MongolZ</v>
+        <v>Mythic</v>
       </c>
       <c r="C15" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="G15" t="str">
         <v>Fourth</v>
       </c>
       <c r="H15">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I15">
-        <v>45000</v>
+        <v>700</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1020,31 +1020,31 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>1789043946191</v>
+        <v>1789045274106</v>
       </c>
       <c r="B16" t="str">
-        <v>Liquid</v>
+        <v>paiN Academy</v>
       </c>
       <c r="C16" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="G16" t="str">
         <v>Fourth</v>
       </c>
       <c r="H16">
-        <v>1790000</v>
+        <v>10000</v>
       </c>
       <c r="I16">
-        <v>60000</v>
+        <v>700</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1061,13 +1061,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>1787471977697</v>
+        <v>1789045224902</v>
       </c>
       <c r="B17" t="str">
-        <v>Astana Dragons</v>
+        <v>Legacy</v>
       </c>
       <c r="C17" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1076,16 +1076,16 @@
         <v>Regional</v>
       </c>
       <c r="F17" t="str">
-        <v>Europe</v>
+        <v>America</v>
       </c>
       <c r="G17" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="H17">
         <v>10000</v>
       </c>
       <c r="I17">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1102,13 +1102,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>1787471970177</v>
+        <v>1789045150461</v>
       </c>
       <c r="B18" t="str">
-        <v>Vox Eminor</v>
+        <v>Into the Beach</v>
       </c>
       <c r="C18" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1117,16 +1117,16 @@
         <v>Regional</v>
       </c>
       <c r="F18" t="str">
-        <v>Europe</v>
+        <v>America</v>
       </c>
       <c r="G18" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="H18">
         <v>10000</v>
       </c>
       <c r="I18">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1143,13 +1143,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>1787471959675</v>
+        <v>1789045118610</v>
       </c>
       <c r="B19" t="str">
-        <v>Fnatic</v>
+        <v>Take Flyte</v>
       </c>
       <c r="C19" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1158,16 +1158,16 @@
         <v>Regional</v>
       </c>
       <c r="F19" t="str">
-        <v>Europe</v>
+        <v>America</v>
       </c>
       <c r="G19" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="H19">
         <v>10000</v>
       </c>
       <c r="I19">
-        <v>3000</v>
+        <v>700</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1184,31 +1184,31 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>1784854079769</v>
+        <v>1789044307262</v>
       </c>
       <c r="B20" t="str">
-        <v>Entropiq</v>
+        <v>Nemiga</v>
       </c>
       <c r="C20" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F20" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="H20">
-        <v>10000</v>
+        <v>1790000</v>
       </c>
       <c r="I20">
-        <v>1500</v>
+        <v>45000</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1225,31 +1225,31 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>1784854026526</v>
+        <v>1789044244253</v>
       </c>
       <c r="B21" t="str">
-        <v>AMKAL</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="C21" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E21" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F21" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="H21">
-        <v>10000</v>
+        <v>1790000</v>
       </c>
       <c r="I21">
-        <v>2000</v>
+        <v>45000</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1266,31 +1266,31 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>1784848026994</v>
+        <v>1789044197304</v>
       </c>
       <c r="B22" t="str">
-        <v>FURIA</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="C22" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E22" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="F22" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="H22">
-        <v>10000</v>
+        <v>1790000</v>
       </c>
       <c r="I22">
-        <v>3000</v>
+        <v>45000</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>1783531248336</v>
+        <v>1789044064380</v>
       </c>
       <c r="B23" t="str">
-        <v>Falcons</v>
+        <v>The MongolZ</v>
       </c>
       <c r="C23" t="str">
         <v>DreamHack Winter 2026</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="H23">
         <v>1790000</v>
       </c>
       <c r="I23">
-        <v>100000</v>
+        <v>45000</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>1783531237020</v>
+        <v>1789043946191</v>
       </c>
       <c r="B24" t="str">
-        <v>Vitality</v>
+        <v>Liquid</v>
       </c>
       <c r="C24" t="str">
         <v>DreamHack Winter 2026</v>
@@ -1366,13 +1366,13 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="H24">
         <v>1790000</v>
       </c>
       <c r="I24">
-        <v>170000</v>
+        <v>60000</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1389,55 +1389,383 @@
     </row>
     <row r="25">
       <c r="A25">
+        <v>1787471977697</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Astana Dragons</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Third</v>
+      </c>
+      <c r="H25">
+        <v>10000</v>
+      </c>
+      <c r="I25">
+        <v>1500</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>1787471970177</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Vox Eminor</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Second</v>
+      </c>
+      <c r="H26">
+        <v>10000</v>
+      </c>
+      <c r="I26">
+        <v>2000</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>1787471959675</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Fnatic</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="H27">
+        <v>10000</v>
+      </c>
+      <c r="I27">
+        <v>3000</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>1784854079769</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Entropiq</v>
+      </c>
+      <c r="C28" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F28" t="str">
+        <v>America</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Third</v>
+      </c>
+      <c r="H28">
+        <v>10000</v>
+      </c>
+      <c r="I28">
+        <v>1500</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>1784854026526</v>
+      </c>
+      <c r="B29" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="C29" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F29" t="str">
+        <v>America</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Second</v>
+      </c>
+      <c r="H29">
+        <v>10000</v>
+      </c>
+      <c r="I29">
+        <v>2000</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>1784848026994</v>
+      </c>
+      <c r="B30" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="C30" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="F30" t="str">
+        <v>America</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="H30">
+        <v>10000</v>
+      </c>
+      <c r="I30">
+        <v>3000</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>1783531248336</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="C31" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>Third</v>
+      </c>
+      <c r="H31">
+        <v>1790000</v>
+      </c>
+      <c r="I31">
+        <v>100000</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>1783531237020</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="C32" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>Second</v>
+      </c>
+      <c r="H32">
+        <v>1790000</v>
+      </c>
+      <c r="I32">
+        <v>170000</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
         <v>1783531219494</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B33" t="str">
         <v>Iluminar</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C33" t="str">
         <v>DreamHack Winter 2026</v>
       </c>
-      <c r="D25">
+      <c r="D33">
         <v>5</v>
       </c>
-      <c r="E25" t="str">
-        <v>Global</v>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
+      <c r="E33" t="str">
+        <v>Global</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
         <v>Winner</v>
       </c>
-      <c r="H25">
+      <c r="H33">
         <v>1790000</v>
       </c>
-      <c r="I25">
+      <c r="I33">
         <v>500000</v>
       </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25" t="str">
-        <v>EVENT</v>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M33"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M180"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1481,23 +1809,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1789045649533-ykis</v>
-      </c>
-      <c r="B2">
-        <v>1789045649533</v>
+      <c r="A2">
+        <v>1789701851248</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>ykis</v>
+        <v>s1mple</v>
       </c>
       <c r="D2" t="str">
-        <v>ENCE Academy</v>
+        <v>BC.Game</v>
       </c>
       <c r="E2" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F2" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1509,7 +1837,7 @@
         <v>Europe</v>
       </c>
       <c r="J2" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1522,23 +1850,23 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>1789045649533-japE</v>
-      </c>
-      <c r="B3">
-        <v>1789045649533</v>
+      <c r="A3">
+        <v>1789701846578</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>japE</v>
+        <v>taco</v>
       </c>
       <c r="D3" t="str">
-        <v>ENCE Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E3" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F3" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1550,7 +1878,7 @@
         <v>Europe</v>
       </c>
       <c r="J3" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1563,23 +1891,23 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>1789045649533-Welho</v>
-      </c>
-      <c r="B4">
-        <v>1789045649533</v>
+      <c r="A4">
+        <v>1789701842702</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v>Welho</v>
+        <v>kyourezz</v>
       </c>
       <c r="D4" t="str">
-        <v>ENCE Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E4" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F4" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1591,7 +1919,7 @@
         <v>Europe</v>
       </c>
       <c r="J4" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1604,23 +1932,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>1789045649533-oopee</v>
-      </c>
-      <c r="B5">
-        <v>1789045649533</v>
+      <c r="A5">
+        <v>1789701830776</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>oopee</v>
+        <v>heroghoxxt</v>
       </c>
       <c r="D5" t="str">
-        <v>ENCE Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E5" t="str">
-        <v>EVENT</v>
+        <v>EVP</v>
       </c>
       <c r="F5" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1632,7 +1960,7 @@
         <v>Europe</v>
       </c>
       <c r="J5" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1645,23 +1973,23 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>1789045649533-arvid</v>
-      </c>
-      <c r="B6">
-        <v>1789045649533</v>
+      <c r="A6">
+        <v>1789701823336</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>arvid</v>
+        <v>kilzys</v>
       </c>
       <c r="D6" t="str">
-        <v>ENCE Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E6" t="str">
-        <v>EVENT</v>
+        <v>MVP</v>
       </c>
       <c r="F6" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1673,7 +2001,7 @@
         <v>Europe</v>
       </c>
       <c r="J6" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1687,31 +2015,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1789045609684-2high</v>
+        <v>1789701749272-xertioN</v>
       </c>
       <c r="B7">
-        <v>1789045609684</v>
+        <v>1789701749272</v>
       </c>
       <c r="C7" t="str">
-        <v>2high</v>
+        <v>xertioN</v>
       </c>
       <c r="D7" t="str">
-        <v>SKYFURY</v>
+        <v>MOUZ</v>
       </c>
       <c r="E7" t="str">
         <v>EVENT</v>
       </c>
       <c r="F7" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I7" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J7" t="str">
         <v>Fourth</v>
@@ -1728,31 +2056,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1789045609684-jL</v>
+        <v>1789701749272-Jimpphat</v>
       </c>
       <c r="B8">
-        <v>1789045609684</v>
+        <v>1789701749272</v>
       </c>
       <c r="C8" t="str">
-        <v>jL</v>
+        <v>Jimpphat</v>
       </c>
       <c r="D8" t="str">
-        <v>SKYFURY</v>
+        <v>MOUZ</v>
       </c>
       <c r="E8" t="str">
         <v>EVENT</v>
       </c>
       <c r="F8" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I8" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J8" t="str">
         <v>Fourth</v>
@@ -1769,31 +2097,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1789045609684-aliStair</v>
+        <v>1789701749272-Spinx</v>
       </c>
       <c r="B9">
-        <v>1789045609684</v>
+        <v>1789701749272</v>
       </c>
       <c r="C9" t="str">
-        <v>aliStair</v>
+        <v>Spinx</v>
       </c>
       <c r="D9" t="str">
-        <v>SKYFURY</v>
+        <v>MOUZ</v>
       </c>
       <c r="E9" t="str">
         <v>EVENT</v>
       </c>
       <c r="F9" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I9" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J9" t="str">
         <v>Fourth</v>
@@ -1810,31 +2138,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1789045609684-gla1ve</v>
+        <v>1789701749272-torzsi</v>
       </c>
       <c r="B10">
-        <v>1789045609684</v>
+        <v>1789701749272</v>
       </c>
       <c r="C10" t="str">
-        <v>gla1ve</v>
+        <v>torzsi</v>
       </c>
       <c r="D10" t="str">
-        <v>SKYFURY</v>
+        <v>MOUZ</v>
       </c>
       <c r="E10" t="str">
         <v>EVENT</v>
       </c>
       <c r="F10" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I10" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J10" t="str">
         <v>Fourth</v>
@@ -1851,31 +2179,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1789045609684-discoStar</v>
+        <v>1789701749272-Brollan</v>
       </c>
       <c r="B11">
-        <v>1789045609684</v>
+        <v>1789701749272</v>
       </c>
       <c r="C11" t="str">
-        <v>discoStar</v>
+        <v>Brollan</v>
       </c>
       <c r="D11" t="str">
-        <v>SKYFURY</v>
+        <v>MOUZ</v>
       </c>
       <c r="E11" t="str">
         <v>EVENT</v>
       </c>
       <c r="F11" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I11" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J11" t="str">
         <v>Fourth</v>
@@ -1892,31 +2220,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1789045581410-forkyz</v>
+        <v>1789701744555-C4LLM3SU3</v>
       </c>
       <c r="B12">
-        <v>1789045581410</v>
+        <v>1789701744555</v>
       </c>
       <c r="C12" t="str">
-        <v>forkyz</v>
+        <v>C4LLM3SU3</v>
       </c>
       <c r="D12" t="str">
-        <v>BIG Academy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E12" t="str">
         <v>EVENT</v>
       </c>
       <c r="F12" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I12" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J12" t="str">
         <v>Fourth</v>
@@ -1933,31 +2261,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1789045581410-Pumpkin66</v>
+        <v>1789701744555-EmiliaQAQ</v>
       </c>
       <c r="B13">
-        <v>1789045581410</v>
+        <v>1789701744555</v>
       </c>
       <c r="C13" t="str">
-        <v>Pumpkin66</v>
+        <v>EmiliaQAQ</v>
       </c>
       <c r="D13" t="str">
-        <v>BIG Academy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E13" t="str">
         <v>EVENT</v>
       </c>
       <c r="F13" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I13" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J13" t="str">
         <v>Fourth</v>
@@ -1974,31 +2302,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1789045581410-def1zer</v>
+        <v>1789701744555-Starry</v>
       </c>
       <c r="B14">
-        <v>1789045581410</v>
+        <v>1789701744555</v>
       </c>
       <c r="C14" t="str">
-        <v>def1zer</v>
+        <v>Starry</v>
       </c>
       <c r="D14" t="str">
-        <v>BIG Academy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E14" t="str">
         <v>EVENT</v>
       </c>
       <c r="F14" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I14" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J14" t="str">
         <v>Fourth</v>
@@ -2015,31 +2343,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>1789045581410-buster</v>
+        <v>1789701744555-z4kr</v>
       </c>
       <c r="B15">
-        <v>1789045581410</v>
+        <v>1789701744555</v>
       </c>
       <c r="C15" t="str">
-        <v>buster</v>
+        <v>z4kr</v>
       </c>
       <c r="D15" t="str">
-        <v>BIG Academy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E15" t="str">
         <v>EVENT</v>
       </c>
       <c r="F15" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I15" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J15" t="str">
         <v>Fourth</v>
@@ -2056,31 +2384,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1789045581410-neaLaN</v>
+        <v>1789701744555-Westmelon</v>
       </c>
       <c r="B16">
-        <v>1789045581410</v>
+        <v>1789701744555</v>
       </c>
       <c r="C16" t="str">
-        <v>neaLaN</v>
+        <v>Westmelon</v>
       </c>
       <c r="D16" t="str">
-        <v>BIG Academy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E16" t="str">
         <v>EVENT</v>
       </c>
       <c r="F16" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I16" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J16" t="str">
         <v>Fourth</v>
@@ -2097,31 +2425,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>1789045560109-cerber</v>
+        <v>1789701734985-Snax</v>
       </c>
       <c r="B17">
-        <v>1789045560109</v>
+        <v>1789701734985</v>
       </c>
       <c r="C17" t="str">
-        <v>cerber</v>
+        <v>Snax</v>
       </c>
       <c r="D17" t="str">
-        <v>Wildcard Academy</v>
+        <v>Envy</v>
       </c>
       <c r="E17" t="str">
         <v>EVENT</v>
       </c>
       <c r="F17" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I17" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J17" t="str">
         <v>Fourth</v>
@@ -2138,31 +2466,31 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1789045560109-SinK</v>
+        <v>1789701734985-PTC</v>
       </c>
       <c r="B18">
-        <v>1789045560109</v>
+        <v>1789701734985</v>
       </c>
       <c r="C18" t="str">
-        <v>SinK</v>
+        <v>PTC</v>
       </c>
       <c r="D18" t="str">
-        <v>Wildcard Academy</v>
+        <v>Envy</v>
       </c>
       <c r="E18" t="str">
         <v>EVENT</v>
       </c>
       <c r="F18" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I18" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J18" t="str">
         <v>Fourth</v>
@@ -2179,31 +2507,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1789045560109-qx</v>
+        <v>1789701734985-h4rn</v>
       </c>
       <c r="B19">
-        <v>1789045560109</v>
+        <v>1789701734985</v>
       </c>
       <c r="C19" t="str">
-        <v>qx</v>
+        <v>h4rn</v>
       </c>
       <c r="D19" t="str">
-        <v>Wildcard Academy</v>
+        <v>Envy</v>
       </c>
       <c r="E19" t="str">
         <v>EVENT</v>
       </c>
       <c r="F19" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I19" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J19" t="str">
         <v>Fourth</v>
@@ -2220,31 +2548,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1789045560109-Griller</v>
+        <v>1789701734985-liTTle</v>
       </c>
       <c r="B20">
-        <v>1789045560109</v>
+        <v>1789701734985</v>
       </c>
       <c r="C20" t="str">
-        <v>Griller</v>
+        <v>liTTle</v>
       </c>
       <c r="D20" t="str">
-        <v>Wildcard Academy</v>
+        <v>Envy</v>
       </c>
       <c r="E20" t="str">
         <v>EVENT</v>
       </c>
       <c r="F20" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I20" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J20" t="str">
         <v>Fourth</v>
@@ -2261,31 +2589,31 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1789045560109-AclioN</v>
+        <v>1789701734985-cosmeeeN</v>
       </c>
       <c r="B21">
-        <v>1789045560109</v>
+        <v>1789701734985</v>
       </c>
       <c r="C21" t="str">
-        <v>AclioN</v>
+        <v>cosmeeeN</v>
       </c>
       <c r="D21" t="str">
-        <v>Wildcard Academy</v>
+        <v>Envy</v>
       </c>
       <c r="E21" t="str">
         <v>EVENT</v>
       </c>
       <c r="F21" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I21" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J21" t="str">
         <v>Fourth</v>
@@ -2302,31 +2630,31 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1789045530768-Matheos</v>
+        <v>1789701723266-leakz</v>
       </c>
       <c r="B22">
-        <v>1789045530768</v>
+        <v>1789701723266</v>
       </c>
       <c r="C22" t="str">
-        <v>Matheos</v>
+        <v>leakz</v>
       </c>
       <c r="D22" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Enemy</v>
       </c>
       <c r="E22" t="str">
         <v>EVENT</v>
       </c>
       <c r="F22" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I22" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J22" t="str">
         <v>Fourth</v>
@@ -2343,31 +2671,31 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>1789045530768-Jorko</v>
+        <v>1789701723266-salaza</v>
       </c>
       <c r="B23">
-        <v>1789045530768</v>
+        <v>1789701723266</v>
       </c>
       <c r="C23" t="str">
-        <v>Jorko</v>
+        <v>salaza</v>
       </c>
       <c r="D23" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Enemy</v>
       </c>
       <c r="E23" t="str">
         <v>EVENT</v>
       </c>
       <c r="F23" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I23" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J23" t="str">
         <v>Fourth</v>
@@ -2384,31 +2712,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>1789045530768-Tapewaare</v>
+        <v>1789701723266-kroK</v>
       </c>
       <c r="B24">
-        <v>1789045530768</v>
+        <v>1789701723266</v>
       </c>
       <c r="C24" t="str">
-        <v>Tapewaare</v>
+        <v>kroK</v>
       </c>
       <c r="D24" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Enemy</v>
       </c>
       <c r="E24" t="str">
         <v>EVENT</v>
       </c>
       <c r="F24" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I24" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J24" t="str">
         <v>Fourth</v>
@@ -2425,31 +2753,31 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>1789045530768-b1elany</v>
+        <v>1789701723266-valde</v>
       </c>
       <c r="B25">
-        <v>1789045530768</v>
+        <v>1789701723266</v>
       </c>
       <c r="C25" t="str">
-        <v>b1elany</v>
+        <v>valde</v>
       </c>
       <c r="D25" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Enemy</v>
       </c>
       <c r="E25" t="str">
         <v>EVENT</v>
       </c>
       <c r="F25" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I25" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J25" t="str">
         <v>Fourth</v>
@@ -2466,31 +2794,31 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>1789045530768-n1Xen</v>
+        <v>1789701723266-Nodios</v>
       </c>
       <c r="B26">
-        <v>1789045530768</v>
+        <v>1789701723266</v>
       </c>
       <c r="C26" t="str">
-        <v>n1Xen</v>
+        <v>Nodios</v>
       </c>
       <c r="D26" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Enemy</v>
       </c>
       <c r="E26" t="str">
         <v>EVENT</v>
       </c>
       <c r="F26" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I26" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J26" t="str">
         <v>Fourth</v>
@@ -2507,34 +2835,34 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>1787471977697-oskar</v>
+        <v>1789701676668-Staehr</v>
       </c>
       <c r="B27">
-        <v>1787471977697</v>
+        <v>1789701676668</v>
       </c>
       <c r="C27" t="str">
-        <v>oskar</v>
+        <v>Staehr</v>
       </c>
       <c r="D27" t="str">
-        <v>Astana Dragons</v>
+        <v>Astralis</v>
       </c>
       <c r="E27" t="str">
         <v>EVENT</v>
       </c>
       <c r="F27" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I27" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J27" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2548,34 +2876,34 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>1787471977697-PR</v>
+        <v>1789701676668-jabbi</v>
       </c>
       <c r="B28">
-        <v>1787471977697</v>
+        <v>1789701676668</v>
       </c>
       <c r="C28" t="str">
-        <v>PR</v>
+        <v>jabbi</v>
       </c>
       <c r="D28" t="str">
-        <v>Astana Dragons</v>
+        <v>Astralis</v>
       </c>
       <c r="E28" t="str">
         <v>EVENT</v>
       </c>
       <c r="F28" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I28" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J28" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2589,34 +2917,34 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>1787471977697-Tauson</v>
+        <v>1789701676668-stavn</v>
       </c>
       <c r="B29">
-        <v>1787471977697</v>
+        <v>1789701676668</v>
       </c>
       <c r="C29" t="str">
-        <v>Tauson</v>
+        <v>stavn</v>
       </c>
       <c r="D29" t="str">
-        <v>Astana Dragons</v>
+        <v>Astralis</v>
       </c>
       <c r="E29" t="str">
         <v>EVENT</v>
       </c>
       <c r="F29" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I29" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J29" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2630,34 +2958,34 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1787471977697-ztr</v>
+        <v>1789701676668-HooXi</v>
       </c>
       <c r="B30">
-        <v>1787471977697</v>
+        <v>1789701676668</v>
       </c>
       <c r="C30" t="str">
-        <v>ztr</v>
+        <v>HooXi</v>
       </c>
       <c r="D30" t="str">
-        <v>Astana Dragons</v>
+        <v>Astralis</v>
       </c>
       <c r="E30" t="str">
         <v>EVENT</v>
       </c>
       <c r="F30" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I30" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J30" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2671,34 +2999,34 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>1787471977697-REZ</v>
+        <v>1789701676668-device</v>
       </c>
       <c r="B31">
-        <v>1787471977697</v>
+        <v>1789701676668</v>
       </c>
       <c r="C31" t="str">
-        <v>REZ</v>
+        <v>device</v>
       </c>
       <c r="D31" t="str">
-        <v>Astana Dragons</v>
+        <v>Astralis</v>
       </c>
       <c r="E31" t="str">
         <v>EVENT</v>
       </c>
       <c r="F31" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I31" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J31" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -2712,34 +3040,34 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>1787471970177-OneUn1que</v>
+        <v>1789701668422-SaVage</v>
       </c>
       <c r="B32">
-        <v>1787471970177</v>
+        <v>1789701668422</v>
       </c>
       <c r="C32" t="str">
-        <v>OneUn1que</v>
+        <v>SaVage</v>
       </c>
       <c r="D32" t="str">
-        <v>Vox Eminor</v>
+        <v>BC.Game</v>
       </c>
       <c r="E32" t="str">
         <v>EVENT</v>
       </c>
       <c r="F32" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I32" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J32" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -2753,34 +3081,34 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>1787471970177-kL1o</v>
+        <v>1789701668422-shadiy</v>
       </c>
       <c r="B33">
-        <v>1787471970177</v>
+        <v>1789701668422</v>
       </c>
       <c r="C33" t="str">
-        <v>kL1o</v>
+        <v>shadiy</v>
       </c>
       <c r="D33" t="str">
-        <v>Vox Eminor</v>
+        <v>BC.Game</v>
       </c>
       <c r="E33" t="str">
         <v>EVENT</v>
       </c>
       <c r="F33" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I33" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J33" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -2794,34 +3122,34 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>1787471970177-marat2k</v>
+        <v>1789701668422-Valiance</v>
       </c>
       <c r="B34">
-        <v>1787471970177</v>
+        <v>1789701668422</v>
       </c>
       <c r="C34" t="str">
-        <v>marat2k</v>
+        <v>Valiance</v>
       </c>
       <c r="D34" t="str">
-        <v>Vox Eminor</v>
+        <v>BC.Game</v>
       </c>
       <c r="E34" t="str">
         <v>EVENT</v>
       </c>
       <c r="F34" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I34" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J34" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -2835,34 +3163,34 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>1787471970177-Malkiss</v>
+        <v>1789701668422-electroNic</v>
       </c>
       <c r="B35">
-        <v>1787471970177</v>
+        <v>1789701668422</v>
       </c>
       <c r="C35" t="str">
-        <v>Malkiss</v>
+        <v>electroNic</v>
       </c>
       <c r="D35" t="str">
-        <v>Vox Eminor</v>
+        <v>BC.Game</v>
       </c>
       <c r="E35" t="str">
         <v>EVENT</v>
       </c>
       <c r="F35" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I35" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J35" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -2876,34 +3204,34 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>1787471970177-kr1vda</v>
+        <v>1789701668422-s1mple</v>
       </c>
       <c r="B36">
-        <v>1787471970177</v>
+        <v>1789701668422</v>
       </c>
       <c r="C36" t="str">
-        <v>kr1vda</v>
+        <v>s1mple</v>
       </c>
       <c r="D36" t="str">
-        <v>Vox Eminor</v>
+        <v>BC.Game</v>
       </c>
       <c r="E36" t="str">
         <v>EVENT</v>
       </c>
       <c r="F36" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I36" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J36" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -2917,34 +3245,34 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>1787471959675-jambo</v>
+        <v>1789701649080-chelo</v>
       </c>
       <c r="B37">
-        <v>1787471959675</v>
+        <v>1789701649080</v>
       </c>
       <c r="C37" t="str">
-        <v>jambo</v>
+        <v>chelo</v>
       </c>
       <c r="D37" t="str">
-        <v>Fnatic</v>
+        <v>Imperial</v>
       </c>
       <c r="E37" t="str">
         <v>EVENT</v>
       </c>
       <c r="F37" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I37" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J37" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -2958,34 +3286,34 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>1787471959675-fear</v>
+        <v>1789701649080-noway</v>
       </c>
       <c r="B38">
-        <v>1787471959675</v>
+        <v>1789701649080</v>
       </c>
       <c r="C38" t="str">
-        <v>fear</v>
+        <v>noway</v>
       </c>
       <c r="D38" t="str">
-        <v>Fnatic</v>
+        <v>Imperial</v>
       </c>
       <c r="E38" t="str">
         <v>EVENT</v>
       </c>
       <c r="F38" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I38" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J38" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -2999,34 +3327,34 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>1787471959675-blameF</v>
+        <v>1789701649080-Shr</v>
       </c>
       <c r="B39">
-        <v>1787471959675</v>
+        <v>1789701649080</v>
       </c>
       <c r="C39" t="str">
-        <v>blameF</v>
+        <v>Shr</v>
       </c>
       <c r="D39" t="str">
-        <v>Fnatic</v>
+        <v>Imperial</v>
       </c>
       <c r="E39" t="str">
         <v>EVENT</v>
       </c>
       <c r="F39" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I39" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J39" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -3040,34 +3368,34 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1787471959675-KRIMZ</v>
+        <v>1789701649080-try</v>
       </c>
       <c r="B40">
-        <v>1787471959675</v>
+        <v>1789701649080</v>
       </c>
       <c r="C40" t="str">
-        <v>KRIMZ</v>
+        <v>try</v>
       </c>
       <c r="D40" t="str">
-        <v>Fnatic</v>
+        <v>Imperial</v>
       </c>
       <c r="E40" t="str">
         <v>EVENT</v>
       </c>
       <c r="F40" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G40">
         <v>1</v>
       </c>
       <c r="H40" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I40" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J40" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K40">
         <v>1</v>
@@ -3081,34 +3409,34 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>1789045299584-hades</v>
+        <v>1789701649080-VINI</v>
       </c>
       <c r="B41">
-        <v>1789045299584</v>
+        <v>1789701649080</v>
       </c>
       <c r="C41" t="str">
-        <v>hades</v>
+        <v>VINI</v>
       </c>
       <c r="D41" t="str">
-        <v>Mythic</v>
+        <v>Imperial</v>
       </c>
       <c r="E41" t="str">
         <v>EVENT</v>
       </c>
       <c r="F41" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I41" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J41" t="str">
-        <v>Fourth</v>
+        <v>Second</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -3122,34 +3450,34 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>1789045299584-PwnAlone</v>
+        <v>1789701627337-boltz</v>
       </c>
       <c r="B42">
-        <v>1789045299584</v>
+        <v>1789701627337</v>
       </c>
       <c r="C42" t="str">
-        <v>PwnAlone</v>
+        <v>boltz</v>
       </c>
       <c r="D42" t="str">
-        <v>Mythic</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E42" t="str">
         <v>EVENT</v>
       </c>
       <c r="F42" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I42" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J42" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -3163,34 +3491,34 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>1789045299584-Trucklover86</v>
+        <v>1789701627337-taco</v>
       </c>
       <c r="B43">
-        <v>1789045299584</v>
+        <v>1789701627337</v>
       </c>
       <c r="C43" t="str">
-        <v>Trucklover86</v>
+        <v>taco</v>
       </c>
       <c r="D43" t="str">
-        <v>Mythic</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E43" t="str">
         <v>EVENT</v>
       </c>
       <c r="F43" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I43" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J43" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -3204,34 +3532,34 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>1789045299584-hyza</v>
+        <v>1789701627337-kyourezz</v>
       </c>
       <c r="B44">
-        <v>1789045299584</v>
+        <v>1789701627337</v>
       </c>
       <c r="C44" t="str">
-        <v>hyza</v>
+        <v>kyourezz</v>
       </c>
       <c r="D44" t="str">
-        <v>Mythic</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E44" t="str">
         <v>EVENT</v>
       </c>
       <c r="F44" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I44" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J44" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -3245,34 +3573,34 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>1789045299584-Cooper</v>
+        <v>1789701627337-heroghoxxt</v>
       </c>
       <c r="B45">
-        <v>1789045299584</v>
+        <v>1789701627337</v>
       </c>
       <c r="C45" t="str">
-        <v>Cooper</v>
+        <v>heroghoxxt</v>
       </c>
       <c r="D45" t="str">
-        <v>Mythic</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E45" t="str">
         <v>EVENT</v>
       </c>
       <c r="F45" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I45" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J45" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K45">
         <v>1</v>
@@ -3286,34 +3614,34 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>1789045274106-blaze</v>
+        <v>1789701627337-kilzys</v>
       </c>
       <c r="B46">
-        <v>1789045274106</v>
+        <v>1789701627337</v>
       </c>
       <c r="C46" t="str">
-        <v>blaze</v>
+        <v>kilzys</v>
       </c>
       <c r="D46" t="str">
-        <v>paiN Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E46" t="str">
         <v>EVENT</v>
       </c>
       <c r="F46" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I46" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J46" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K46">
         <v>1</v>
@@ -3327,22 +3655,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>1789045274106-h0t</v>
+        <v>1789045649533-ykis</v>
       </c>
       <c r="B47">
-        <v>1789045274106</v>
+        <v>1789045649533</v>
       </c>
       <c r="C47" t="str">
-        <v>h0t</v>
+        <v>ykis</v>
       </c>
       <c r="D47" t="str">
-        <v>paiN Academy</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E47" t="str">
         <v>EVENT</v>
       </c>
       <c r="F47" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -3351,7 +3679,7 @@
         <v>Regional</v>
       </c>
       <c r="I47" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J47" t="str">
         <v>Fourth</v>
@@ -3368,22 +3696,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>1789045274106-bsd</v>
+        <v>1789045649533-japE</v>
       </c>
       <c r="B48">
-        <v>1789045274106</v>
+        <v>1789045649533</v>
       </c>
       <c r="C48" t="str">
-        <v>bsd</v>
+        <v>japE</v>
       </c>
       <c r="D48" t="str">
-        <v>paiN Academy</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E48" t="str">
         <v>EVENT</v>
       </c>
       <c r="F48" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -3392,7 +3720,7 @@
         <v>Regional</v>
       </c>
       <c r="I48" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J48" t="str">
         <v>Fourth</v>
@@ -3409,22 +3737,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>1789045274106-b4rtiN</v>
+        <v>1789045649533-Welho</v>
       </c>
       <c r="B49">
-        <v>1789045274106</v>
+        <v>1789045649533</v>
       </c>
       <c r="C49" t="str">
-        <v>b4rtiN</v>
+        <v>Welho</v>
       </c>
       <c r="D49" t="str">
-        <v>paiN Academy</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E49" t="str">
         <v>EVENT</v>
       </c>
       <c r="F49" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3433,7 +3761,7 @@
         <v>Regional</v>
       </c>
       <c r="I49" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J49" t="str">
         <v>Fourth</v>
@@ -3450,22 +3778,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>1789045274106-NEKIZ</v>
+        <v>1789045649533-oopee</v>
       </c>
       <c r="B50">
-        <v>1789045274106</v>
+        <v>1789045649533</v>
       </c>
       <c r="C50" t="str">
-        <v>NEKIZ</v>
+        <v>oopee</v>
       </c>
       <c r="D50" t="str">
-        <v>paiN Academy</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E50" t="str">
         <v>EVENT</v>
       </c>
       <c r="F50" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -3474,7 +3802,7 @@
         <v>Regional</v>
       </c>
       <c r="I50" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J50" t="str">
         <v>Fourth</v>
@@ -3491,22 +3819,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>1789045224902-saadzin</v>
+        <v>1789045649533-arvid</v>
       </c>
       <c r="B51">
-        <v>1789045224902</v>
+        <v>1789045649533</v>
       </c>
       <c r="C51" t="str">
-        <v>saadzin</v>
+        <v>arvid</v>
       </c>
       <c r="D51" t="str">
-        <v>Legacy</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E51" t="str">
         <v>EVENT</v>
       </c>
       <c r="F51" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -3515,7 +3843,7 @@
         <v>Regional</v>
       </c>
       <c r="I51" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J51" t="str">
         <v>Fourth</v>
@@ -3532,22 +3860,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>1789045224902-lux</v>
+        <v>1789045609684-2high</v>
       </c>
       <c r="B52">
-        <v>1789045224902</v>
+        <v>1789045609684</v>
       </c>
       <c r="C52" t="str">
-        <v>lux</v>
+        <v>2high</v>
       </c>
       <c r="D52" t="str">
-        <v>Legacy</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E52" t="str">
         <v>EVENT</v>
       </c>
       <c r="F52" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -3556,7 +3884,7 @@
         <v>Regional</v>
       </c>
       <c r="I52" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J52" t="str">
         <v>Fourth</v>
@@ -3573,22 +3901,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>1789045224902-n1ssim</v>
+        <v>1789045609684-jL</v>
       </c>
       <c r="B53">
-        <v>1789045224902</v>
+        <v>1789045609684</v>
       </c>
       <c r="C53" t="str">
-        <v>n1ssim</v>
+        <v>jL</v>
       </c>
       <c r="D53" t="str">
-        <v>Legacy</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E53" t="str">
         <v>EVENT</v>
       </c>
       <c r="F53" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3597,7 +3925,7 @@
         <v>Regional</v>
       </c>
       <c r="I53" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J53" t="str">
         <v>Fourth</v>
@@ -3614,22 +3942,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>1789045224902-latto</v>
+        <v>1789045609684-aliStair</v>
       </c>
       <c r="B54">
-        <v>1789045224902</v>
+        <v>1789045609684</v>
       </c>
       <c r="C54" t="str">
-        <v>latto</v>
+        <v>aliStair</v>
       </c>
       <c r="D54" t="str">
-        <v>Legacy</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E54" t="str">
         <v>EVENT</v>
       </c>
       <c r="F54" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -3638,7 +3966,7 @@
         <v>Regional</v>
       </c>
       <c r="I54" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J54" t="str">
         <v>Fourth</v>
@@ -3655,22 +3983,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>1789045224902-dumau</v>
+        <v>1789045609684-gla1ve</v>
       </c>
       <c r="B55">
-        <v>1789045224902</v>
+        <v>1789045609684</v>
       </c>
       <c r="C55" t="str">
-        <v>dumau</v>
+        <v>gla1ve</v>
       </c>
       <c r="D55" t="str">
-        <v>Legacy</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E55" t="str">
         <v>EVENT</v>
       </c>
       <c r="F55" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3679,7 +4007,7 @@
         <v>Regional</v>
       </c>
       <c r="I55" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J55" t="str">
         <v>Fourth</v>
@@ -3696,22 +4024,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>1789045150461-levi</v>
+        <v>1789045609684-discoStar</v>
       </c>
       <c r="B56">
-        <v>1789045150461</v>
+        <v>1789045609684</v>
       </c>
       <c r="C56" t="str">
-        <v>levi</v>
+        <v>discoStar</v>
       </c>
       <c r="D56" t="str">
-        <v>Into the Beach</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E56" t="str">
         <v>EVENT</v>
       </c>
       <c r="F56" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -3720,7 +4048,7 @@
         <v>Regional</v>
       </c>
       <c r="I56" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J56" t="str">
         <v>Fourth</v>
@@ -3737,22 +4065,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>1789045150461-urban0</v>
+        <v>1789045581410-forkyz</v>
       </c>
       <c r="B57">
-        <v>1789045150461</v>
+        <v>1789045581410</v>
       </c>
       <c r="C57" t="str">
-        <v>urban0</v>
+        <v>forkyz</v>
       </c>
       <c r="D57" t="str">
-        <v>Into the Beach</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E57" t="str">
         <v>EVENT</v>
       </c>
       <c r="F57" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -3761,7 +4089,7 @@
         <v>Regional</v>
       </c>
       <c r="I57" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J57" t="str">
         <v>Fourth</v>
@@ -3778,22 +4106,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>1789045150461-t9rnay</v>
+        <v>1789045581410-Pumpkin66</v>
       </c>
       <c r="B58">
-        <v>1789045150461</v>
+        <v>1789045581410</v>
       </c>
       <c r="C58" t="str">
-        <v>t9rnay</v>
+        <v>Pumpkin66</v>
       </c>
       <c r="D58" t="str">
-        <v>Into the Beach</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E58" t="str">
         <v>EVENT</v>
       </c>
       <c r="F58" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -3802,7 +4130,7 @@
         <v>Regional</v>
       </c>
       <c r="I58" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J58" t="str">
         <v>Fourth</v>
@@ -3819,22 +4147,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>1789045150461-JOTA</v>
+        <v>1789045581410-def1zer</v>
       </c>
       <c r="B59">
-        <v>1789045150461</v>
+        <v>1789045581410</v>
       </c>
       <c r="C59" t="str">
-        <v>JOTA</v>
+        <v>def1zer</v>
       </c>
       <c r="D59" t="str">
-        <v>Into the Beach</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E59" t="str">
         <v>EVENT</v>
       </c>
       <c r="F59" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -3843,7 +4171,7 @@
         <v>Regional</v>
       </c>
       <c r="I59" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J59" t="str">
         <v>Fourth</v>
@@ -3860,22 +4188,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>1789045150461-shz</v>
+        <v>1789045581410-buster</v>
       </c>
       <c r="B60">
-        <v>1789045150461</v>
+        <v>1789045581410</v>
       </c>
       <c r="C60" t="str">
-        <v>shz</v>
+        <v>buster</v>
       </c>
       <c r="D60" t="str">
-        <v>Into the Beach</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E60" t="str">
         <v>EVENT</v>
       </c>
       <c r="F60" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -3884,7 +4212,7 @@
         <v>Regional</v>
       </c>
       <c r="I60" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J60" t="str">
         <v>Fourth</v>
@@ -3901,22 +4229,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>1789045118610-huncho</v>
+        <v>1789045581410-neaLaN</v>
       </c>
       <c r="B61">
-        <v>1789045118610</v>
+        <v>1789045581410</v>
       </c>
       <c r="C61" t="str">
-        <v>huncho</v>
+        <v>neaLaN</v>
       </c>
       <c r="D61" t="str">
-        <v>Take Flyte</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E61" t="str">
         <v>EVENT</v>
       </c>
       <c r="F61" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -3925,7 +4253,7 @@
         <v>Regional</v>
       </c>
       <c r="I61" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J61" t="str">
         <v>Fourth</v>
@@ -3942,22 +4270,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>1789045118610-Crisp</v>
+        <v>1789045560109-cerber</v>
       </c>
       <c r="B62">
-        <v>1789045118610</v>
+        <v>1789045560109</v>
       </c>
       <c r="C62" t="str">
-        <v>Crisp</v>
+        <v>cerber</v>
       </c>
       <c r="D62" t="str">
-        <v>Take Flyte</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E62" t="str">
         <v>EVENT</v>
       </c>
       <c r="F62" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3966,7 +4294,7 @@
         <v>Regional</v>
       </c>
       <c r="I62" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J62" t="str">
         <v>Fourth</v>
@@ -3983,22 +4311,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>1789045118610-FxRE</v>
+        <v>1789045560109-SinK</v>
       </c>
       <c r="B63">
-        <v>1789045118610</v>
+        <v>1789045560109</v>
       </c>
       <c r="C63" t="str">
-        <v>FxRE</v>
+        <v>SinK</v>
       </c>
       <c r="D63" t="str">
-        <v>Take Flyte</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E63" t="str">
         <v>EVENT</v>
       </c>
       <c r="F63" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -4007,7 +4335,7 @@
         <v>Regional</v>
       </c>
       <c r="I63" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J63" t="str">
         <v>Fourth</v>
@@ -4024,22 +4352,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>1789045118610-Panic</v>
+        <v>1789045560109-qx</v>
       </c>
       <c r="B64">
-        <v>1789045118610</v>
+        <v>1789045560109</v>
       </c>
       <c r="C64" t="str">
-        <v>Panic</v>
+        <v>qx</v>
       </c>
       <c r="D64" t="str">
-        <v>Take Flyte</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E64" t="str">
         <v>EVENT</v>
       </c>
       <c r="F64" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -4048,7 +4376,7 @@
         <v>Regional</v>
       </c>
       <c r="I64" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J64" t="str">
         <v>Fourth</v>
@@ -4065,22 +4393,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>1789045118610-REKMEISTER</v>
+        <v>1789045560109-Griller</v>
       </c>
       <c r="B65">
-        <v>1789045118610</v>
+        <v>1789045560109</v>
       </c>
       <c r="C65" t="str">
-        <v>REKMEISTER</v>
+        <v>Griller</v>
       </c>
       <c r="D65" t="str">
-        <v>Take Flyte</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E65" t="str">
         <v>EVENT</v>
       </c>
       <c r="F65" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -4089,7 +4417,7 @@
         <v>Regional</v>
       </c>
       <c r="I65" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J65" t="str">
         <v>Fourth</v>
@@ -4106,22 +4434,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>1784854079769-Benkai</v>
+        <v>1789045560109-AclioN</v>
       </c>
       <c r="B66">
-        <v>1784854079769</v>
+        <v>1789045560109</v>
       </c>
       <c r="C66" t="str">
-        <v>Benkai</v>
+        <v>AclioN</v>
       </c>
       <c r="D66" t="str">
-        <v>Entropiq</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E66" t="str">
         <v>EVENT</v>
       </c>
       <c r="F66" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -4130,10 +4458,10 @@
         <v>Regional</v>
       </c>
       <c r="I66" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J66" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K66">
         <v>1</v>
@@ -4147,22 +4475,22 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>1784854079769-dea</v>
+        <v>1789045530768-Matheos</v>
       </c>
       <c r="B67">
-        <v>1784854079769</v>
+        <v>1789045530768</v>
       </c>
       <c r="C67" t="str">
-        <v>dea</v>
+        <v>Matheos</v>
       </c>
       <c r="D67" t="str">
-        <v>Entropiq</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E67" t="str">
         <v>EVENT</v>
       </c>
       <c r="F67" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -4171,10 +4499,10 @@
         <v>Regional</v>
       </c>
       <c r="I67" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J67" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K67">
         <v>1</v>
@@ -4188,22 +4516,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>1784854079769-shane</v>
+        <v>1789045530768-Jorko</v>
       </c>
       <c r="B68">
-        <v>1784854079769</v>
+        <v>1789045530768</v>
       </c>
       <c r="C68" t="str">
-        <v>shane</v>
+        <v>Jorko</v>
       </c>
       <c r="D68" t="str">
-        <v>Entropiq</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E68" t="str">
         <v>EVENT</v>
       </c>
       <c r="F68" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -4212,10 +4540,10 @@
         <v>Regional</v>
       </c>
       <c r="I68" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J68" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K68">
         <v>1</v>
@@ -4229,22 +4557,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>1784854079769-nosraC</v>
+        <v>1789045530768-Tapewaare</v>
       </c>
       <c r="B69">
-        <v>1784854079769</v>
+        <v>1789045530768</v>
       </c>
       <c r="C69" t="str">
-        <v>nosraC</v>
+        <v>Tapewaare</v>
       </c>
       <c r="D69" t="str">
-        <v>Entropiq</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E69" t="str">
         <v>EVENT</v>
       </c>
       <c r="F69" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -4253,10 +4581,10 @@
         <v>Regional</v>
       </c>
       <c r="I69" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J69" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K69">
         <v>1</v>
@@ -4270,22 +4598,22 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>1784854079769-MarKE</v>
+        <v>1789045530768-b1elany</v>
       </c>
       <c r="B70">
-        <v>1784854079769</v>
+        <v>1789045530768</v>
       </c>
       <c r="C70" t="str">
-        <v>MarKE</v>
+        <v>b1elany</v>
       </c>
       <c r="D70" t="str">
-        <v>Entropiq</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E70" t="str">
         <v>EVENT</v>
       </c>
       <c r="F70" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -4294,10 +4622,10 @@
         <v>Regional</v>
       </c>
       <c r="I70" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J70" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K70">
         <v>1</v>
@@ -4311,22 +4639,22 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>1784854026526-ivz</v>
+        <v>1789045530768-n1Xen</v>
       </c>
       <c r="B71">
-        <v>1784854026526</v>
+        <v>1789045530768</v>
       </c>
       <c r="C71" t="str">
-        <v>ivz</v>
+        <v>n1Xen</v>
       </c>
       <c r="D71" t="str">
-        <v>AMKAL</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E71" t="str">
         <v>EVENT</v>
       </c>
       <c r="F71" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -4335,10 +4663,10 @@
         <v>Regional</v>
       </c>
       <c r="I71" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J71" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K71">
         <v>1</v>
@@ -4352,22 +4680,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>1784854026526-abizz</v>
+        <v>1787471977697-oskar</v>
       </c>
       <c r="B72">
-        <v>1784854026526</v>
+        <v>1787471977697</v>
       </c>
       <c r="C72" t="str">
-        <v>abizz</v>
+        <v>oskar</v>
       </c>
       <c r="D72" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E72" t="str">
         <v>EVENT</v>
       </c>
       <c r="F72" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -4376,10 +4704,10 @@
         <v>Regional</v>
       </c>
       <c r="I72" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J72" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K72">
         <v>1</v>
@@ -4393,22 +4721,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>1784854026526-nacho</v>
+        <v>1787471977697-PR</v>
       </c>
       <c r="B73">
-        <v>1784854026526</v>
+        <v>1787471977697</v>
       </c>
       <c r="C73" t="str">
-        <v>nacho</v>
+        <v>PR</v>
       </c>
       <c r="D73" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E73" t="str">
         <v>EVENT</v>
       </c>
       <c r="F73" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -4417,10 +4745,10 @@
         <v>Regional</v>
       </c>
       <c r="I73" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J73" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K73">
         <v>1</v>
@@ -4434,22 +4762,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>1784854026526-BK1</v>
+        <v>1787471977697-Tauson</v>
       </c>
       <c r="B74">
-        <v>1784854026526</v>
+        <v>1787471977697</v>
       </c>
       <c r="C74" t="str">
-        <v>BK1</v>
+        <v>Tauson</v>
       </c>
       <c r="D74" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E74" t="str">
         <v>EVENT</v>
       </c>
       <c r="F74" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -4458,10 +4786,10 @@
         <v>Regional</v>
       </c>
       <c r="I74" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J74" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K74">
         <v>1</v>
@@ -4475,22 +4803,22 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>1784854026526-next</v>
+        <v>1787471977697-ztr</v>
       </c>
       <c r="B75">
-        <v>1784854026526</v>
+        <v>1787471977697</v>
       </c>
       <c r="C75" t="str">
-        <v>next</v>
+        <v>ztr</v>
       </c>
       <c r="D75" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E75" t="str">
         <v>EVENT</v>
       </c>
       <c r="F75" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -4499,10 +4827,10 @@
         <v>Regional</v>
       </c>
       <c r="I75" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J75" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K75">
         <v>1</v>
@@ -4516,22 +4844,22 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>1784848026994-molodoy</v>
+        <v>1787471977697-REZ</v>
       </c>
       <c r="B76">
-        <v>1784848026994</v>
+        <v>1787471977697</v>
       </c>
       <c r="C76" t="str">
-        <v>molodoy</v>
+        <v>REZ</v>
       </c>
       <c r="D76" t="str">
-        <v>FURIA</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E76" t="str">
         <v>EVENT</v>
       </c>
       <c r="F76" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -4540,10 +4868,10 @@
         <v>Regional</v>
       </c>
       <c r="I76" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J76" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K76">
         <v>1</v>
@@ -4557,22 +4885,22 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>1784848026994-KSCERATO</v>
+        <v>1787471970177-OneUn1que</v>
       </c>
       <c r="B77">
-        <v>1784848026994</v>
+        <v>1787471970177</v>
       </c>
       <c r="C77" t="str">
-        <v>KSCERATO</v>
+        <v>OneUn1que</v>
       </c>
       <c r="D77" t="str">
-        <v>FURIA</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E77" t="str">
         <v>EVENT</v>
       </c>
       <c r="F77" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -4581,10 +4909,10 @@
         <v>Regional</v>
       </c>
       <c r="I77" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J77" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K77">
         <v>1</v>
@@ -4598,22 +4926,22 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>1784848026994-YEKINDAR</v>
+        <v>1787471970177-kL1o</v>
       </c>
       <c r="B78">
-        <v>1784848026994</v>
+        <v>1787471970177</v>
       </c>
       <c r="C78" t="str">
-        <v>YEKINDAR</v>
+        <v>kL1o</v>
       </c>
       <c r="D78" t="str">
-        <v>FURIA</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E78" t="str">
         <v>EVENT</v>
       </c>
       <c r="F78" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -4622,10 +4950,10 @@
         <v>Regional</v>
       </c>
       <c r="I78" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J78" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K78">
         <v>1</v>
@@ -4639,22 +4967,22 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>1784848026994-yuurih</v>
+        <v>1787471970177-marat2k</v>
       </c>
       <c r="B79">
-        <v>1784848026994</v>
+        <v>1787471970177</v>
       </c>
       <c r="C79" t="str">
-        <v>yuurih</v>
+        <v>marat2k</v>
       </c>
       <c r="D79" t="str">
-        <v>FURIA</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E79" t="str">
         <v>EVENT</v>
       </c>
       <c r="F79" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -4663,10 +4991,10 @@
         <v>Regional</v>
       </c>
       <c r="I79" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J79" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K79">
         <v>1</v>
@@ -4680,22 +5008,22 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>1784848026994-FalleN</v>
+        <v>1787471970177-Malkiss</v>
       </c>
       <c r="B80">
-        <v>1784848026994</v>
+        <v>1787471970177</v>
       </c>
       <c r="C80" t="str">
-        <v>FalleN</v>
+        <v>Malkiss</v>
       </c>
       <c r="D80" t="str">
-        <v>FURIA</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E80" t="str">
         <v>EVENT</v>
       </c>
       <c r="F80" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -4704,10 +5032,10 @@
         <v>Regional</v>
       </c>
       <c r="I80" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J80" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K80">
         <v>1</v>
@@ -4721,34 +5049,34 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>1789044307262-sowalio</v>
+        <v>1787471970177-kr1vda</v>
       </c>
       <c r="B81">
-        <v>1789044307262</v>
+        <v>1787471970177</v>
       </c>
       <c r="C81" t="str">
-        <v>sowalio</v>
+        <v>kr1vda</v>
       </c>
       <c r="D81" t="str">
-        <v>Nemiga</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E81" t="str">
         <v>EVENT</v>
       </c>
       <c r="F81" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G81">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H81" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J81" t="str">
-        <v>Fourth</v>
+        <v>Second</v>
       </c>
       <c r="K81">
         <v>1</v>
@@ -4762,34 +5090,34 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>1789044307262-khaN</v>
+        <v>1787471959675-jambo</v>
       </c>
       <c r="B82">
-        <v>1789044307262</v>
+        <v>1787471959675</v>
       </c>
       <c r="C82" t="str">
-        <v>khaN</v>
+        <v>jambo</v>
       </c>
       <c r="D82" t="str">
-        <v>Nemiga</v>
+        <v>Fnatic</v>
       </c>
       <c r="E82" t="str">
         <v>EVENT</v>
       </c>
       <c r="F82" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G82">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H82" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J82" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K82">
         <v>1</v>
@@ -4803,34 +5131,34 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>1789044307262-riskyb0b</v>
+        <v>1787471959675-fear</v>
       </c>
       <c r="B83">
-        <v>1789044307262</v>
+        <v>1787471959675</v>
       </c>
       <c r="C83" t="str">
-        <v>riskyb0b</v>
+        <v>fear</v>
       </c>
       <c r="D83" t="str">
-        <v>Nemiga</v>
+        <v>Fnatic</v>
       </c>
       <c r="E83" t="str">
         <v>EVENT</v>
       </c>
       <c r="F83" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G83">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H83" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J83" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K83">
         <v>1</v>
@@ -4844,34 +5172,34 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>1789044307262-1eeR</v>
+        <v>1787471959675-blameF</v>
       </c>
       <c r="B84">
-        <v>1789044307262</v>
+        <v>1787471959675</v>
       </c>
       <c r="C84" t="str">
-        <v>1eeR</v>
+        <v>blameF</v>
       </c>
       <c r="D84" t="str">
-        <v>Nemiga</v>
+        <v>Fnatic</v>
       </c>
       <c r="E84" t="str">
         <v>EVENT</v>
       </c>
       <c r="F84" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G84">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H84" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J84" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K84">
         <v>1</v>
@@ -4885,34 +5213,34 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>1789044307262-Xant3r</v>
+        <v>1787471959675-KRIMZ</v>
       </c>
       <c r="B85">
-        <v>1789044307262</v>
+        <v>1787471959675</v>
       </c>
       <c r="C85" t="str">
-        <v>Xant3r</v>
+        <v>KRIMZ</v>
       </c>
       <c r="D85" t="str">
-        <v>Nemiga</v>
+        <v>Fnatic</v>
       </c>
       <c r="E85" t="str">
         <v>EVENT</v>
       </c>
       <c r="F85" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H85" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J85" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K85">
         <v>1</v>
@@ -4926,31 +5254,31 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>1789044244253-w0nderful</v>
+        <v>1789045299584-hades</v>
       </c>
       <c r="B86">
-        <v>1789044244253</v>
+        <v>1789045299584</v>
       </c>
       <c r="C86" t="str">
-        <v>w0nderful</v>
+        <v>hades</v>
       </c>
       <c r="D86" t="str">
-        <v>Natus Vincere</v>
+        <v>Mythic</v>
       </c>
       <c r="E86" t="str">
         <v>EVENT</v>
       </c>
       <c r="F86" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G86">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H86" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I86" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J86" t="str">
         <v>Fourth</v>
@@ -4967,31 +5295,31 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>1789044244253-makazze</v>
+        <v>1789045299584-PwnAlone</v>
       </c>
       <c r="B87">
-        <v>1789044244253</v>
+        <v>1789045299584</v>
       </c>
       <c r="C87" t="str">
-        <v>makazze</v>
+        <v>PwnAlone</v>
       </c>
       <c r="D87" t="str">
-        <v>Natus Vincere</v>
+        <v>Mythic</v>
       </c>
       <c r="E87" t="str">
         <v>EVENT</v>
       </c>
       <c r="F87" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G87">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H87" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I87" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J87" t="str">
         <v>Fourth</v>
@@ -5008,31 +5336,31 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>1789044244253-b1t</v>
+        <v>1789045299584-Trucklover86</v>
       </c>
       <c r="B88">
-        <v>1789044244253</v>
+        <v>1789045299584</v>
       </c>
       <c r="C88" t="str">
-        <v>b1t</v>
+        <v>Trucklover86</v>
       </c>
       <c r="D88" t="str">
-        <v>Natus Vincere</v>
+        <v>Mythic</v>
       </c>
       <c r="E88" t="str">
         <v>EVENT</v>
       </c>
       <c r="F88" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G88">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H88" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J88" t="str">
         <v>Fourth</v>
@@ -5049,31 +5377,31 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>1789044244253-iM</v>
+        <v>1789045299584-hyza</v>
       </c>
       <c r="B89">
-        <v>1789044244253</v>
+        <v>1789045299584</v>
       </c>
       <c r="C89" t="str">
-        <v>iM</v>
+        <v>hyza</v>
       </c>
       <c r="D89" t="str">
-        <v>Natus Vincere</v>
+        <v>Mythic</v>
       </c>
       <c r="E89" t="str">
         <v>EVENT</v>
       </c>
       <c r="F89" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G89">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H89" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J89" t="str">
         <v>Fourth</v>
@@ -5090,31 +5418,31 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>1789044244253-Aleksib</v>
+        <v>1789045299584-Cooper</v>
       </c>
       <c r="B90">
-        <v>1789044244253</v>
+        <v>1789045299584</v>
       </c>
       <c r="C90" t="str">
-        <v>Aleksib</v>
+        <v>Cooper</v>
       </c>
       <c r="D90" t="str">
-        <v>Natus Vincere</v>
+        <v>Mythic</v>
       </c>
       <c r="E90" t="str">
         <v>EVENT</v>
       </c>
       <c r="F90" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G90">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H90" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J90" t="str">
         <v>Fourth</v>
@@ -5131,31 +5459,31 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>1789044197304-Dytor</v>
+        <v>1789045274106-blaze</v>
       </c>
       <c r="B91">
-        <v>1789044197304</v>
+        <v>1789045274106</v>
       </c>
       <c r="C91" t="str">
-        <v>Dytor</v>
+        <v>blaze</v>
       </c>
       <c r="D91" t="str">
-        <v>Copenhagen Flames</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E91" t="str">
         <v>EVENT</v>
       </c>
       <c r="F91" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G91">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H91" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I91" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J91" t="str">
         <v>Fourth</v>
@@ -5172,31 +5500,31 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>1789044197304-nbqq</v>
+        <v>1789045274106-h0t</v>
       </c>
       <c r="B92">
-        <v>1789044197304</v>
+        <v>1789045274106</v>
       </c>
       <c r="C92" t="str">
-        <v>nbqq</v>
+        <v>h0t</v>
       </c>
       <c r="D92" t="str">
-        <v>Copenhagen Flames</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E92" t="str">
         <v>EVENT</v>
       </c>
       <c r="F92" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G92">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H92" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J92" t="str">
         <v>Fourth</v>
@@ -5213,31 +5541,31 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>1789044197304-forsyy</v>
+        <v>1789045274106-bsd</v>
       </c>
       <c r="B93">
-        <v>1789044197304</v>
+        <v>1789045274106</v>
       </c>
       <c r="C93" t="str">
-        <v>forsyy</v>
+        <v>bsd</v>
       </c>
       <c r="D93" t="str">
-        <v>Copenhagen Flames</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E93" t="str">
         <v>EVENT</v>
       </c>
       <c r="F93" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G93">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H93" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I93" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J93" t="str">
         <v>Fourth</v>
@@ -5254,31 +5582,31 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>1789044197304-ROGA</v>
+        <v>1789045274106-b4rtiN</v>
       </c>
       <c r="B94">
-        <v>1789044197304</v>
+        <v>1789045274106</v>
       </c>
       <c r="C94" t="str">
-        <v>ROGA</v>
+        <v>b4rtiN</v>
       </c>
       <c r="D94" t="str">
-        <v>Copenhagen Flames</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E94" t="str">
         <v>EVENT</v>
       </c>
       <c r="F94" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G94">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H94" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J94" t="str">
         <v>Fourth</v>
@@ -5295,31 +5623,31 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>1789044197304-DANK1NG</v>
+        <v>1789045274106-NEKIZ</v>
       </c>
       <c r="B95">
-        <v>1789044197304</v>
+        <v>1789045274106</v>
       </c>
       <c r="C95" t="str">
-        <v>DANK1NG</v>
+        <v>NEKIZ</v>
       </c>
       <c r="D95" t="str">
-        <v>Copenhagen Flames</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E95" t="str">
         <v>EVENT</v>
       </c>
       <c r="F95" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H95" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J95" t="str">
         <v>Fourth</v>
@@ -5336,31 +5664,31 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>1789044064380-910</v>
+        <v>1789045224902-saadzin</v>
       </c>
       <c r="B96">
-        <v>1789044064380</v>
+        <v>1789045224902</v>
       </c>
       <c r="C96" t="str">
-        <v>910</v>
+        <v>saadzin</v>
       </c>
       <c r="D96" t="str">
-        <v>The MongolZ</v>
+        <v>Legacy</v>
       </c>
       <c r="E96" t="str">
         <v>EVENT</v>
       </c>
       <c r="F96" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H96" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J96" t="str">
         <v>Fourth</v>
@@ -5377,31 +5705,31 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>1789044064380-mzinho</v>
+        <v>1789045224902-lux</v>
       </c>
       <c r="B97">
-        <v>1789044064380</v>
+        <v>1789045224902</v>
       </c>
       <c r="C97" t="str">
-        <v>mzinho</v>
+        <v>lux</v>
       </c>
       <c r="D97" t="str">
-        <v>The MongolZ</v>
+        <v>Legacy</v>
       </c>
       <c r="E97" t="str">
         <v>EVENT</v>
       </c>
       <c r="F97" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H97" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J97" t="str">
         <v>Fourth</v>
@@ -5418,31 +5746,31 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>1789044064380-Senzu</v>
+        <v>1789045224902-n1ssim</v>
       </c>
       <c r="B98">
-        <v>1789044064380</v>
+        <v>1789045224902</v>
       </c>
       <c r="C98" t="str">
-        <v>Senzu</v>
+        <v>n1ssim</v>
       </c>
       <c r="D98" t="str">
-        <v>The MongolZ</v>
+        <v>Legacy</v>
       </c>
       <c r="E98" t="str">
         <v>EVENT</v>
       </c>
       <c r="F98" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G98">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H98" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I98" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J98" t="str">
         <v>Fourth</v>
@@ -5459,31 +5787,31 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>1789044064380-Techno</v>
+        <v>1789045224902-latto</v>
       </c>
       <c r="B99">
-        <v>1789044064380</v>
+        <v>1789045224902</v>
       </c>
       <c r="C99" t="str">
-        <v>Techno</v>
+        <v>latto</v>
       </c>
       <c r="D99" t="str">
-        <v>The MongolZ</v>
+        <v>Legacy</v>
       </c>
       <c r="E99" t="str">
         <v>EVENT</v>
       </c>
       <c r="F99" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G99">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H99" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I99" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J99" t="str">
         <v>Fourth</v>
@@ -5500,31 +5828,31 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>1789044064380-bLitz</v>
+        <v>1789045224902-dumau</v>
       </c>
       <c r="B100">
-        <v>1789044064380</v>
+        <v>1789045224902</v>
       </c>
       <c r="C100" t="str">
-        <v>bLitz</v>
+        <v>dumau</v>
       </c>
       <c r="D100" t="str">
-        <v>The MongolZ</v>
+        <v>Legacy</v>
       </c>
       <c r="E100" t="str">
         <v>EVENT</v>
       </c>
       <c r="F100" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H100" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J100" t="str">
         <v>Fourth</v>
@@ -5541,31 +5869,31 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>1789043946191-ultimate</v>
+        <v>1789045150461-levi</v>
       </c>
       <c r="B101">
-        <v>1789043946191</v>
+        <v>1789045150461</v>
       </c>
       <c r="C101" t="str">
-        <v>ultimate</v>
+        <v>levi</v>
       </c>
       <c r="D101" t="str">
-        <v>Liquid</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E101" t="str">
         <v>EVENT</v>
       </c>
       <c r="F101" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H101" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I101" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J101" t="str">
         <v>Fourth</v>
@@ -5582,31 +5910,31 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>1789043946191-siuhy</v>
+        <v>1789045150461-urban0</v>
       </c>
       <c r="B102">
-        <v>1789043946191</v>
+        <v>1789045150461</v>
       </c>
       <c r="C102" t="str">
-        <v>siuhy</v>
+        <v>urban0</v>
       </c>
       <c r="D102" t="str">
-        <v>Liquid</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E102" t="str">
         <v>EVENT</v>
       </c>
       <c r="F102" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G102">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H102" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J102" t="str">
         <v>Fourth</v>
@@ -5623,31 +5951,31 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>1789043946191-EliGE</v>
+        <v>1789045150461-t9rnay</v>
       </c>
       <c r="B103">
-        <v>1789043946191</v>
+        <v>1789045150461</v>
       </c>
       <c r="C103" t="str">
-        <v>EliGE</v>
+        <v>t9rnay</v>
       </c>
       <c r="D103" t="str">
-        <v>Liquid</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E103" t="str">
         <v>EVENT</v>
       </c>
       <c r="F103" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G103">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H103" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J103" t="str">
         <v>Fourth</v>
@@ -5664,31 +5992,31 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>1789043946191-NertZ</v>
+        <v>1789045150461-JOTA</v>
       </c>
       <c r="B104">
-        <v>1789043946191</v>
+        <v>1789045150461</v>
       </c>
       <c r="C104" t="str">
-        <v>NertZ</v>
+        <v>JOTA</v>
       </c>
       <c r="D104" t="str">
-        <v>Liquid</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E104" t="str">
         <v>EVENT</v>
       </c>
       <c r="F104" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G104">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H104" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I104" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J104" t="str">
         <v>Fourth</v>
@@ -5705,31 +6033,31 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>1789043946191-NAF</v>
+        <v>1789045150461-shz</v>
       </c>
       <c r="B105">
-        <v>1789043946191</v>
+        <v>1789045150461</v>
       </c>
       <c r="C105" t="str">
-        <v>NAF</v>
+        <v>shz</v>
       </c>
       <c r="D105" t="str">
-        <v>Liquid</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E105" t="str">
         <v>EVENT</v>
       </c>
       <c r="F105" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G105">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H105" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I105" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J105" t="str">
         <v>Fourth</v>
@@ -5746,34 +6074,34 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>1783531237020-mezii</v>
+        <v>1789045118610-huncho</v>
       </c>
       <c r="B106">
-        <v>1783531237020</v>
+        <v>1789045118610</v>
       </c>
       <c r="C106" t="str">
-        <v>mezii</v>
+        <v>huncho</v>
       </c>
       <c r="D106" t="str">
-        <v>Vitality</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E106" t="str">
         <v>EVENT</v>
       </c>
       <c r="F106" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G106">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H106" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I106" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J106" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K106">
         <v>1</v>
@@ -5787,34 +6115,34 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>1783531237020-flameZ</v>
+        <v>1789045118610-Crisp</v>
       </c>
       <c r="B107">
-        <v>1783531237020</v>
+        <v>1789045118610</v>
       </c>
       <c r="C107" t="str">
-        <v>flameZ</v>
+        <v>Crisp</v>
       </c>
       <c r="D107" t="str">
-        <v>Vitality</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E107" t="str">
         <v>EVENT</v>
       </c>
       <c r="F107" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G107">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H107" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I107" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J107" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K107">
         <v>1</v>
@@ -5828,34 +6156,34 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>1783531237020-ropz</v>
+        <v>1789045118610-FxRE</v>
       </c>
       <c r="B108">
-        <v>1783531237020</v>
+        <v>1789045118610</v>
       </c>
       <c r="C108" t="str">
-        <v>ropz</v>
+        <v>FxRE</v>
       </c>
       <c r="D108" t="str">
-        <v>Vitality</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E108" t="str">
         <v>EVENT</v>
       </c>
       <c r="F108" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G108">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H108" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I108" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J108" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K108">
         <v>1</v>
@@ -5869,34 +6197,34 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>1783531237020-apEX</v>
+        <v>1789045118610-Panic</v>
       </c>
       <c r="B109">
-        <v>1783531237020</v>
+        <v>1789045118610</v>
       </c>
       <c r="C109" t="str">
-        <v>apEX</v>
+        <v>Panic</v>
       </c>
       <c r="D109" t="str">
-        <v>Vitality</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E109" t="str">
         <v>EVENT</v>
       </c>
       <c r="F109" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G109">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H109" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I109" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J109" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K109">
         <v>1</v>
@@ -5910,34 +6238,34 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>1783531237020-ZywOo</v>
+        <v>1789045118610-REKMEISTER</v>
       </c>
       <c r="B110">
-        <v>1783531237020</v>
+        <v>1789045118610</v>
       </c>
       <c r="C110" t="str">
-        <v>ZywOo</v>
+        <v>REKMEISTER</v>
       </c>
       <c r="D110" t="str">
-        <v>Vitality</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E110" t="str">
         <v>EVENT</v>
       </c>
       <c r="F110" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G110">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H110" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I110" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J110" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K110">
         <v>1</v>
@@ -5951,31 +6279,31 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>1783531248336-kyousuke</v>
+        <v>1784854079769-Benkai</v>
       </c>
       <c r="B111">
-        <v>1783531248336</v>
+        <v>1784854079769</v>
       </c>
       <c r="C111" t="str">
-        <v>kyousuke</v>
+        <v>Benkai</v>
       </c>
       <c r="D111" t="str">
-        <v>Falcons</v>
+        <v>Entropiq</v>
       </c>
       <c r="E111" t="str">
         <v>EVENT</v>
       </c>
       <c r="F111" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G111">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H111" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I111" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J111" t="str">
         <v>Third</v>
@@ -5992,31 +6320,31 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>1783531248336-kyxsan</v>
+        <v>1784854079769-dea</v>
       </c>
       <c r="B112">
-        <v>1783531248336</v>
+        <v>1784854079769</v>
       </c>
       <c r="C112" t="str">
-        <v>kyxsan</v>
+        <v>dea</v>
       </c>
       <c r="D112" t="str">
-        <v>Falcons</v>
+        <v>Entropiq</v>
       </c>
       <c r="E112" t="str">
         <v>EVENT</v>
       </c>
       <c r="F112" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G112">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H112" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I112" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J112" t="str">
         <v>Third</v>
@@ -6033,31 +6361,31 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>1783531248336-NiKo</v>
+        <v>1784854079769-shane</v>
       </c>
       <c r="B113">
-        <v>1783531248336</v>
+        <v>1784854079769</v>
       </c>
       <c r="C113" t="str">
-        <v>NiKo</v>
+        <v>shane</v>
       </c>
       <c r="D113" t="str">
-        <v>Falcons</v>
+        <v>Entropiq</v>
       </c>
       <c r="E113" t="str">
         <v>EVENT</v>
       </c>
       <c r="F113" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G113">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H113" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I113" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J113" t="str">
         <v>Third</v>
@@ -6074,31 +6402,31 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>1783531248336-TeSeS</v>
+        <v>1784854079769-nosraC</v>
       </c>
       <c r="B114">
-        <v>1783531248336</v>
+        <v>1784854079769</v>
       </c>
       <c r="C114" t="str">
-        <v>TeSeS</v>
+        <v>nosraC</v>
       </c>
       <c r="D114" t="str">
-        <v>Falcons</v>
+        <v>Entropiq</v>
       </c>
       <c r="E114" t="str">
         <v>EVENT</v>
       </c>
       <c r="F114" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G114">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H114" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I114" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J114" t="str">
         <v>Third</v>
@@ -6115,31 +6443,31 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>1783531248336-m0NESY</v>
+        <v>1784854079769-MarKE</v>
       </c>
       <c r="B115">
-        <v>1783531248336</v>
+        <v>1784854079769</v>
       </c>
       <c r="C115" t="str">
-        <v>m0NESY</v>
+        <v>MarKE</v>
       </c>
       <c r="D115" t="str">
-        <v>Falcons</v>
+        <v>Entropiq</v>
       </c>
       <c r="E115" t="str">
         <v>EVENT</v>
       </c>
       <c r="F115" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G115">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H115" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I115" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J115" t="str">
         <v>Third</v>
@@ -6156,34 +6484,34 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>1789043725277-heroghoxxt</v>
-      </c>
-      <c r="B116" t="str">
-        <v/>
+        <v>1784854026526-ivz</v>
+      </c>
+      <c r="B116">
+        <v>1784854026526</v>
       </c>
       <c r="C116" t="str">
-        <v>heroghoxxt</v>
+        <v>ivz</v>
       </c>
       <c r="D116" t="str">
-        <v>Lux Tenebris</v>
+        <v>AMKAL</v>
       </c>
       <c r="E116" t="str">
         <v>EVENT</v>
       </c>
       <c r="F116" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G116">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H116" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I116" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J116" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K116">
         <v>1</v>
@@ -6197,34 +6525,34 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>1789043725277-kilzys</v>
-      </c>
-      <c r="B117" t="str">
-        <v/>
+        <v>1784854026526-abizz</v>
+      </c>
+      <c r="B117">
+        <v>1784854026526</v>
       </c>
       <c r="C117" t="str">
-        <v>kilzys</v>
+        <v>abizz</v>
       </c>
       <c r="D117" t="str">
-        <v>Lux Tenebris</v>
+        <v>AMKAL</v>
       </c>
       <c r="E117" t="str">
         <v>EVENT</v>
       </c>
       <c r="F117" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G117">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H117" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I117" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J117" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K117">
         <v>1</v>
@@ -6238,34 +6566,34 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>1783531219494-history</v>
+        <v>1784854026526-nacho</v>
       </c>
       <c r="B118">
-        <v>1783531219494</v>
+        <v>1784854026526</v>
       </c>
       <c r="C118" t="str">
-        <v>history</v>
+        <v>nacho</v>
       </c>
       <c r="D118" t="str">
-        <v>Iluminar</v>
+        <v>AMKAL</v>
       </c>
       <c r="E118" t="str">
         <v>EVENT</v>
       </c>
       <c r="F118" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G118">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H118" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I118" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J118" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K118">
         <v>1</v>
@@ -6279,34 +6607,34 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>1783531219494-SpavaQu</v>
+        <v>1784854026526-BK1</v>
       </c>
       <c r="B119">
-        <v>1783531219494</v>
+        <v>1784854026526</v>
       </c>
       <c r="C119" t="str">
-        <v>SpavaQu</v>
+        <v>BK1</v>
       </c>
       <c r="D119" t="str">
-        <v>Iluminar</v>
+        <v>AMKAL</v>
       </c>
       <c r="E119" t="str">
         <v>EVENT</v>
       </c>
       <c r="F119" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G119">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H119" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I119" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J119" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K119">
         <v>1</v>
@@ -6320,34 +6648,34 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>1783531219494-Pelle</v>
+        <v>1784854026526-next</v>
       </c>
       <c r="B120">
-        <v>1783531219494</v>
+        <v>1784854026526</v>
       </c>
       <c r="C120" t="str">
-        <v>Pelle</v>
+        <v>next</v>
       </c>
       <c r="D120" t="str">
-        <v>Iluminar</v>
+        <v>AMKAL</v>
       </c>
       <c r="E120" t="str">
         <v>EVENT</v>
       </c>
       <c r="F120" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G120">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H120" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I120" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J120" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K120">
         <v>1</v>
@@ -6360,23 +6688,23 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121">
-        <v>1787472254648</v>
-      </c>
-      <c r="B121" t="str">
-        <v/>
+      <c r="A121" t="str">
+        <v>1784848026994-molodoy</v>
+      </c>
+      <c r="B121">
+        <v>1784848026994</v>
       </c>
       <c r="C121" t="str">
-        <v>REZ</v>
+        <v>molodoy</v>
       </c>
       <c r="D121" t="str">
-        <v>Astana Dragons</v>
+        <v>FURIA</v>
       </c>
       <c r="E121" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F121" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -6385,7 +6713,7 @@
         <v>Regional</v>
       </c>
       <c r="I121" t="str">
-        <v>Europe</v>
+        <v>America</v>
       </c>
       <c r="J121" t="str">
         <v>Winner</v>
@@ -6401,23 +6729,23 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122">
-        <v>1787472247600</v>
-      </c>
-      <c r="B122" t="str">
-        <v/>
+      <c r="A122" t="str">
+        <v>1784848026994-KSCERATO</v>
+      </c>
+      <c r="B122">
+        <v>1784848026994</v>
       </c>
       <c r="C122" t="str">
-        <v>kr1vda</v>
+        <v>KSCERATO</v>
       </c>
       <c r="D122" t="str">
-        <v>Vox Eminor</v>
+        <v>FURIA</v>
       </c>
       <c r="E122" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F122" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -6426,7 +6754,7 @@
         <v>Regional</v>
       </c>
       <c r="I122" t="str">
-        <v>Europe</v>
+        <v>America</v>
       </c>
       <c r="J122" t="str">
         <v>Winner</v>
@@ -6442,23 +6770,23 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123">
-        <v>1787472243903</v>
-      </c>
-      <c r="B123" t="str">
-        <v/>
+      <c r="A123" t="str">
+        <v>1784848026994-YEKINDAR</v>
+      </c>
+      <c r="B123">
+        <v>1784848026994</v>
       </c>
       <c r="C123" t="str">
-        <v>fear</v>
+        <v>YEKINDAR</v>
       </c>
       <c r="D123" t="str">
-        <v>Fnatic</v>
+        <v>FURIA</v>
       </c>
       <c r="E123" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F123" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -6467,7 +6795,7 @@
         <v>Regional</v>
       </c>
       <c r="I123" t="str">
-        <v>Europe</v>
+        <v>America</v>
       </c>
       <c r="J123" t="str">
         <v>Winner</v>
@@ -6483,23 +6811,23 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124">
-        <v>1787472232104</v>
-      </c>
-      <c r="B124" t="str">
-        <v/>
+      <c r="A124" t="str">
+        <v>1784848026994-yuurih</v>
+      </c>
+      <c r="B124">
+        <v>1784848026994</v>
       </c>
       <c r="C124" t="str">
-        <v>KRIMZ</v>
+        <v>yuurih</v>
       </c>
       <c r="D124" t="str">
-        <v>Fnatic</v>
+        <v>FURIA</v>
       </c>
       <c r="E124" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F124" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -6508,7 +6836,7 @@
         <v>Regional</v>
       </c>
       <c r="I124" t="str">
-        <v>Europe</v>
+        <v>America</v>
       </c>
       <c r="J124" t="str">
         <v>Winner</v>
@@ -6524,23 +6852,23 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125">
-        <v>1787472226864</v>
-      </c>
-      <c r="B125" t="str">
-        <v/>
+      <c r="A125" t="str">
+        <v>1784848026994-FalleN</v>
+      </c>
+      <c r="B125">
+        <v>1784848026994</v>
       </c>
       <c r="C125" t="str">
-        <v>blameF</v>
+        <v>FalleN</v>
       </c>
       <c r="D125" t="str">
-        <v>Fnatic</v>
+        <v>FURIA</v>
       </c>
       <c r="E125" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F125" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -6549,7 +6877,7 @@
         <v>Regional</v>
       </c>
       <c r="I125" t="str">
-        <v>Europe</v>
+        <v>America</v>
       </c>
       <c r="J125" t="str">
         <v>Winner</v>
@@ -6565,35 +6893,35 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126">
-        <v>1784847962039</v>
-      </c>
-      <c r="B126" t="str">
-        <v/>
+      <c r="A126" t="str">
+        <v>1789044307262-sowalio</v>
+      </c>
+      <c r="B126">
+        <v>1789044307262</v>
       </c>
       <c r="C126" t="str">
-        <v>abizz</v>
+        <v>sowalio</v>
       </c>
       <c r="D126" t="str">
-        <v>AMKAL</v>
+        <v>Nemiga</v>
       </c>
       <c r="E126" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F126" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G126">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H126" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I126" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J126" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K126">
         <v>1</v>
@@ -6606,35 +6934,35 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127">
-        <v>1784847955956</v>
-      </c>
-      <c r="B127" t="str">
-        <v/>
+      <c r="A127" t="str">
+        <v>1789044307262-khaN</v>
+      </c>
+      <c r="B127">
+        <v>1789044307262</v>
       </c>
       <c r="C127" t="str">
-        <v>next</v>
+        <v>khaN</v>
       </c>
       <c r="D127" t="str">
-        <v>AMKAL</v>
+        <v>Nemiga</v>
       </c>
       <c r="E127" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F127" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G127">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H127" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I127" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J127" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K127">
         <v>1</v>
@@ -6647,35 +6975,35 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128">
-        <v>1784847948890</v>
-      </c>
-      <c r="B128" t="str">
-        <v/>
+      <c r="A128" t="str">
+        <v>1789044307262-riskyb0b</v>
+      </c>
+      <c r="B128">
+        <v>1789044307262</v>
       </c>
       <c r="C128" t="str">
-        <v>yuurih</v>
+        <v>riskyb0b</v>
       </c>
       <c r="D128" t="str">
-        <v>FURIA</v>
+        <v>Nemiga</v>
       </c>
       <c r="E128" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F128" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G128">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H128" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I128" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J128" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K128">
         <v>1</v>
@@ -6688,35 +7016,35 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129">
-        <v>1784847943609</v>
-      </c>
-      <c r="B129" t="str">
-        <v/>
+      <c r="A129" t="str">
+        <v>1789044307262-1eeR</v>
+      </c>
+      <c r="B129">
+        <v>1789044307262</v>
       </c>
       <c r="C129" t="str">
-        <v>KSCERATO</v>
+        <v>1eeR</v>
       </c>
       <c r="D129" t="str">
-        <v>FURIA</v>
+        <v>Nemiga</v>
       </c>
       <c r="E129" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F129" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H129" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I129" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J129" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K129">
         <v>1</v>
@@ -6729,35 +7057,35 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130">
-        <v>1784847935905</v>
-      </c>
-      <c r="B130" t="str">
-        <v/>
+      <c r="A130" t="str">
+        <v>1789044307262-Xant3r</v>
+      </c>
+      <c r="B130">
+        <v>1789044307262</v>
       </c>
       <c r="C130" t="str">
-        <v>molodoy</v>
+        <v>Xant3r</v>
       </c>
       <c r="D130" t="str">
-        <v>FURIA</v>
+        <v>Nemiga</v>
       </c>
       <c r="E130" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F130" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G130">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H130" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I130" t="str">
-        <v>America</v>
+        <v/>
       </c>
       <c r="J130" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K130">
         <v>1</v>
@@ -6770,20 +7098,20 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131">
-        <v>1783531290361</v>
-      </c>
-      <c r="B131" t="str">
-        <v/>
+      <c r="A131" t="str">
+        <v>1789044244253-w0nderful</v>
+      </c>
+      <c r="B131">
+        <v>1789044244253</v>
       </c>
       <c r="C131" t="str">
-        <v>m0NESY</v>
+        <v>w0nderful</v>
       </c>
       <c r="D131" t="str">
-        <v>Falcons</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E131" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F131" t="str">
         <v>DreamHack Winter 2026</v>
@@ -6798,7 +7126,7 @@
         <v/>
       </c>
       <c r="J131" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K131">
         <v>1</v>
@@ -6811,20 +7139,20 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132">
-        <v>1783531284605</v>
-      </c>
-      <c r="B132" t="str">
-        <v/>
+      <c r="A132" t="str">
+        <v>1789044244253-makazze</v>
+      </c>
+      <c r="B132">
+        <v>1789044244253</v>
       </c>
       <c r="C132" t="str">
-        <v>ropz</v>
+        <v>makazze</v>
       </c>
       <c r="D132" t="str">
-        <v>Vitality</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E132" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F132" t="str">
         <v>DreamHack Winter 2026</v>
@@ -6839,7 +7167,7 @@
         <v/>
       </c>
       <c r="J132" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K132">
         <v>1</v>
@@ -6852,20 +7180,20 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133">
-        <v>1783531278450</v>
-      </c>
-      <c r="B133" t="str">
-        <v/>
+      <c r="A133" t="str">
+        <v>1789044244253-b1t</v>
+      </c>
+      <c r="B133">
+        <v>1789044244253</v>
       </c>
       <c r="C133" t="str">
-        <v>ZywOo</v>
+        <v>b1t</v>
       </c>
       <c r="D133" t="str">
-        <v>Vitality</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E133" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F133" t="str">
         <v>DreamHack Winter 2026</v>
@@ -6880,7 +7208,7 @@
         <v/>
       </c>
       <c r="J133" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K133">
         <v>1</v>
@@ -6893,20 +7221,20 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134">
-        <v>1783531271104</v>
-      </c>
-      <c r="B134" t="str">
-        <v/>
+      <c r="A134" t="str">
+        <v>1789044244253-iM</v>
+      </c>
+      <c r="B134">
+        <v>1789044244253</v>
       </c>
       <c r="C134" t="str">
-        <v>heroghoxxt</v>
+        <v>iM</v>
       </c>
       <c r="D134" t="str">
-        <v>Iluminar</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E134" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F134" t="str">
         <v>DreamHack Winter 2026</v>
@@ -6921,7 +7249,7 @@
         <v/>
       </c>
       <c r="J134" t="str">
-        <v>Winner</v>
+        <v>Fourth</v>
       </c>
       <c r="K134">
         <v>1</v>
@@ -6934,20 +7262,20 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135">
-        <v>1783531262507</v>
-      </c>
-      <c r="B135" t="str">
-        <v/>
+      <c r="A135" t="str">
+        <v>1789044244253-Aleksib</v>
+      </c>
+      <c r="B135">
+        <v>1789044244253</v>
       </c>
       <c r="C135" t="str">
-        <v>kilzys</v>
+        <v>Aleksib</v>
       </c>
       <c r="D135" t="str">
-        <v>Iluminar</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E135" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F135" t="str">
         <v>DreamHack Winter 2026</v>
@@ -6962,21 +7290,1866 @@
         <v/>
       </c>
       <c r="J135" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>1789044197304-Dytor</v>
+      </c>
+      <c r="B136">
+        <v>1789044197304</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Dytor</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E136" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F136" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G136">
+        <v>5</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>1789044197304-nbqq</v>
+      </c>
+      <c r="B137">
+        <v>1789044197304</v>
+      </c>
+      <c r="C137" t="str">
+        <v>nbqq</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E137" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F137" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G137">
+        <v>5</v>
+      </c>
+      <c r="H137" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>1789044197304-forsyy</v>
+      </c>
+      <c r="B138">
+        <v>1789044197304</v>
+      </c>
+      <c r="C138" t="str">
+        <v>forsyy</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E138" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F138" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G138">
+        <v>5</v>
+      </c>
+      <c r="H138" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>1789044197304-ROGA</v>
+      </c>
+      <c r="B139">
+        <v>1789044197304</v>
+      </c>
+      <c r="C139" t="str">
+        <v>ROGA</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E139" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F139" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G139">
+        <v>5</v>
+      </c>
+      <c r="H139" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>1789044197304-DANK1NG</v>
+      </c>
+      <c r="B140">
+        <v>1789044197304</v>
+      </c>
+      <c r="C140" t="str">
+        <v>DANK1NG</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Copenhagen Flames</v>
+      </c>
+      <c r="E140" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F140" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G140">
+        <v>5</v>
+      </c>
+      <c r="H140" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>1789044064380-910</v>
+      </c>
+      <c r="B141">
+        <v>1789044064380</v>
+      </c>
+      <c r="C141" t="str">
+        <v>910</v>
+      </c>
+      <c r="D141" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E141" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F141" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G141">
+        <v>5</v>
+      </c>
+      <c r="H141" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K141">
+        <v>1</v>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>1789044064380-mzinho</v>
+      </c>
+      <c r="B142">
+        <v>1789044064380</v>
+      </c>
+      <c r="C142" t="str">
+        <v>mzinho</v>
+      </c>
+      <c r="D142" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E142" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F142" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G142">
+        <v>5</v>
+      </c>
+      <c r="H142" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I142" t="str">
+        <v/>
+      </c>
+      <c r="J142" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>1789044064380-Senzu</v>
+      </c>
+      <c r="B143">
+        <v>1789044064380</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Senzu</v>
+      </c>
+      <c r="D143" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E143" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F143" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G143">
+        <v>5</v>
+      </c>
+      <c r="H143" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+      <c r="J143" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K143">
+        <v>1</v>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>1789044064380-Techno</v>
+      </c>
+      <c r="B144">
+        <v>1789044064380</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Techno</v>
+      </c>
+      <c r="D144" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E144" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F144" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G144">
+        <v>5</v>
+      </c>
+      <c r="H144" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K144">
+        <v>1</v>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>1789044064380-bLitz</v>
+      </c>
+      <c r="B145">
+        <v>1789044064380</v>
+      </c>
+      <c r="C145" t="str">
+        <v>bLitz</v>
+      </c>
+      <c r="D145" t="str">
+        <v>The MongolZ</v>
+      </c>
+      <c r="E145" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F145" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G145">
+        <v>5</v>
+      </c>
+      <c r="H145" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K145">
+        <v>1</v>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>1789043946191-ultimate</v>
+      </c>
+      <c r="B146">
+        <v>1789043946191</v>
+      </c>
+      <c r="C146" t="str">
+        <v>ultimate</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E146" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F146" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G146">
+        <v>5</v>
+      </c>
+      <c r="H146" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+      <c r="J146" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K146">
+        <v>1</v>
+      </c>
+      <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>1789043946191-siuhy</v>
+      </c>
+      <c r="B147">
+        <v>1789043946191</v>
+      </c>
+      <c r="C147" t="str">
+        <v>siuhy</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E147" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F147" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G147">
+        <v>5</v>
+      </c>
+      <c r="H147" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+      <c r="J147" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>1789043946191-EliGE</v>
+      </c>
+      <c r="B148">
+        <v>1789043946191</v>
+      </c>
+      <c r="C148" t="str">
+        <v>EliGE</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E148" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F148" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G148">
+        <v>5</v>
+      </c>
+      <c r="H148" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>1789043946191-NertZ</v>
+      </c>
+      <c r="B149">
+        <v>1789043946191</v>
+      </c>
+      <c r="C149" t="str">
+        <v>NertZ</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E149" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F149" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G149">
+        <v>5</v>
+      </c>
+      <c r="H149" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I149" t="str">
+        <v/>
+      </c>
+      <c r="J149" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+      <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>1789043946191-NAF</v>
+      </c>
+      <c r="B150">
+        <v>1789043946191</v>
+      </c>
+      <c r="C150" t="str">
+        <v>NAF</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Liquid</v>
+      </c>
+      <c r="E150" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F150" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G150">
+        <v>5</v>
+      </c>
+      <c r="H150" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150" t="str">
+        <v>Fourth</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>1783531237020-mezii</v>
+      </c>
+      <c r="B151">
+        <v>1783531237020</v>
+      </c>
+      <c r="C151" t="str">
+        <v>mezii</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E151" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F151" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G151">
+        <v>5</v>
+      </c>
+      <c r="H151" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I151" t="str">
+        <v/>
+      </c>
+      <c r="J151" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>1783531237020-flameZ</v>
+      </c>
+      <c r="B152">
+        <v>1783531237020</v>
+      </c>
+      <c r="C152" t="str">
+        <v>flameZ</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E152" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F152" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G152">
+        <v>5</v>
+      </c>
+      <c r="H152" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K152">
+        <v>1</v>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>1783531237020-ropz</v>
+      </c>
+      <c r="B153">
+        <v>1783531237020</v>
+      </c>
+      <c r="C153" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E153" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F153" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G153">
+        <v>5</v>
+      </c>
+      <c r="H153" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
+      <c r="J153" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K153">
+        <v>1</v>
+      </c>
+      <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>1783531237020-apEX</v>
+      </c>
+      <c r="B154">
+        <v>1783531237020</v>
+      </c>
+      <c r="C154" t="str">
+        <v>apEX</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E154" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F154" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G154">
+        <v>5</v>
+      </c>
+      <c r="H154" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>1783531237020-ZywOo</v>
+      </c>
+      <c r="B155">
+        <v>1783531237020</v>
+      </c>
+      <c r="C155" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E155" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F155" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G155">
+        <v>5</v>
+      </c>
+      <c r="H155" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>1783531248336-kyousuke</v>
+      </c>
+      <c r="B156">
+        <v>1783531248336</v>
+      </c>
+      <c r="C156" t="str">
+        <v>kyousuke</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E156" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F156" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G156">
+        <v>5</v>
+      </c>
+      <c r="H156" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I156" t="str">
+        <v/>
+      </c>
+      <c r="J156" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>1783531248336-kyxsan</v>
+      </c>
+      <c r="B157">
+        <v>1783531248336</v>
+      </c>
+      <c r="C157" t="str">
+        <v>kyxsan</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E157" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F157" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G157">
+        <v>5</v>
+      </c>
+      <c r="H157" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>1783531248336-NiKo</v>
+      </c>
+      <c r="B158">
+        <v>1783531248336</v>
+      </c>
+      <c r="C158" t="str">
+        <v>NiKo</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E158" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F158" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G158">
+        <v>5</v>
+      </c>
+      <c r="H158" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
+      <c r="J158" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+      <c r="L158" t="str">
+        <v/>
+      </c>
+      <c r="M158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>1783531248336-TeSeS</v>
+      </c>
+      <c r="B159">
+        <v>1783531248336</v>
+      </c>
+      <c r="C159" t="str">
+        <v>TeSeS</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E159" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F159" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G159">
+        <v>5</v>
+      </c>
+      <c r="H159" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
+      <c r="J159" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>1783531248336-m0NESY</v>
+      </c>
+      <c r="B160">
+        <v>1783531248336</v>
+      </c>
+      <c r="C160" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E160" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F160" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G160">
+        <v>5</v>
+      </c>
+      <c r="H160" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
+      <c r="J160" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>1789043725277-heroghoxxt</v>
+      </c>
+      <c r="B161" t="str">
+        <v/>
+      </c>
+      <c r="C161" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="E161" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F161" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G161">
+        <v>5</v>
+      </c>
+      <c r="H161" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
+      <c r="J161" t="str">
         <v>Winner</v>
       </c>
-      <c r="K135">
-        <v>1</v>
-      </c>
-      <c r="L135" t="str">
-        <v/>
-      </c>
-      <c r="M135" t="str">
+      <c r="K161">
+        <v>1</v>
+      </c>
+      <c r="L161" t="str">
+        <v/>
+      </c>
+      <c r="M161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>1789043725277-kilzys</v>
+      </c>
+      <c r="B162" t="str">
+        <v/>
+      </c>
+      <c r="C162" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="E162" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F162" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G162">
+        <v>5</v>
+      </c>
+      <c r="H162" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
+      <c r="J162" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>1783531219494-history</v>
+      </c>
+      <c r="B163">
+        <v>1783531219494</v>
+      </c>
+      <c r="C163" t="str">
+        <v>history</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E163" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F163" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G163">
+        <v>5</v>
+      </c>
+      <c r="H163" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>1783531219494-SpavaQu</v>
+      </c>
+      <c r="B164">
+        <v>1783531219494</v>
+      </c>
+      <c r="C164" t="str">
+        <v>SpavaQu</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E164" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F164" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G164">
+        <v>5</v>
+      </c>
+      <c r="H164" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>1783531219494-Pelle</v>
+      </c>
+      <c r="B165">
+        <v>1783531219494</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Pelle</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E165" t="str">
+        <v>EVENT</v>
+      </c>
+      <c r="F165" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G165">
+        <v>5</v>
+      </c>
+      <c r="H165" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>1787472254648</v>
+      </c>
+      <c r="B166" t="str">
+        <v/>
+      </c>
+      <c r="C166" t="str">
+        <v>REZ</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Astana Dragons</v>
+      </c>
+      <c r="E166" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F166" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I166" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="J166" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>1787472247600</v>
+      </c>
+      <c r="B167" t="str">
+        <v/>
+      </c>
+      <c r="C167" t="str">
+        <v>kr1vda</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Vox Eminor</v>
+      </c>
+      <c r="E167" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G167">
+        <v>1</v>
+      </c>
+      <c r="H167" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I167" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="J167" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>1787472243903</v>
+      </c>
+      <c r="B168" t="str">
+        <v/>
+      </c>
+      <c r="C168" t="str">
+        <v>fear</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Fnatic</v>
+      </c>
+      <c r="E168" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F168" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I168" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="J168" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>1787472232104</v>
+      </c>
+      <c r="B169" t="str">
+        <v/>
+      </c>
+      <c r="C169" t="str">
+        <v>KRIMZ</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Fnatic</v>
+      </c>
+      <c r="E169" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F169" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+      <c r="H169" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I169" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="J169" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>1787472226864</v>
+      </c>
+      <c r="B170" t="str">
+        <v/>
+      </c>
+      <c r="C170" t="str">
+        <v>blameF</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Fnatic</v>
+      </c>
+      <c r="E170" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F170" t="str">
+        <v>Winamax Spanish Cirtuit  2026</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I170" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="J170" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>1784847962039</v>
+      </c>
+      <c r="B171" t="str">
+        <v/>
+      </c>
+      <c r="C171" t="str">
+        <v>abizz</v>
+      </c>
+      <c r="D171" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E171" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F171" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I171" t="str">
+        <v>America</v>
+      </c>
+      <c r="J171" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>1784847955956</v>
+      </c>
+      <c r="B172" t="str">
+        <v/>
+      </c>
+      <c r="C172" t="str">
+        <v>next</v>
+      </c>
+      <c r="D172" t="str">
+        <v>AMKAL</v>
+      </c>
+      <c r="E172" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F172" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I172" t="str">
+        <v>America</v>
+      </c>
+      <c r="J172" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>1784847948890</v>
+      </c>
+      <c r="B173" t="str">
+        <v/>
+      </c>
+      <c r="C173" t="str">
+        <v>yuurih</v>
+      </c>
+      <c r="D173" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E173" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F173" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I173" t="str">
+        <v>America</v>
+      </c>
+      <c r="J173" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>1784847943609</v>
+      </c>
+      <c r="B174" t="str">
+        <v/>
+      </c>
+      <c r="C174" t="str">
+        <v>KSCERATO</v>
+      </c>
+      <c r="D174" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E174" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F174" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+      <c r="H174" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I174" t="str">
+        <v>America</v>
+      </c>
+      <c r="J174" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>1784847935905</v>
+      </c>
+      <c r="B175" t="str">
+        <v/>
+      </c>
+      <c r="C175" t="str">
+        <v>molodoy</v>
+      </c>
+      <c r="D175" t="str">
+        <v>FURIA</v>
+      </c>
+      <c r="E175" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F175" t="str">
+        <v>FiReLEAGUE Buenos Aires 2026</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="I175" t="str">
+        <v>America</v>
+      </c>
+      <c r="J175" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>1783531290361</v>
+      </c>
+      <c r="B176" t="str">
+        <v/>
+      </c>
+      <c r="C176" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E176" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F176" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G176">
+        <v>5</v>
+      </c>
+      <c r="H176" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>1783531284605</v>
+      </c>
+      <c r="B177" t="str">
+        <v/>
+      </c>
+      <c r="C177" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E177" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F177" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G177">
+        <v>5</v>
+      </c>
+      <c r="H177" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>1783531278450</v>
+      </c>
+      <c r="B178" t="str">
+        <v/>
+      </c>
+      <c r="C178" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E178" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F178" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G178">
+        <v>5</v>
+      </c>
+      <c r="H178" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>1783531271104</v>
+      </c>
+      <c r="B179" t="str">
+        <v/>
+      </c>
+      <c r="C179" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E179" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F179" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G179">
+        <v>5</v>
+      </c>
+      <c r="H179" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>1783531262507</v>
+      </c>
+      <c r="B180" t="str">
+        <v/>
+      </c>
+      <c r="C180" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E180" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F180" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G180">
+        <v>5</v>
+      </c>
+      <c r="H180" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M135"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M180"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -8338,7 +8338,7 @@
         <v>heroghoxxt</v>
       </c>
       <c r="D161" t="str">
-        <v>Lux Tenebris</v>
+        <v>Iluminar</v>
       </c>
       <c r="E161" t="str">
         <v>EVENT</v>
@@ -8379,7 +8379,7 @@
         <v>kilzys</v>
       </c>
       <c r="D162" t="str">
-        <v>Lux Tenebris</v>
+        <v>Iluminar</v>
       </c>
       <c r="E162" t="str">
         <v>EVENT</v>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -2093,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M220"/>
+  <dimension ref="A1:M225"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2137,20 +2137,20 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1790465222432-slimey</v>
-      </c>
-      <c r="B2">
-        <v>1790465222432</v>
+      <c r="A2">
+        <v>1790466260757</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>slimey</v>
+        <v>Triton</v>
       </c>
       <c r="D2" t="str">
-        <v>Rogue</v>
+        <v>Bravado</v>
       </c>
       <c r="E2" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F2" t="str">
         <v>Fragadelphia 2026</v>
@@ -2165,7 +2165,7 @@
         <v>Asia</v>
       </c>
       <c r="J2" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -2178,20 +2178,20 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>1790465222432-TjP</v>
-      </c>
-      <c r="B3">
-        <v>1790465222432</v>
+      <c r="A3">
+        <v>1790466256728</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>TjP</v>
+        <v>m1N1</v>
       </c>
       <c r="D3" t="str">
-        <v>Rogue</v>
+        <v>LGB</v>
       </c>
       <c r="E3" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F3" t="str">
         <v>Fragadelphia 2026</v>
@@ -2206,7 +2206,7 @@
         <v>Asia</v>
       </c>
       <c r="J3" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2219,20 +2219,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>1790465222432-asap</v>
-      </c>
-      <c r="B4">
-        <v>1790465222432</v>
+      <c r="A4">
+        <v>1790466252073</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v>asap</v>
+        <v>0z</v>
       </c>
       <c r="D4" t="str">
-        <v>Rogue</v>
+        <v>kONO</v>
       </c>
       <c r="E4" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F4" t="str">
         <v>Fragadelphia 2026</v>
@@ -2247,7 +2247,7 @@
         <v>Asia</v>
       </c>
       <c r="J4" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2260,20 +2260,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>1790465222432-DannyG</v>
-      </c>
-      <c r="B5">
-        <v>1790465222432</v>
+      <c r="A5">
+        <v>1790466163177</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>DannyG</v>
+        <v>somebody</v>
       </c>
       <c r="D5" t="str">
-        <v>Rogue</v>
+        <v>kONO</v>
       </c>
       <c r="E5" t="str">
-        <v>EVENT</v>
+        <v>EVP</v>
       </c>
       <c r="F5" t="str">
         <v>Fragadelphia 2026</v>
@@ -2288,7 +2288,7 @@
         <v>Asia</v>
       </c>
       <c r="J5" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2301,20 +2301,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>1790465222432-chelleos</v>
-      </c>
-      <c r="B6">
-        <v>1790465222432</v>
+      <c r="A6">
+        <v>1790466152494</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>chelleos</v>
+        <v>NIGHT666LADE</v>
       </c>
       <c r="D6" t="str">
-        <v>Rogue</v>
+        <v>kONO</v>
       </c>
       <c r="E6" t="str">
-        <v>EVENT</v>
+        <v>MVP</v>
       </c>
       <c r="F6" t="str">
         <v>Fragadelphia 2026</v>
@@ -2329,7 +2329,7 @@
         <v>Asia</v>
       </c>
       <c r="J6" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -2343,16 +2343,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1790465217923-suki</v>
+        <v>1790465222432-slimey</v>
       </c>
       <c r="B7">
-        <v>1790465217923</v>
+        <v>1790465222432</v>
       </c>
       <c r="C7" t="str">
-        <v>suki</v>
+        <v>slimey</v>
       </c>
       <c r="D7" t="str">
-        <v>GATERON</v>
+        <v>Rogue</v>
       </c>
       <c r="E7" t="str">
         <v>EVENT</v>
@@ -2384,16 +2384,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1790465217923-2x2x</v>
+        <v>1790465222432-TjP</v>
       </c>
       <c r="B8">
-        <v>1790465217923</v>
+        <v>1790465222432</v>
       </c>
       <c r="C8" t="str">
-        <v>2x2x</v>
+        <v>TjP</v>
       </c>
       <c r="D8" t="str">
-        <v>GATERON</v>
+        <v>Rogue</v>
       </c>
       <c r="E8" t="str">
         <v>EVENT</v>
@@ -2425,16 +2425,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1790465217923-Miami</v>
+        <v>1790465222432-asap</v>
       </c>
       <c r="B9">
-        <v>1790465217923</v>
+        <v>1790465222432</v>
       </c>
       <c r="C9" t="str">
-        <v>Miami</v>
+        <v>asap</v>
       </c>
       <c r="D9" t="str">
-        <v>GATERON</v>
+        <v>Rogue</v>
       </c>
       <c r="E9" t="str">
         <v>EVENT</v>
@@ -2466,16 +2466,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1790465217923-rage</v>
+        <v>1790465222432-DannyG</v>
       </c>
       <c r="B10">
-        <v>1790465217923</v>
+        <v>1790465222432</v>
       </c>
       <c r="C10" t="str">
-        <v>rage</v>
+        <v>DannyG</v>
       </c>
       <c r="D10" t="str">
-        <v>GATERON</v>
+        <v>Rogue</v>
       </c>
       <c r="E10" t="str">
         <v>EVENT</v>
@@ -2507,16 +2507,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1790465217923-SPine</v>
+        <v>1790465222432-chelleos</v>
       </c>
       <c r="B11">
-        <v>1790465217923</v>
+        <v>1790465222432</v>
       </c>
       <c r="C11" t="str">
-        <v>SPine</v>
+        <v>chelleos</v>
       </c>
       <c r="D11" t="str">
-        <v>GATERON</v>
+        <v>Rogue</v>
       </c>
       <c r="E11" t="str">
         <v>EVENT</v>
@@ -2548,16 +2548,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1790465213739-jung1e</v>
+        <v>1790465217923-suki</v>
       </c>
       <c r="B12">
-        <v>1790465213739</v>
+        <v>1790465217923</v>
       </c>
       <c r="C12" t="str">
-        <v>jung1e</v>
+        <v>suki</v>
       </c>
       <c r="D12" t="str">
-        <v>FORZE</v>
+        <v>GATERON</v>
       </c>
       <c r="E12" t="str">
         <v>EVENT</v>
@@ -2589,16 +2589,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1790465213739-3gl</v>
+        <v>1790465217923-2x2x</v>
       </c>
       <c r="B13">
-        <v>1790465213739</v>
+        <v>1790465217923</v>
       </c>
       <c r="C13" t="str">
-        <v>3gl</v>
+        <v>2x2x</v>
       </c>
       <c r="D13" t="str">
-        <v>FORZE</v>
+        <v>GATERON</v>
       </c>
       <c r="E13" t="str">
         <v>EVENT</v>
@@ -2630,16 +2630,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1790465213739-p5p</v>
+        <v>1790465217923-Miami</v>
       </c>
       <c r="B14">
-        <v>1790465213739</v>
+        <v>1790465217923</v>
       </c>
       <c r="C14" t="str">
-        <v>p5p</v>
+        <v>Miami</v>
       </c>
       <c r="D14" t="str">
-        <v>FORZE</v>
+        <v>GATERON</v>
       </c>
       <c r="E14" t="str">
         <v>EVENT</v>
@@ -2671,16 +2671,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>1790465213739-chengking</v>
+        <v>1790465217923-rage</v>
       </c>
       <c r="B15">
-        <v>1790465213739</v>
+        <v>1790465217923</v>
       </c>
       <c r="C15" t="str">
-        <v>chengking</v>
+        <v>rage</v>
       </c>
       <c r="D15" t="str">
-        <v>FORZE</v>
+        <v>GATERON</v>
       </c>
       <c r="E15" t="str">
         <v>EVENT</v>
@@ -2712,16 +2712,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1790465213739-1337x9</v>
+        <v>1790465217923-SPine</v>
       </c>
       <c r="B16">
-        <v>1790465213739</v>
+        <v>1790465217923</v>
       </c>
       <c r="C16" t="str">
-        <v>1337x9</v>
+        <v>SPine</v>
       </c>
       <c r="D16" t="str">
-        <v>FORZE</v>
+        <v>GATERON</v>
       </c>
       <c r="E16" t="str">
         <v>EVENT</v>
@@ -2753,16 +2753,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>1790465209723-Zy88</v>
+        <v>1790465213739-jung1e</v>
       </c>
       <c r="B17">
-        <v>1790465209723</v>
+        <v>1790465213739</v>
       </c>
       <c r="C17" t="str">
-        <v>Zy88</v>
+        <v>jung1e</v>
       </c>
       <c r="D17" t="str">
-        <v>Shika</v>
+        <v>FORZE</v>
       </c>
       <c r="E17" t="str">
         <v>EVENT</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1790465209723-jiejie</v>
+        <v>1790465213739-3gl</v>
       </c>
       <c r="B18">
-        <v>1790465209723</v>
+        <v>1790465213739</v>
       </c>
       <c r="C18" t="str">
-        <v>jiejie</v>
+        <v>3gl</v>
       </c>
       <c r="D18" t="str">
-        <v>Shika</v>
+        <v>FORZE</v>
       </c>
       <c r="E18" t="str">
         <v>EVENT</v>
@@ -2835,16 +2835,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1790465209723-Biuckmt</v>
+        <v>1790465213739-p5p</v>
       </c>
       <c r="B19">
-        <v>1790465209723</v>
+        <v>1790465213739</v>
       </c>
       <c r="C19" t="str">
-        <v>Biuckmt</v>
+        <v>p5p</v>
       </c>
       <c r="D19" t="str">
-        <v>Shika</v>
+        <v>FORZE</v>
       </c>
       <c r="E19" t="str">
         <v>EVENT</v>
@@ -2876,16 +2876,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1790465209723-ImpressioN</v>
+        <v>1790465213739-chengking</v>
       </c>
       <c r="B20">
-        <v>1790465209723</v>
+        <v>1790465213739</v>
       </c>
       <c r="C20" t="str">
-        <v>ImpressioN</v>
+        <v>chengking</v>
       </c>
       <c r="D20" t="str">
-        <v>Shika</v>
+        <v>FORZE</v>
       </c>
       <c r="E20" t="str">
         <v>EVENT</v>
@@ -2917,16 +2917,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1790465209723-splashske</v>
+        <v>1790465213739-1337x9</v>
       </c>
       <c r="B21">
-        <v>1790465209723</v>
+        <v>1790465213739</v>
       </c>
       <c r="C21" t="str">
-        <v>splashske</v>
+        <v>1337x9</v>
       </c>
       <c r="D21" t="str">
-        <v>Shika</v>
+        <v>FORZE</v>
       </c>
       <c r="E21" t="str">
         <v>EVENT</v>
@@ -2958,16 +2958,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1790465205562-Annihilation</v>
+        <v>1790465209723-Zy88</v>
       </c>
       <c r="B22">
-        <v>1790465205562</v>
+        <v>1790465209723</v>
       </c>
       <c r="C22" t="str">
-        <v>Annihilation</v>
+        <v>Zy88</v>
       </c>
       <c r="D22" t="str">
-        <v>Avangar</v>
+        <v>Shika</v>
       </c>
       <c r="E22" t="str">
         <v>EVENT</v>
@@ -2999,16 +2999,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>1790465205562-fejtZ</v>
+        <v>1790465209723-jiejie</v>
       </c>
       <c r="B23">
-        <v>1790465205562</v>
+        <v>1790465209723</v>
       </c>
       <c r="C23" t="str">
-        <v>fejtZ</v>
+        <v>jiejie</v>
       </c>
       <c r="D23" t="str">
-        <v>Avangar</v>
+        <v>Shika</v>
       </c>
       <c r="E23" t="str">
         <v>EVENT</v>
@@ -3040,16 +3040,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>1790465205562-XigN</v>
+        <v>1790465209723-Biuckmt</v>
       </c>
       <c r="B24">
-        <v>1790465205562</v>
+        <v>1790465209723</v>
       </c>
       <c r="C24" t="str">
-        <v>XigN</v>
+        <v>Biuckmt</v>
       </c>
       <c r="D24" t="str">
-        <v>Avangar</v>
+        <v>Shika</v>
       </c>
       <c r="E24" t="str">
         <v>EVENT</v>
@@ -3081,16 +3081,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>1790465205562-BnTeT</v>
+        <v>1790465209723-ImpressioN</v>
       </c>
       <c r="B25">
-        <v>1790465205562</v>
+        <v>1790465209723</v>
       </c>
       <c r="C25" t="str">
-        <v>BnTeT</v>
+        <v>ImpressioN</v>
       </c>
       <c r="D25" t="str">
-        <v>Avangar</v>
+        <v>Shika</v>
       </c>
       <c r="E25" t="str">
         <v>EVENT</v>
@@ -3122,16 +3122,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>1790465205562-ArtFr0st</v>
+        <v>1790465209723-splashske</v>
       </c>
       <c r="B26">
-        <v>1790465205562</v>
+        <v>1790465209723</v>
       </c>
       <c r="C26" t="str">
-        <v>ArtFr0st</v>
+        <v>splashske</v>
       </c>
       <c r="D26" t="str">
-        <v>Avangar</v>
+        <v>Shika</v>
       </c>
       <c r="E26" t="str">
         <v>EVENT</v>
@@ -3163,16 +3163,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>1790465142470-Triton</v>
+        <v>1790465205562-Annihilation</v>
       </c>
       <c r="B27">
-        <v>1790465142470</v>
+        <v>1790465205562</v>
       </c>
       <c r="C27" t="str">
-        <v>Triton</v>
+        <v>Annihilation</v>
       </c>
       <c r="D27" t="str">
-        <v>Bravado</v>
+        <v>Avangar</v>
       </c>
       <c r="E27" t="str">
         <v>EVENT</v>
@@ -3190,7 +3190,7 @@
         <v>Asia</v>
       </c>
       <c r="J27" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -3204,16 +3204,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>1790465142470-FROZ3N</v>
+        <v>1790465205562-fejtZ</v>
       </c>
       <c r="B28">
-        <v>1790465142470</v>
+        <v>1790465205562</v>
       </c>
       <c r="C28" t="str">
-        <v>FROZ3N</v>
+        <v>fejtZ</v>
       </c>
       <c r="D28" t="str">
-        <v>Bravado</v>
+        <v>Avangar</v>
       </c>
       <c r="E28" t="str">
         <v>EVENT</v>
@@ -3231,7 +3231,7 @@
         <v>Asia</v>
       </c>
       <c r="J28" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -3245,16 +3245,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>1790465142470-Doru</v>
+        <v>1790465205562-XigN</v>
       </c>
       <c r="B29">
-        <v>1790465142470</v>
+        <v>1790465205562</v>
       </c>
       <c r="C29" t="str">
-        <v>Doru</v>
+        <v>XigN</v>
       </c>
       <c r="D29" t="str">
-        <v>Bravado</v>
+        <v>Avangar</v>
       </c>
       <c r="E29" t="str">
         <v>EVENT</v>
@@ -3272,7 +3272,7 @@
         <v>Asia</v>
       </c>
       <c r="J29" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -3286,16 +3286,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1790465142470-wilj</v>
+        <v>1790465205562-BnTeT</v>
       </c>
       <c r="B30">
-        <v>1790465142470</v>
+        <v>1790465205562</v>
       </c>
       <c r="C30" t="str">
-        <v>wilj</v>
+        <v>BnTeT</v>
       </c>
       <c r="D30" t="str">
-        <v>Bravado</v>
+        <v>Avangar</v>
       </c>
       <c r="E30" t="str">
         <v>EVENT</v>
@@ -3313,7 +3313,7 @@
         <v>Asia</v>
       </c>
       <c r="J30" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -3327,16 +3327,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>1790465142470-march</v>
+        <v>1790465205562-ArtFr0st</v>
       </c>
       <c r="B31">
-        <v>1790465142470</v>
+        <v>1790465205562</v>
       </c>
       <c r="C31" t="str">
-        <v>march</v>
+        <v>ArtFr0st</v>
       </c>
       <c r="D31" t="str">
-        <v>Bravado</v>
+        <v>Avangar</v>
       </c>
       <c r="E31" t="str">
         <v>EVENT</v>
@@ -3354,7 +3354,7 @@
         <v>Asia</v>
       </c>
       <c r="J31" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -3368,16 +3368,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>1790465130116-Terryyy</v>
+        <v>1790465142470-Triton</v>
       </c>
       <c r="B32">
-        <v>1790465130116</v>
+        <v>1790465142470</v>
       </c>
       <c r="C32" t="str">
-        <v>Terryyy</v>
+        <v>Triton</v>
       </c>
       <c r="D32" t="str">
-        <v>kONO</v>
+        <v>Bravado</v>
       </c>
       <c r="E32" t="str">
         <v>EVENT</v>
@@ -3395,7 +3395,7 @@
         <v>Asia</v>
       </c>
       <c r="J32" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -3409,16 +3409,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>1790465130116-Dawy</v>
+        <v>1790465142470-FROZ3N</v>
       </c>
       <c r="B33">
-        <v>1790465130116</v>
+        <v>1790465142470</v>
       </c>
       <c r="C33" t="str">
-        <v>Dawy</v>
+        <v>FROZ3N</v>
       </c>
       <c r="D33" t="str">
-        <v>kONO</v>
+        <v>Bravado</v>
       </c>
       <c r="E33" t="str">
         <v>EVENT</v>
@@ -3436,7 +3436,7 @@
         <v>Asia</v>
       </c>
       <c r="J33" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -3450,16 +3450,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>1790465130116-NIGHT666LADE</v>
+        <v>1790465142470-Doru</v>
       </c>
       <c r="B34">
-        <v>1790465130116</v>
+        <v>1790465142470</v>
       </c>
       <c r="C34" t="str">
-        <v>NIGHT666LADE</v>
+        <v>Doru</v>
       </c>
       <c r="D34" t="str">
-        <v>kONO</v>
+        <v>Bravado</v>
       </c>
       <c r="E34" t="str">
         <v>EVENT</v>
@@ -3477,7 +3477,7 @@
         <v>Asia</v>
       </c>
       <c r="J34" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -3491,16 +3491,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>1790465130116-somebody</v>
+        <v>1790465142470-wilj</v>
       </c>
       <c r="B35">
-        <v>1790465130116</v>
+        <v>1790465142470</v>
       </c>
       <c r="C35" t="str">
-        <v>somebody</v>
+        <v>wilj</v>
       </c>
       <c r="D35" t="str">
-        <v>kONO</v>
+        <v>Bravado</v>
       </c>
       <c r="E35" t="str">
         <v>EVENT</v>
@@ -3518,7 +3518,7 @@
         <v>Asia</v>
       </c>
       <c r="J35" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -3532,16 +3532,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>1790465130116-0z</v>
+        <v>1790465142470-march</v>
       </c>
       <c r="B36">
-        <v>1790465130116</v>
+        <v>1790465142470</v>
       </c>
       <c r="C36" t="str">
-        <v>0z</v>
+        <v>march</v>
       </c>
       <c r="D36" t="str">
-        <v>kONO</v>
+        <v>Bravado</v>
       </c>
       <c r="E36" t="str">
         <v>EVENT</v>
@@ -3559,7 +3559,7 @@
         <v>Asia</v>
       </c>
       <c r="J36" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -3573,16 +3573,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>1790465037611-0SAMAS</v>
+        <v>1790465130116-Terryyy</v>
       </c>
       <c r="B37">
-        <v>1790465037611</v>
+        <v>1790465130116</v>
       </c>
       <c r="C37" t="str">
-        <v>0SAMAS</v>
+        <v>Terryyy</v>
       </c>
       <c r="D37" t="str">
-        <v>LGB</v>
+        <v>kONO</v>
       </c>
       <c r="E37" t="str">
         <v>EVENT</v>
@@ -3600,7 +3600,7 @@
         <v>Asia</v>
       </c>
       <c r="J37" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>1790465037611-BOROS</v>
+        <v>1790465130116-Dawy</v>
       </c>
       <c r="B38">
-        <v>1790465037611</v>
+        <v>1790465130116</v>
       </c>
       <c r="C38" t="str">
-        <v>BOROS</v>
+        <v>Dawy</v>
       </c>
       <c r="D38" t="str">
-        <v>LGB</v>
+        <v>kONO</v>
       </c>
       <c r="E38" t="str">
         <v>EVENT</v>
@@ -3641,7 +3641,7 @@
         <v>Asia</v>
       </c>
       <c r="J38" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -3655,16 +3655,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>1790465037611-Bibu</v>
+        <v>1790465130116-NIGHT666LADE</v>
       </c>
       <c r="B39">
-        <v>1790465037611</v>
+        <v>1790465130116</v>
       </c>
       <c r="C39" t="str">
-        <v>Bibu</v>
+        <v>NIGHT666LADE</v>
       </c>
       <c r="D39" t="str">
-        <v>LGB</v>
+        <v>kONO</v>
       </c>
       <c r="E39" t="str">
         <v>EVENT</v>
@@ -3682,7 +3682,7 @@
         <v>Asia</v>
       </c>
       <c r="J39" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -3696,16 +3696,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1790465037611-m1N1</v>
+        <v>1790465130116-somebody</v>
       </c>
       <c r="B40">
-        <v>1790465037611</v>
+        <v>1790465130116</v>
       </c>
       <c r="C40" t="str">
-        <v>m1N1</v>
+        <v>somebody</v>
       </c>
       <c r="D40" t="str">
-        <v>LGB</v>
+        <v>kONO</v>
       </c>
       <c r="E40" t="str">
         <v>EVENT</v>
@@ -3723,7 +3723,7 @@
         <v>Asia</v>
       </c>
       <c r="J40" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K40">
         <v>1</v>
@@ -3737,16 +3737,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>1790465037611-ISSAA</v>
+        <v>1790465130116-0z</v>
       </c>
       <c r="B41">
-        <v>1790465037611</v>
+        <v>1790465130116</v>
       </c>
       <c r="C41" t="str">
-        <v>ISSAA</v>
+        <v>0z</v>
       </c>
       <c r="D41" t="str">
-        <v>LGB</v>
+        <v>kONO</v>
       </c>
       <c r="E41" t="str">
         <v>EVENT</v>
@@ -3764,7 +3764,7 @@
         <v>Asia</v>
       </c>
       <c r="J41" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -3777,23 +3777,23 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>1789701851248</v>
-      </c>
-      <c r="B42" t="str">
-        <v/>
+      <c r="A42" t="str">
+        <v>1790465037611-0SAMAS</v>
+      </c>
+      <c r="B42">
+        <v>1790465037611</v>
       </c>
       <c r="C42" t="str">
-        <v>s1mple</v>
+        <v>0SAMAS</v>
       </c>
       <c r="D42" t="str">
-        <v>BC.Game</v>
+        <v>LGB</v>
       </c>
       <c r="E42" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F42" t="str">
-        <v>BLAST Premier 2026 Seoul</v>
+        <v>Fragadelphia 2026</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -3802,7 +3802,7 @@
         <v>Regional</v>
       </c>
       <c r="I42" t="str">
-        <v>Europe</v>
+        <v>Asia</v>
       </c>
       <c r="J42" t="str">
         <v>Winner</v>
@@ -3818,23 +3818,23 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>1789701846578</v>
-      </c>
-      <c r="B43" t="str">
-        <v/>
+      <c r="A43" t="str">
+        <v>1790465037611-BOROS</v>
+      </c>
+      <c r="B43">
+        <v>1790465037611</v>
       </c>
       <c r="C43" t="str">
-        <v>taco</v>
+        <v>BOROS</v>
       </c>
       <c r="D43" t="str">
-        <v>Lux Tenebris</v>
+        <v>LGB</v>
       </c>
       <c r="E43" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F43" t="str">
-        <v>BLAST Premier 2026 Seoul</v>
+        <v>Fragadelphia 2026</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -3843,7 +3843,7 @@
         <v>Regional</v>
       </c>
       <c r="I43" t="str">
-        <v>Europe</v>
+        <v>Asia</v>
       </c>
       <c r="J43" t="str">
         <v>Winner</v>
@@ -3859,23 +3859,23 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>1789701842702</v>
-      </c>
-      <c r="B44" t="str">
-        <v/>
+      <c r="A44" t="str">
+        <v>1790465037611-Bibu</v>
+      </c>
+      <c r="B44">
+        <v>1790465037611</v>
       </c>
       <c r="C44" t="str">
-        <v>kyourezz</v>
+        <v>Bibu</v>
       </c>
       <c r="D44" t="str">
-        <v>Lux Tenebris</v>
+        <v>LGB</v>
       </c>
       <c r="E44" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F44" t="str">
-        <v>BLAST Premier 2026 Seoul</v>
+        <v>Fragadelphia 2026</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -3884,7 +3884,7 @@
         <v>Regional</v>
       </c>
       <c r="I44" t="str">
-        <v>Europe</v>
+        <v>Asia</v>
       </c>
       <c r="J44" t="str">
         <v>Winner</v>
@@ -3900,23 +3900,23 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>1789701830776</v>
-      </c>
-      <c r="B45" t="str">
-        <v/>
+      <c r="A45" t="str">
+        <v>1790465037611-m1N1</v>
+      </c>
+      <c r="B45">
+        <v>1790465037611</v>
       </c>
       <c r="C45" t="str">
-        <v>heroghoxxt</v>
+        <v>m1N1</v>
       </c>
       <c r="D45" t="str">
-        <v>Lux Tenebris</v>
+        <v>LGB</v>
       </c>
       <c r="E45" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F45" t="str">
-        <v>BLAST Premier 2026 Seoul</v>
+        <v>Fragadelphia 2026</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -3925,7 +3925,7 @@
         <v>Regional</v>
       </c>
       <c r="I45" t="str">
-        <v>Europe</v>
+        <v>Asia</v>
       </c>
       <c r="J45" t="str">
         <v>Winner</v>
@@ -3941,23 +3941,23 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>1789701823336</v>
-      </c>
-      <c r="B46" t="str">
-        <v/>
+      <c r="A46" t="str">
+        <v>1790465037611-ISSAA</v>
+      </c>
+      <c r="B46">
+        <v>1790465037611</v>
       </c>
       <c r="C46" t="str">
-        <v>kilzys</v>
+        <v>ISSAA</v>
       </c>
       <c r="D46" t="str">
-        <v>Lux Tenebris</v>
+        <v>LGB</v>
       </c>
       <c r="E46" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F46" t="str">
-        <v>BLAST Premier 2026 Seoul</v>
+        <v>Fragadelphia 2026</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -3966,7 +3966,7 @@
         <v>Regional</v>
       </c>
       <c r="I46" t="str">
-        <v>Europe</v>
+        <v>Asia</v>
       </c>
       <c r="J46" t="str">
         <v>Winner</v>
@@ -3982,20 +3982,20 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>1789701749272-xertioN</v>
-      </c>
-      <c r="B47">
-        <v>1789701749272</v>
+      <c r="A47">
+        <v>1789701851248</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
       </c>
       <c r="C47" t="str">
-        <v>xertioN</v>
+        <v>s1mple</v>
       </c>
       <c r="D47" t="str">
-        <v>MOUZ</v>
+        <v>BC.Game</v>
       </c>
       <c r="E47" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F47" t="str">
         <v>BLAST Premier 2026 Seoul</v>
@@ -4004,13 +4004,13 @@
         <v>1</v>
       </c>
       <c r="H47" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J47" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K47">
         <v>1</v>
@@ -4023,20 +4023,20 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
-        <v>1789701749272-Jimpphat</v>
-      </c>
-      <c r="B48">
-        <v>1789701749272</v>
+      <c r="A48">
+        <v>1789701846578</v>
+      </c>
+      <c r="B48" t="str">
+        <v/>
       </c>
       <c r="C48" t="str">
-        <v>Jimpphat</v>
+        <v>taco</v>
       </c>
       <c r="D48" t="str">
-        <v>MOUZ</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E48" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F48" t="str">
         <v>BLAST Premier 2026 Seoul</v>
@@ -4045,13 +4045,13 @@
         <v>1</v>
       </c>
       <c r="H48" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J48" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -4064,20 +4064,20 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v>1789701749272-Spinx</v>
-      </c>
-      <c r="B49">
-        <v>1789701749272</v>
+      <c r="A49">
+        <v>1789701842702</v>
+      </c>
+      <c r="B49" t="str">
+        <v/>
       </c>
       <c r="C49" t="str">
-        <v>Spinx</v>
+        <v>kyourezz</v>
       </c>
       <c r="D49" t="str">
-        <v>MOUZ</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E49" t="str">
-        <v>EVENT</v>
+        <v>VP</v>
       </c>
       <c r="F49" t="str">
         <v>BLAST Premier 2026 Seoul</v>
@@ -4086,13 +4086,13 @@
         <v>1</v>
       </c>
       <c r="H49" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J49" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K49">
         <v>1</v>
@@ -4105,20 +4105,20 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>1789701749272-torzsi</v>
-      </c>
-      <c r="B50">
-        <v>1789701749272</v>
+      <c r="A50">
+        <v>1789701830776</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
       </c>
       <c r="C50" t="str">
-        <v>torzsi</v>
+        <v>heroghoxxt</v>
       </c>
       <c r="D50" t="str">
-        <v>MOUZ</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E50" t="str">
-        <v>EVENT</v>
+        <v>EVP</v>
       </c>
       <c r="F50" t="str">
         <v>BLAST Premier 2026 Seoul</v>
@@ -4127,13 +4127,13 @@
         <v>1</v>
       </c>
       <c r="H50" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J50" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -4146,20 +4146,20 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
-        <v>1789701749272-Brollan</v>
-      </c>
-      <c r="B51">
-        <v>1789701749272</v>
+      <c r="A51">
+        <v>1789701823336</v>
+      </c>
+      <c r="B51" t="str">
+        <v/>
       </c>
       <c r="C51" t="str">
-        <v>Brollan</v>
+        <v>kilzys</v>
       </c>
       <c r="D51" t="str">
-        <v>MOUZ</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E51" t="str">
-        <v>EVENT</v>
+        <v>MVP</v>
       </c>
       <c r="F51" t="str">
         <v>BLAST Premier 2026 Seoul</v>
@@ -4168,13 +4168,13 @@
         <v>1</v>
       </c>
       <c r="H51" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="J51" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K51">
         <v>1</v>
@@ -4188,16 +4188,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>1789701744555-C4LLM3SU3</v>
+        <v>1789701749272-xertioN</v>
       </c>
       <c r="B52">
-        <v>1789701744555</v>
+        <v>1789701749272</v>
       </c>
       <c r="C52" t="str">
-        <v>C4LLM3SU3</v>
+        <v>xertioN</v>
       </c>
       <c r="D52" t="str">
-        <v>Lynn Vision</v>
+        <v>MOUZ</v>
       </c>
       <c r="E52" t="str">
         <v>EVENT</v>
@@ -4229,16 +4229,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>1789701744555-EmiliaQAQ</v>
+        <v>1789701749272-Jimpphat</v>
       </c>
       <c r="B53">
-        <v>1789701744555</v>
+        <v>1789701749272</v>
       </c>
       <c r="C53" t="str">
-        <v>EmiliaQAQ</v>
+        <v>Jimpphat</v>
       </c>
       <c r="D53" t="str">
-        <v>Lynn Vision</v>
+        <v>MOUZ</v>
       </c>
       <c r="E53" t="str">
         <v>EVENT</v>
@@ -4270,16 +4270,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>1789701744555-Starry</v>
+        <v>1789701749272-Spinx</v>
       </c>
       <c r="B54">
-        <v>1789701744555</v>
+        <v>1789701749272</v>
       </c>
       <c r="C54" t="str">
-        <v>Starry</v>
+        <v>Spinx</v>
       </c>
       <c r="D54" t="str">
-        <v>Lynn Vision</v>
+        <v>MOUZ</v>
       </c>
       <c r="E54" t="str">
         <v>EVENT</v>
@@ -4311,16 +4311,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>1789701744555-z4kr</v>
+        <v>1789701749272-torzsi</v>
       </c>
       <c r="B55">
-        <v>1789701744555</v>
+        <v>1789701749272</v>
       </c>
       <c r="C55" t="str">
-        <v>z4kr</v>
+        <v>torzsi</v>
       </c>
       <c r="D55" t="str">
-        <v>Lynn Vision</v>
+        <v>MOUZ</v>
       </c>
       <c r="E55" t="str">
         <v>EVENT</v>
@@ -4352,16 +4352,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>1789701744555-Westmelon</v>
+        <v>1789701749272-Brollan</v>
       </c>
       <c r="B56">
-        <v>1789701744555</v>
+        <v>1789701749272</v>
       </c>
       <c r="C56" t="str">
-        <v>Westmelon</v>
+        <v>Brollan</v>
       </c>
       <c r="D56" t="str">
-        <v>Lynn Vision</v>
+        <v>MOUZ</v>
       </c>
       <c r="E56" t="str">
         <v>EVENT</v>
@@ -4393,16 +4393,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>1789701734985-Snax</v>
+        <v>1789701744555-C4LLM3SU3</v>
       </c>
       <c r="B57">
-        <v>1789701734985</v>
+        <v>1789701744555</v>
       </c>
       <c r="C57" t="str">
-        <v>Snax</v>
+        <v>C4LLM3SU3</v>
       </c>
       <c r="D57" t="str">
-        <v>Envy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E57" t="str">
         <v>EVENT</v>
@@ -4434,16 +4434,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>1789701734985-PTC</v>
+        <v>1789701744555-EmiliaQAQ</v>
       </c>
       <c r="B58">
-        <v>1789701734985</v>
+        <v>1789701744555</v>
       </c>
       <c r="C58" t="str">
-        <v>PTC</v>
+        <v>EmiliaQAQ</v>
       </c>
       <c r="D58" t="str">
-        <v>Envy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E58" t="str">
         <v>EVENT</v>
@@ -4475,16 +4475,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>1789701734985-h4rn</v>
+        <v>1789701744555-Starry</v>
       </c>
       <c r="B59">
-        <v>1789701734985</v>
+        <v>1789701744555</v>
       </c>
       <c r="C59" t="str">
-        <v>h4rn</v>
+        <v>Starry</v>
       </c>
       <c r="D59" t="str">
-        <v>Envy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E59" t="str">
         <v>EVENT</v>
@@ -4516,16 +4516,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>1789701734985-liTTle</v>
+        <v>1789701744555-z4kr</v>
       </c>
       <c r="B60">
-        <v>1789701734985</v>
+        <v>1789701744555</v>
       </c>
       <c r="C60" t="str">
-        <v>liTTle</v>
+        <v>z4kr</v>
       </c>
       <c r="D60" t="str">
-        <v>Envy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E60" t="str">
         <v>EVENT</v>
@@ -4557,16 +4557,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>1789701734985-cosmeeeN</v>
+        <v>1789701744555-Westmelon</v>
       </c>
       <c r="B61">
-        <v>1789701734985</v>
+        <v>1789701744555</v>
       </c>
       <c r="C61" t="str">
-        <v>cosmeeeN</v>
+        <v>Westmelon</v>
       </c>
       <c r="D61" t="str">
-        <v>Envy</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="E61" t="str">
         <v>EVENT</v>
@@ -4598,16 +4598,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>1789701723266-leakz</v>
+        <v>1789701734985-Snax</v>
       </c>
       <c r="B62">
-        <v>1789701723266</v>
+        <v>1789701734985</v>
       </c>
       <c r="C62" t="str">
-        <v>leakz</v>
+        <v>Snax</v>
       </c>
       <c r="D62" t="str">
-        <v>Enemy</v>
+        <v>Envy</v>
       </c>
       <c r="E62" t="str">
         <v>EVENT</v>
@@ -4639,16 +4639,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>1789701723266-salaza</v>
+        <v>1789701734985-PTC</v>
       </c>
       <c r="B63">
-        <v>1789701723266</v>
+        <v>1789701734985</v>
       </c>
       <c r="C63" t="str">
-        <v>salaza</v>
+        <v>PTC</v>
       </c>
       <c r="D63" t="str">
-        <v>Enemy</v>
+        <v>Envy</v>
       </c>
       <c r="E63" t="str">
         <v>EVENT</v>
@@ -4680,16 +4680,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>1789701723266-kroK</v>
+        <v>1789701734985-h4rn</v>
       </c>
       <c r="B64">
-        <v>1789701723266</v>
+        <v>1789701734985</v>
       </c>
       <c r="C64" t="str">
-        <v>kroK</v>
+        <v>h4rn</v>
       </c>
       <c r="D64" t="str">
-        <v>Enemy</v>
+        <v>Envy</v>
       </c>
       <c r="E64" t="str">
         <v>EVENT</v>
@@ -4721,16 +4721,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>1789701723266-valde</v>
+        <v>1789701734985-liTTle</v>
       </c>
       <c r="B65">
-        <v>1789701723266</v>
+        <v>1789701734985</v>
       </c>
       <c r="C65" t="str">
-        <v>valde</v>
+        <v>liTTle</v>
       </c>
       <c r="D65" t="str">
-        <v>Enemy</v>
+        <v>Envy</v>
       </c>
       <c r="E65" t="str">
         <v>EVENT</v>
@@ -4762,16 +4762,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>1789701723266-Nodios</v>
+        <v>1789701734985-cosmeeeN</v>
       </c>
       <c r="B66">
-        <v>1789701723266</v>
+        <v>1789701734985</v>
       </c>
       <c r="C66" t="str">
-        <v>Nodios</v>
+        <v>cosmeeeN</v>
       </c>
       <c r="D66" t="str">
-        <v>Enemy</v>
+        <v>Envy</v>
       </c>
       <c r="E66" t="str">
         <v>EVENT</v>
@@ -4803,16 +4803,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>1789701676668-Staehr</v>
+        <v>1789701723266-leakz</v>
       </c>
       <c r="B67">
-        <v>1789701676668</v>
+        <v>1789701723266</v>
       </c>
       <c r="C67" t="str">
-        <v>Staehr</v>
+        <v>leakz</v>
       </c>
       <c r="D67" t="str">
-        <v>Astralis</v>
+        <v>Enemy</v>
       </c>
       <c r="E67" t="str">
         <v>EVENT</v>
@@ -4844,16 +4844,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>1789701676668-jabbi</v>
+        <v>1789701723266-salaza</v>
       </c>
       <c r="B68">
-        <v>1789701676668</v>
+        <v>1789701723266</v>
       </c>
       <c r="C68" t="str">
-        <v>jabbi</v>
+        <v>salaza</v>
       </c>
       <c r="D68" t="str">
-        <v>Astralis</v>
+        <v>Enemy</v>
       </c>
       <c r="E68" t="str">
         <v>EVENT</v>
@@ -4885,16 +4885,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>1789701676668-stavn</v>
+        <v>1789701723266-kroK</v>
       </c>
       <c r="B69">
-        <v>1789701676668</v>
+        <v>1789701723266</v>
       </c>
       <c r="C69" t="str">
-        <v>stavn</v>
+        <v>kroK</v>
       </c>
       <c r="D69" t="str">
-        <v>Astralis</v>
+        <v>Enemy</v>
       </c>
       <c r="E69" t="str">
         <v>EVENT</v>
@@ -4926,16 +4926,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>1789701676668-HooXi</v>
+        <v>1789701723266-valde</v>
       </c>
       <c r="B70">
-        <v>1789701676668</v>
+        <v>1789701723266</v>
       </c>
       <c r="C70" t="str">
-        <v>HooXi</v>
+        <v>valde</v>
       </c>
       <c r="D70" t="str">
-        <v>Astralis</v>
+        <v>Enemy</v>
       </c>
       <c r="E70" t="str">
         <v>EVENT</v>
@@ -4967,16 +4967,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>1789701676668-device</v>
+        <v>1789701723266-Nodios</v>
       </c>
       <c r="B71">
-        <v>1789701676668</v>
+        <v>1789701723266</v>
       </c>
       <c r="C71" t="str">
-        <v>device</v>
+        <v>Nodios</v>
       </c>
       <c r="D71" t="str">
-        <v>Astralis</v>
+        <v>Enemy</v>
       </c>
       <c r="E71" t="str">
         <v>EVENT</v>
@@ -5008,16 +5008,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>1789701668422-SaVage</v>
+        <v>1789701676668-Staehr</v>
       </c>
       <c r="B72">
-        <v>1789701668422</v>
+        <v>1789701676668</v>
       </c>
       <c r="C72" t="str">
-        <v>SaVage</v>
+        <v>Staehr</v>
       </c>
       <c r="D72" t="str">
-        <v>BC.Game</v>
+        <v>Astralis</v>
       </c>
       <c r="E72" t="str">
         <v>EVENT</v>
@@ -5035,7 +5035,7 @@
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K72">
         <v>1</v>
@@ -5049,16 +5049,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>1789701668422-shadiy</v>
+        <v>1789701676668-jabbi</v>
       </c>
       <c r="B73">
-        <v>1789701668422</v>
+        <v>1789701676668</v>
       </c>
       <c r="C73" t="str">
-        <v>shadiy</v>
+        <v>jabbi</v>
       </c>
       <c r="D73" t="str">
-        <v>BC.Game</v>
+        <v>Astralis</v>
       </c>
       <c r="E73" t="str">
         <v>EVENT</v>
@@ -5076,7 +5076,7 @@
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K73">
         <v>1</v>
@@ -5090,16 +5090,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>1789701668422-Valiance</v>
+        <v>1789701676668-stavn</v>
       </c>
       <c r="B74">
-        <v>1789701668422</v>
+        <v>1789701676668</v>
       </c>
       <c r="C74" t="str">
-        <v>Valiance</v>
+        <v>stavn</v>
       </c>
       <c r="D74" t="str">
-        <v>BC.Game</v>
+        <v>Astralis</v>
       </c>
       <c r="E74" t="str">
         <v>EVENT</v>
@@ -5117,7 +5117,7 @@
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K74">
         <v>1</v>
@@ -5131,16 +5131,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>1789701668422-electroNic</v>
+        <v>1789701676668-HooXi</v>
       </c>
       <c r="B75">
-        <v>1789701668422</v>
+        <v>1789701676668</v>
       </c>
       <c r="C75" t="str">
-        <v>electroNic</v>
+        <v>HooXi</v>
       </c>
       <c r="D75" t="str">
-        <v>BC.Game</v>
+        <v>Astralis</v>
       </c>
       <c r="E75" t="str">
         <v>EVENT</v>
@@ -5158,7 +5158,7 @@
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K75">
         <v>1</v>
@@ -5172,16 +5172,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>1789701668422-s1mple</v>
+        <v>1789701676668-device</v>
       </c>
       <c r="B76">
-        <v>1789701668422</v>
+        <v>1789701676668</v>
       </c>
       <c r="C76" t="str">
-        <v>s1mple</v>
+        <v>device</v>
       </c>
       <c r="D76" t="str">
-        <v>BC.Game</v>
+        <v>Astralis</v>
       </c>
       <c r="E76" t="str">
         <v>EVENT</v>
@@ -5199,7 +5199,7 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K76">
         <v>1</v>
@@ -5213,16 +5213,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>1789701649080-chelo</v>
+        <v>1789701668422-SaVage</v>
       </c>
       <c r="B77">
-        <v>1789701649080</v>
+        <v>1789701668422</v>
       </c>
       <c r="C77" t="str">
-        <v>chelo</v>
+        <v>SaVage</v>
       </c>
       <c r="D77" t="str">
-        <v>Imperial</v>
+        <v>BC.Game</v>
       </c>
       <c r="E77" t="str">
         <v>EVENT</v>
@@ -5240,7 +5240,7 @@
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K77">
         <v>1</v>
@@ -5254,16 +5254,16 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>1789701649080-noway</v>
+        <v>1789701668422-shadiy</v>
       </c>
       <c r="B78">
-        <v>1789701649080</v>
+        <v>1789701668422</v>
       </c>
       <c r="C78" t="str">
-        <v>noway</v>
+        <v>shadiy</v>
       </c>
       <c r="D78" t="str">
-        <v>Imperial</v>
+        <v>BC.Game</v>
       </c>
       <c r="E78" t="str">
         <v>EVENT</v>
@@ -5281,7 +5281,7 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K78">
         <v>1</v>
@@ -5295,16 +5295,16 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>1789701649080-Shr</v>
+        <v>1789701668422-Valiance</v>
       </c>
       <c r="B79">
-        <v>1789701649080</v>
+        <v>1789701668422</v>
       </c>
       <c r="C79" t="str">
-        <v>Shr</v>
+        <v>Valiance</v>
       </c>
       <c r="D79" t="str">
-        <v>Imperial</v>
+        <v>BC.Game</v>
       </c>
       <c r="E79" t="str">
         <v>EVENT</v>
@@ -5322,7 +5322,7 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K79">
         <v>1</v>
@@ -5336,16 +5336,16 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>1789701649080-try</v>
+        <v>1789701668422-electroNic</v>
       </c>
       <c r="B80">
-        <v>1789701649080</v>
+        <v>1789701668422</v>
       </c>
       <c r="C80" t="str">
-        <v>try</v>
+        <v>electroNic</v>
       </c>
       <c r="D80" t="str">
-        <v>Imperial</v>
+        <v>BC.Game</v>
       </c>
       <c r="E80" t="str">
         <v>EVENT</v>
@@ -5363,7 +5363,7 @@
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K80">
         <v>1</v>
@@ -5377,16 +5377,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>1789701649080-VINI</v>
+        <v>1789701668422-s1mple</v>
       </c>
       <c r="B81">
-        <v>1789701649080</v>
+        <v>1789701668422</v>
       </c>
       <c r="C81" t="str">
-        <v>VINI</v>
+        <v>s1mple</v>
       </c>
       <c r="D81" t="str">
-        <v>Imperial</v>
+        <v>BC.Game</v>
       </c>
       <c r="E81" t="str">
         <v>EVENT</v>
@@ -5404,7 +5404,7 @@
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K81">
         <v>1</v>
@@ -5418,16 +5418,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>1789701627337-boltz</v>
+        <v>1789701649080-chelo</v>
       </c>
       <c r="B82">
-        <v>1789701627337</v>
+        <v>1789701649080</v>
       </c>
       <c r="C82" t="str">
-        <v>boltz</v>
+        <v>chelo</v>
       </c>
       <c r="D82" t="str">
-        <v>Lux Tenebris</v>
+        <v>Imperial</v>
       </c>
       <c r="E82" t="str">
         <v>EVENT</v>
@@ -5445,7 +5445,7 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K82">
         <v>1</v>
@@ -5459,16 +5459,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>1789701627337-taco</v>
+        <v>1789701649080-noway</v>
       </c>
       <c r="B83">
-        <v>1789701627337</v>
+        <v>1789701649080</v>
       </c>
       <c r="C83" t="str">
-        <v>taco</v>
+        <v>noway</v>
       </c>
       <c r="D83" t="str">
-        <v>Lux Tenebris</v>
+        <v>Imperial</v>
       </c>
       <c r="E83" t="str">
         <v>EVENT</v>
@@ -5486,7 +5486,7 @@
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K83">
         <v>1</v>
@@ -5500,16 +5500,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>1789701627337-kyourezz</v>
+        <v>1789701649080-Shr</v>
       </c>
       <c r="B84">
-        <v>1789701627337</v>
+        <v>1789701649080</v>
       </c>
       <c r="C84" t="str">
-        <v>kyourezz</v>
+        <v>Shr</v>
       </c>
       <c r="D84" t="str">
-        <v>Lux Tenebris</v>
+        <v>Imperial</v>
       </c>
       <c r="E84" t="str">
         <v>EVENT</v>
@@ -5527,7 +5527,7 @@
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K84">
         <v>1</v>
@@ -5541,16 +5541,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>1789701627337-heroghoxxt</v>
+        <v>1789701649080-try</v>
       </c>
       <c r="B85">
-        <v>1789701627337</v>
+        <v>1789701649080</v>
       </c>
       <c r="C85" t="str">
-        <v>heroghoxxt</v>
+        <v>try</v>
       </c>
       <c r="D85" t="str">
-        <v>Lux Tenebris</v>
+        <v>Imperial</v>
       </c>
       <c r="E85" t="str">
         <v>EVENT</v>
@@ -5568,7 +5568,7 @@
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K85">
         <v>1</v>
@@ -5582,16 +5582,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>1789701627337-kilzys</v>
+        <v>1789701649080-VINI</v>
       </c>
       <c r="B86">
-        <v>1789701627337</v>
+        <v>1789701649080</v>
       </c>
       <c r="C86" t="str">
-        <v>kilzys</v>
+        <v>VINI</v>
       </c>
       <c r="D86" t="str">
-        <v>Lux Tenebris</v>
+        <v>Imperial</v>
       </c>
       <c r="E86" t="str">
         <v>EVENT</v>
@@ -5609,7 +5609,7 @@
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K86">
         <v>1</v>
@@ -5623,34 +5623,34 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>1789045649533-ykis</v>
+        <v>1789701627337-boltz</v>
       </c>
       <c r="B87">
-        <v>1789045649533</v>
+        <v>1789701627337</v>
       </c>
       <c r="C87" t="str">
-        <v>ykis</v>
+        <v>boltz</v>
       </c>
       <c r="D87" t="str">
-        <v>ENCE Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E87" t="str">
         <v>EVENT</v>
       </c>
       <c r="F87" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G87">
         <v>1</v>
       </c>
       <c r="H87" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I87" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J87" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K87">
         <v>1</v>
@@ -5664,34 +5664,34 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>1789045649533-japE</v>
+        <v>1789701627337-taco</v>
       </c>
       <c r="B88">
-        <v>1789045649533</v>
+        <v>1789701627337</v>
       </c>
       <c r="C88" t="str">
-        <v>japE</v>
+        <v>taco</v>
       </c>
       <c r="D88" t="str">
-        <v>ENCE Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E88" t="str">
         <v>EVENT</v>
       </c>
       <c r="F88" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
       <c r="H88" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I88" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J88" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K88">
         <v>1</v>
@@ -5705,34 +5705,34 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>1789045649533-Welho</v>
+        <v>1789701627337-kyourezz</v>
       </c>
       <c r="B89">
-        <v>1789045649533</v>
+        <v>1789701627337</v>
       </c>
       <c r="C89" t="str">
-        <v>Welho</v>
+        <v>kyourezz</v>
       </c>
       <c r="D89" t="str">
-        <v>ENCE Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E89" t="str">
         <v>EVENT</v>
       </c>
       <c r="F89" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I89" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J89" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K89">
         <v>1</v>
@@ -5746,34 +5746,34 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>1789045649533-oopee</v>
+        <v>1789701627337-heroghoxxt</v>
       </c>
       <c r="B90">
-        <v>1789045649533</v>
+        <v>1789701627337</v>
       </c>
       <c r="C90" t="str">
-        <v>oopee</v>
+        <v>heroghoxxt</v>
       </c>
       <c r="D90" t="str">
-        <v>ENCE Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E90" t="str">
         <v>EVENT</v>
       </c>
       <c r="F90" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G90">
         <v>1</v>
       </c>
       <c r="H90" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I90" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J90" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K90">
         <v>1</v>
@@ -5787,34 +5787,34 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>1789045649533-arvid</v>
+        <v>1789701627337-kilzys</v>
       </c>
       <c r="B91">
-        <v>1789045649533</v>
+        <v>1789701627337</v>
       </c>
       <c r="C91" t="str">
-        <v>arvid</v>
+        <v>kilzys</v>
       </c>
       <c r="D91" t="str">
-        <v>ENCE Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="E91" t="str">
         <v>EVENT</v>
       </c>
       <c r="F91" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>BLAST Premier 2026 Seoul</v>
       </c>
       <c r="G91">
         <v>1</v>
       </c>
       <c r="H91" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I91" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J91" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K91">
         <v>1</v>
@@ -5828,16 +5828,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>1789045609684-2high</v>
+        <v>1789045649533-ykis</v>
       </c>
       <c r="B92">
-        <v>1789045609684</v>
+        <v>1789045649533</v>
       </c>
       <c r="C92" t="str">
-        <v>2high</v>
+        <v>ykis</v>
       </c>
       <c r="D92" t="str">
-        <v>SKYFURY</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E92" t="str">
         <v>EVENT</v>
@@ -5869,16 +5869,16 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>1789045609684-jL</v>
+        <v>1789045649533-japE</v>
       </c>
       <c r="B93">
-        <v>1789045609684</v>
+        <v>1789045649533</v>
       </c>
       <c r="C93" t="str">
-        <v>jL</v>
+        <v>japE</v>
       </c>
       <c r="D93" t="str">
-        <v>SKYFURY</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E93" t="str">
         <v>EVENT</v>
@@ -5910,16 +5910,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>1789045609684-aliStair</v>
+        <v>1789045649533-Welho</v>
       </c>
       <c r="B94">
-        <v>1789045609684</v>
+        <v>1789045649533</v>
       </c>
       <c r="C94" t="str">
-        <v>aliStair</v>
+        <v>Welho</v>
       </c>
       <c r="D94" t="str">
-        <v>SKYFURY</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E94" t="str">
         <v>EVENT</v>
@@ -5951,16 +5951,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>1789045609684-gla1ve</v>
+        <v>1789045649533-oopee</v>
       </c>
       <c r="B95">
-        <v>1789045609684</v>
+        <v>1789045649533</v>
       </c>
       <c r="C95" t="str">
-        <v>gla1ve</v>
+        <v>oopee</v>
       </c>
       <c r="D95" t="str">
-        <v>SKYFURY</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E95" t="str">
         <v>EVENT</v>
@@ -5992,16 +5992,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>1789045609684-discoStar</v>
+        <v>1789045649533-arvid</v>
       </c>
       <c r="B96">
-        <v>1789045609684</v>
+        <v>1789045649533</v>
       </c>
       <c r="C96" t="str">
-        <v>discoStar</v>
+        <v>arvid</v>
       </c>
       <c r="D96" t="str">
-        <v>SKYFURY</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="E96" t="str">
         <v>EVENT</v>
@@ -6033,16 +6033,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>1789045581410-forkyz</v>
+        <v>1789045609684-2high</v>
       </c>
       <c r="B97">
-        <v>1789045581410</v>
+        <v>1789045609684</v>
       </c>
       <c r="C97" t="str">
-        <v>forkyz</v>
+        <v>2high</v>
       </c>
       <c r="D97" t="str">
-        <v>BIG Academy</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E97" t="str">
         <v>EVENT</v>
@@ -6074,16 +6074,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>1789045581410-Pumpkin66</v>
+        <v>1789045609684-jL</v>
       </c>
       <c r="B98">
-        <v>1789045581410</v>
+        <v>1789045609684</v>
       </c>
       <c r="C98" t="str">
-        <v>Pumpkin66</v>
+        <v>jL</v>
       </c>
       <c r="D98" t="str">
-        <v>BIG Academy</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E98" t="str">
         <v>EVENT</v>
@@ -6115,16 +6115,16 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>1789045581410-def1zer</v>
+        <v>1789045609684-aliStair</v>
       </c>
       <c r="B99">
-        <v>1789045581410</v>
+        <v>1789045609684</v>
       </c>
       <c r="C99" t="str">
-        <v>def1zer</v>
+        <v>aliStair</v>
       </c>
       <c r="D99" t="str">
-        <v>BIG Academy</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E99" t="str">
         <v>EVENT</v>
@@ -6156,16 +6156,16 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>1789045581410-buster</v>
+        <v>1789045609684-gla1ve</v>
       </c>
       <c r="B100">
-        <v>1789045581410</v>
+        <v>1789045609684</v>
       </c>
       <c r="C100" t="str">
-        <v>buster</v>
+        <v>gla1ve</v>
       </c>
       <c r="D100" t="str">
-        <v>BIG Academy</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E100" t="str">
         <v>EVENT</v>
@@ -6197,16 +6197,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>1789045581410-neaLaN</v>
+        <v>1789045609684-discoStar</v>
       </c>
       <c r="B101">
-        <v>1789045581410</v>
+        <v>1789045609684</v>
       </c>
       <c r="C101" t="str">
-        <v>neaLaN</v>
+        <v>discoStar</v>
       </c>
       <c r="D101" t="str">
-        <v>BIG Academy</v>
+        <v>SKYFURY</v>
       </c>
       <c r="E101" t="str">
         <v>EVENT</v>
@@ -6238,16 +6238,16 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>1789045560109-cerber</v>
+        <v>1789045581410-forkyz</v>
       </c>
       <c r="B102">
-        <v>1789045560109</v>
+        <v>1789045581410</v>
       </c>
       <c r="C102" t="str">
-        <v>cerber</v>
+        <v>forkyz</v>
       </c>
       <c r="D102" t="str">
-        <v>Wildcard Academy</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E102" t="str">
         <v>EVENT</v>
@@ -6279,16 +6279,16 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>1789045560109-SinK</v>
+        <v>1789045581410-Pumpkin66</v>
       </c>
       <c r="B103">
-        <v>1789045560109</v>
+        <v>1789045581410</v>
       </c>
       <c r="C103" t="str">
-        <v>SinK</v>
+        <v>Pumpkin66</v>
       </c>
       <c r="D103" t="str">
-        <v>Wildcard Academy</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E103" t="str">
         <v>EVENT</v>
@@ -6320,16 +6320,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>1789045560109-qx</v>
+        <v>1789045581410-def1zer</v>
       </c>
       <c r="B104">
-        <v>1789045560109</v>
+        <v>1789045581410</v>
       </c>
       <c r="C104" t="str">
-        <v>qx</v>
+        <v>def1zer</v>
       </c>
       <c r="D104" t="str">
-        <v>Wildcard Academy</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E104" t="str">
         <v>EVENT</v>
@@ -6361,16 +6361,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>1789045560109-Griller</v>
+        <v>1789045581410-buster</v>
       </c>
       <c r="B105">
-        <v>1789045560109</v>
+        <v>1789045581410</v>
       </c>
       <c r="C105" t="str">
-        <v>Griller</v>
+        <v>buster</v>
       </c>
       <c r="D105" t="str">
-        <v>Wildcard Academy</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E105" t="str">
         <v>EVENT</v>
@@ -6402,16 +6402,16 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>1789045560109-AclioN</v>
+        <v>1789045581410-neaLaN</v>
       </c>
       <c r="B106">
-        <v>1789045560109</v>
+        <v>1789045581410</v>
       </c>
       <c r="C106" t="str">
-        <v>AclioN</v>
+        <v>neaLaN</v>
       </c>
       <c r="D106" t="str">
-        <v>Wildcard Academy</v>
+        <v>BIG Academy</v>
       </c>
       <c r="E106" t="str">
         <v>EVENT</v>
@@ -6443,16 +6443,16 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>1789045530768-Matheos</v>
+        <v>1789045560109-cerber</v>
       </c>
       <c r="B107">
-        <v>1789045530768</v>
+        <v>1789045560109</v>
       </c>
       <c r="C107" t="str">
-        <v>Matheos</v>
+        <v>cerber</v>
       </c>
       <c r="D107" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E107" t="str">
         <v>EVENT</v>
@@ -6484,16 +6484,16 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>1789045530768-Jorko</v>
+        <v>1789045560109-SinK</v>
       </c>
       <c r="B108">
-        <v>1789045530768</v>
+        <v>1789045560109</v>
       </c>
       <c r="C108" t="str">
-        <v>Jorko</v>
+        <v>SinK</v>
       </c>
       <c r="D108" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E108" t="str">
         <v>EVENT</v>
@@ -6525,16 +6525,16 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>1789045530768-Tapewaare</v>
+        <v>1789045560109-qx</v>
       </c>
       <c r="B109">
-        <v>1789045530768</v>
+        <v>1789045560109</v>
       </c>
       <c r="C109" t="str">
-        <v>Tapewaare</v>
+        <v>qx</v>
       </c>
       <c r="D109" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E109" t="str">
         <v>EVENT</v>
@@ -6566,16 +6566,16 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>1789045530768-b1elany</v>
+        <v>1789045560109-Griller</v>
       </c>
       <c r="B110">
-        <v>1789045530768</v>
+        <v>1789045560109</v>
       </c>
       <c r="C110" t="str">
-        <v>b1elany</v>
+        <v>Griller</v>
       </c>
       <c r="D110" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E110" t="str">
         <v>EVENT</v>
@@ -6607,16 +6607,16 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>1789045530768-n1Xen</v>
+        <v>1789045560109-AclioN</v>
       </c>
       <c r="B111">
-        <v>1789045530768</v>
+        <v>1789045560109</v>
       </c>
       <c r="C111" t="str">
-        <v>n1Xen</v>
+        <v>AclioN</v>
       </c>
       <c r="D111" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="E111" t="str">
         <v>EVENT</v>
@@ -6648,16 +6648,16 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>1787471977697-oskar</v>
+        <v>1789045530768-Matheos</v>
       </c>
       <c r="B112">
-        <v>1787471977697</v>
+        <v>1789045530768</v>
       </c>
       <c r="C112" t="str">
-        <v>oskar</v>
+        <v>Matheos</v>
       </c>
       <c r="D112" t="str">
-        <v>Astana Dragons</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E112" t="str">
         <v>EVENT</v>
@@ -6675,7 +6675,7 @@
         <v>Europe</v>
       </c>
       <c r="J112" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K112">
         <v>1</v>
@@ -6689,16 +6689,16 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>1787471977697-PR</v>
+        <v>1789045530768-Jorko</v>
       </c>
       <c r="B113">
-        <v>1787471977697</v>
+        <v>1789045530768</v>
       </c>
       <c r="C113" t="str">
-        <v>PR</v>
+        <v>Jorko</v>
       </c>
       <c r="D113" t="str">
-        <v>Astana Dragons</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E113" t="str">
         <v>EVENT</v>
@@ -6716,7 +6716,7 @@
         <v>Europe</v>
       </c>
       <c r="J113" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K113">
         <v>1</v>
@@ -6730,16 +6730,16 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>1787471977697-Tauson</v>
+        <v>1789045530768-Tapewaare</v>
       </c>
       <c r="B114">
-        <v>1787471977697</v>
+        <v>1789045530768</v>
       </c>
       <c r="C114" t="str">
-        <v>Tauson</v>
+        <v>Tapewaare</v>
       </c>
       <c r="D114" t="str">
-        <v>Astana Dragons</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E114" t="str">
         <v>EVENT</v>
@@ -6757,7 +6757,7 @@
         <v>Europe</v>
       </c>
       <c r="J114" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K114">
         <v>1</v>
@@ -6771,16 +6771,16 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>1787471977697-ztr</v>
+        <v>1789045530768-b1elany</v>
       </c>
       <c r="B115">
-        <v>1787471977697</v>
+        <v>1789045530768</v>
       </c>
       <c r="C115" t="str">
-        <v>ztr</v>
+        <v>b1elany</v>
       </c>
       <c r="D115" t="str">
-        <v>Astana Dragons</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E115" t="str">
         <v>EVENT</v>
@@ -6798,7 +6798,7 @@
         <v>Europe</v>
       </c>
       <c r="J115" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K115">
         <v>1</v>
@@ -6812,16 +6812,16 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>1787471977697-REZ</v>
+        <v>1789045530768-n1Xen</v>
       </c>
       <c r="B116">
-        <v>1787471977697</v>
+        <v>1789045530768</v>
       </c>
       <c r="C116" t="str">
-        <v>REZ</v>
+        <v>n1Xen</v>
       </c>
       <c r="D116" t="str">
-        <v>Astana Dragons</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="E116" t="str">
         <v>EVENT</v>
@@ -6839,7 +6839,7 @@
         <v>Europe</v>
       </c>
       <c r="J116" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K116">
         <v>1</v>
@@ -6853,16 +6853,16 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>1787471970177-OneUn1que</v>
+        <v>1787471977697-oskar</v>
       </c>
       <c r="B117">
-        <v>1787471970177</v>
+        <v>1787471977697</v>
       </c>
       <c r="C117" t="str">
-        <v>OneUn1que</v>
+        <v>oskar</v>
       </c>
       <c r="D117" t="str">
-        <v>Vox Eminor</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E117" t="str">
         <v>EVENT</v>
@@ -6880,7 +6880,7 @@
         <v>Europe</v>
       </c>
       <c r="J117" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K117">
         <v>1</v>
@@ -6894,16 +6894,16 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>1787471970177-kL1o</v>
+        <v>1787471977697-PR</v>
       </c>
       <c r="B118">
-        <v>1787471970177</v>
+        <v>1787471977697</v>
       </c>
       <c r="C118" t="str">
-        <v>kL1o</v>
+        <v>PR</v>
       </c>
       <c r="D118" t="str">
-        <v>Vox Eminor</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E118" t="str">
         <v>EVENT</v>
@@ -6921,7 +6921,7 @@
         <v>Europe</v>
       </c>
       <c r="J118" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K118">
         <v>1</v>
@@ -6935,16 +6935,16 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>1787471970177-marat2k</v>
+        <v>1787471977697-Tauson</v>
       </c>
       <c r="B119">
-        <v>1787471970177</v>
+        <v>1787471977697</v>
       </c>
       <c r="C119" t="str">
-        <v>marat2k</v>
+        <v>Tauson</v>
       </c>
       <c r="D119" t="str">
-        <v>Vox Eminor</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E119" t="str">
         <v>EVENT</v>
@@ -6962,7 +6962,7 @@
         <v>Europe</v>
       </c>
       <c r="J119" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K119">
         <v>1</v>
@@ -6976,16 +6976,16 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>1787471970177-Malkiss</v>
+        <v>1787471977697-ztr</v>
       </c>
       <c r="B120">
-        <v>1787471970177</v>
+        <v>1787471977697</v>
       </c>
       <c r="C120" t="str">
-        <v>Malkiss</v>
+        <v>ztr</v>
       </c>
       <c r="D120" t="str">
-        <v>Vox Eminor</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E120" t="str">
         <v>EVENT</v>
@@ -7003,7 +7003,7 @@
         <v>Europe</v>
       </c>
       <c r="J120" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K120">
         <v>1</v>
@@ -7017,16 +7017,16 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>1787471970177-kr1vda</v>
+        <v>1787471977697-REZ</v>
       </c>
       <c r="B121">
-        <v>1787471970177</v>
+        <v>1787471977697</v>
       </c>
       <c r="C121" t="str">
-        <v>kr1vda</v>
+        <v>REZ</v>
       </c>
       <c r="D121" t="str">
-        <v>Vox Eminor</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E121" t="str">
         <v>EVENT</v>
@@ -7044,7 +7044,7 @@
         <v>Europe</v>
       </c>
       <c r="J121" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K121">
         <v>1</v>
@@ -7058,16 +7058,16 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>1787471959675-jambo</v>
+        <v>1787471970177-OneUn1que</v>
       </c>
       <c r="B122">
-        <v>1787471959675</v>
+        <v>1787471970177</v>
       </c>
       <c r="C122" t="str">
-        <v>jambo</v>
+        <v>OneUn1que</v>
       </c>
       <c r="D122" t="str">
-        <v>Fnatic</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E122" t="str">
         <v>EVENT</v>
@@ -7085,7 +7085,7 @@
         <v>Europe</v>
       </c>
       <c r="J122" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K122">
         <v>1</v>
@@ -7099,16 +7099,16 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>1787471959675-fear</v>
+        <v>1787471970177-kL1o</v>
       </c>
       <c r="B123">
-        <v>1787471959675</v>
+        <v>1787471970177</v>
       </c>
       <c r="C123" t="str">
-        <v>fear</v>
+        <v>kL1o</v>
       </c>
       <c r="D123" t="str">
-        <v>Fnatic</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E123" t="str">
         <v>EVENT</v>
@@ -7126,7 +7126,7 @@
         <v>Europe</v>
       </c>
       <c r="J123" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K123">
         <v>1</v>
@@ -7140,16 +7140,16 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>1787471959675-blameF</v>
+        <v>1787471970177-marat2k</v>
       </c>
       <c r="B124">
-        <v>1787471959675</v>
+        <v>1787471970177</v>
       </c>
       <c r="C124" t="str">
-        <v>blameF</v>
+        <v>marat2k</v>
       </c>
       <c r="D124" t="str">
-        <v>Fnatic</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E124" t="str">
         <v>EVENT</v>
@@ -7167,7 +7167,7 @@
         <v>Europe</v>
       </c>
       <c r="J124" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K124">
         <v>1</v>
@@ -7181,16 +7181,16 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>1787471959675-KRIMZ</v>
+        <v>1787471970177-Malkiss</v>
       </c>
       <c r="B125">
-        <v>1787471959675</v>
+        <v>1787471970177</v>
       </c>
       <c r="C125" t="str">
-        <v>KRIMZ</v>
+        <v>Malkiss</v>
       </c>
       <c r="D125" t="str">
-        <v>Fnatic</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E125" t="str">
         <v>EVENT</v>
@@ -7208,7 +7208,7 @@
         <v>Europe</v>
       </c>
       <c r="J125" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K125">
         <v>1</v>
@@ -7222,22 +7222,22 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>1789045299584-hades</v>
+        <v>1787471970177-kr1vda</v>
       </c>
       <c r="B126">
-        <v>1789045299584</v>
+        <v>1787471970177</v>
       </c>
       <c r="C126" t="str">
-        <v>hades</v>
+        <v>kr1vda</v>
       </c>
       <c r="D126" t="str">
-        <v>Mythic</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E126" t="str">
         <v>EVENT</v>
       </c>
       <c r="F126" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -7246,10 +7246,10 @@
         <v>Regional</v>
       </c>
       <c r="I126" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J126" t="str">
-        <v>Fourth</v>
+        <v>Second</v>
       </c>
       <c r="K126">
         <v>1</v>
@@ -7263,22 +7263,22 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>1789045299584-PwnAlone</v>
+        <v>1787471959675-jambo</v>
       </c>
       <c r="B127">
-        <v>1789045299584</v>
+        <v>1787471959675</v>
       </c>
       <c r="C127" t="str">
-        <v>PwnAlone</v>
+        <v>jambo</v>
       </c>
       <c r="D127" t="str">
-        <v>Mythic</v>
+        <v>Fnatic</v>
       </c>
       <c r="E127" t="str">
         <v>EVENT</v>
       </c>
       <c r="F127" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -7287,10 +7287,10 @@
         <v>Regional</v>
       </c>
       <c r="I127" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J127" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K127">
         <v>1</v>
@@ -7304,22 +7304,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>1789045299584-Trucklover86</v>
+        <v>1787471959675-fear</v>
       </c>
       <c r="B128">
-        <v>1789045299584</v>
+        <v>1787471959675</v>
       </c>
       <c r="C128" t="str">
-        <v>Trucklover86</v>
+        <v>fear</v>
       </c>
       <c r="D128" t="str">
-        <v>Mythic</v>
+        <v>Fnatic</v>
       </c>
       <c r="E128" t="str">
         <v>EVENT</v>
       </c>
       <c r="F128" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -7328,10 +7328,10 @@
         <v>Regional</v>
       </c>
       <c r="I128" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J128" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K128">
         <v>1</v>
@@ -7345,22 +7345,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>1789045299584-hyza</v>
+        <v>1787471959675-blameF</v>
       </c>
       <c r="B129">
-        <v>1789045299584</v>
+        <v>1787471959675</v>
       </c>
       <c r="C129" t="str">
-        <v>hyza</v>
+        <v>blameF</v>
       </c>
       <c r="D129" t="str">
-        <v>Mythic</v>
+        <v>Fnatic</v>
       </c>
       <c r="E129" t="str">
         <v>EVENT</v>
       </c>
       <c r="F129" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -7369,10 +7369,10 @@
         <v>Regional</v>
       </c>
       <c r="I129" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J129" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K129">
         <v>1</v>
@@ -7386,22 +7386,22 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>1789045299584-Cooper</v>
+        <v>1787471959675-KRIMZ</v>
       </c>
       <c r="B130">
-        <v>1789045299584</v>
+        <v>1787471959675</v>
       </c>
       <c r="C130" t="str">
-        <v>Cooper</v>
+        <v>KRIMZ</v>
       </c>
       <c r="D130" t="str">
-        <v>Mythic</v>
+        <v>Fnatic</v>
       </c>
       <c r="E130" t="str">
         <v>EVENT</v>
       </c>
       <c r="F130" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -7410,10 +7410,10 @@
         <v>Regional</v>
       </c>
       <c r="I130" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J130" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K130">
         <v>1</v>
@@ -7427,16 +7427,16 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>1789045274106-blaze</v>
+        <v>1789045299584-hades</v>
       </c>
       <c r="B131">
-        <v>1789045274106</v>
+        <v>1789045299584</v>
       </c>
       <c r="C131" t="str">
-        <v>blaze</v>
+        <v>hades</v>
       </c>
       <c r="D131" t="str">
-        <v>paiN Academy</v>
+        <v>Mythic</v>
       </c>
       <c r="E131" t="str">
         <v>EVENT</v>
@@ -7468,16 +7468,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>1789045274106-h0t</v>
+        <v>1789045299584-PwnAlone</v>
       </c>
       <c r="B132">
-        <v>1789045274106</v>
+        <v>1789045299584</v>
       </c>
       <c r="C132" t="str">
-        <v>h0t</v>
+        <v>PwnAlone</v>
       </c>
       <c r="D132" t="str">
-        <v>paiN Academy</v>
+        <v>Mythic</v>
       </c>
       <c r="E132" t="str">
         <v>EVENT</v>
@@ -7509,16 +7509,16 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>1789045274106-bsd</v>
+        <v>1789045299584-Trucklover86</v>
       </c>
       <c r="B133">
-        <v>1789045274106</v>
+        <v>1789045299584</v>
       </c>
       <c r="C133" t="str">
-        <v>bsd</v>
+        <v>Trucklover86</v>
       </c>
       <c r="D133" t="str">
-        <v>paiN Academy</v>
+        <v>Mythic</v>
       </c>
       <c r="E133" t="str">
         <v>EVENT</v>
@@ -7550,16 +7550,16 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>1789045274106-b4rtiN</v>
+        <v>1789045299584-hyza</v>
       </c>
       <c r="B134">
-        <v>1789045274106</v>
+        <v>1789045299584</v>
       </c>
       <c r="C134" t="str">
-        <v>b4rtiN</v>
+        <v>hyza</v>
       </c>
       <c r="D134" t="str">
-        <v>paiN Academy</v>
+        <v>Mythic</v>
       </c>
       <c r="E134" t="str">
         <v>EVENT</v>
@@ -7591,16 +7591,16 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>1789045274106-NEKIZ</v>
+        <v>1789045299584-Cooper</v>
       </c>
       <c r="B135">
-        <v>1789045274106</v>
+        <v>1789045299584</v>
       </c>
       <c r="C135" t="str">
-        <v>NEKIZ</v>
+        <v>Cooper</v>
       </c>
       <c r="D135" t="str">
-        <v>paiN Academy</v>
+        <v>Mythic</v>
       </c>
       <c r="E135" t="str">
         <v>EVENT</v>
@@ -7632,16 +7632,16 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>1789045224902-saadzin</v>
+        <v>1789045274106-blaze</v>
       </c>
       <c r="B136">
-        <v>1789045224902</v>
+        <v>1789045274106</v>
       </c>
       <c r="C136" t="str">
-        <v>saadzin</v>
+        <v>blaze</v>
       </c>
       <c r="D136" t="str">
-        <v>Legacy</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E136" t="str">
         <v>EVENT</v>
@@ -7673,16 +7673,16 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>1789045224902-lux</v>
+        <v>1789045274106-h0t</v>
       </c>
       <c r="B137">
-        <v>1789045224902</v>
+        <v>1789045274106</v>
       </c>
       <c r="C137" t="str">
-        <v>lux</v>
+        <v>h0t</v>
       </c>
       <c r="D137" t="str">
-        <v>Legacy</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E137" t="str">
         <v>EVENT</v>
@@ -7714,16 +7714,16 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>1789045224902-n1ssim</v>
+        <v>1789045274106-bsd</v>
       </c>
       <c r="B138">
-        <v>1789045224902</v>
+        <v>1789045274106</v>
       </c>
       <c r="C138" t="str">
-        <v>n1ssim</v>
+        <v>bsd</v>
       </c>
       <c r="D138" t="str">
-        <v>Legacy</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E138" t="str">
         <v>EVENT</v>
@@ -7755,16 +7755,16 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>1789045224902-latto</v>
+        <v>1789045274106-b4rtiN</v>
       </c>
       <c r="B139">
-        <v>1789045224902</v>
+        <v>1789045274106</v>
       </c>
       <c r="C139" t="str">
-        <v>latto</v>
+        <v>b4rtiN</v>
       </c>
       <c r="D139" t="str">
-        <v>Legacy</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E139" t="str">
         <v>EVENT</v>
@@ -7796,16 +7796,16 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>1789045224902-dumau</v>
+        <v>1789045274106-NEKIZ</v>
       </c>
       <c r="B140">
-        <v>1789045224902</v>
+        <v>1789045274106</v>
       </c>
       <c r="C140" t="str">
-        <v>dumau</v>
+        <v>NEKIZ</v>
       </c>
       <c r="D140" t="str">
-        <v>Legacy</v>
+        <v>paiN Academy</v>
       </c>
       <c r="E140" t="str">
         <v>EVENT</v>
@@ -7837,16 +7837,16 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>1789045150461-levi</v>
+        <v>1789045224902-saadzin</v>
       </c>
       <c r="B141">
-        <v>1789045150461</v>
+        <v>1789045224902</v>
       </c>
       <c r="C141" t="str">
-        <v>levi</v>
+        <v>saadzin</v>
       </c>
       <c r="D141" t="str">
-        <v>Into the Beach</v>
+        <v>Legacy</v>
       </c>
       <c r="E141" t="str">
         <v>EVENT</v>
@@ -7878,16 +7878,16 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>1789045150461-urban0</v>
+        <v>1789045224902-lux</v>
       </c>
       <c r="B142">
-        <v>1789045150461</v>
+        <v>1789045224902</v>
       </c>
       <c r="C142" t="str">
-        <v>urban0</v>
+        <v>lux</v>
       </c>
       <c r="D142" t="str">
-        <v>Into the Beach</v>
+        <v>Legacy</v>
       </c>
       <c r="E142" t="str">
         <v>EVENT</v>
@@ -7919,16 +7919,16 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>1789045150461-t9rnay</v>
+        <v>1789045224902-n1ssim</v>
       </c>
       <c r="B143">
-        <v>1789045150461</v>
+        <v>1789045224902</v>
       </c>
       <c r="C143" t="str">
-        <v>t9rnay</v>
+        <v>n1ssim</v>
       </c>
       <c r="D143" t="str">
-        <v>Into the Beach</v>
+        <v>Legacy</v>
       </c>
       <c r="E143" t="str">
         <v>EVENT</v>
@@ -7960,16 +7960,16 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>1789045150461-JOTA</v>
+        <v>1789045224902-latto</v>
       </c>
       <c r="B144">
-        <v>1789045150461</v>
+        <v>1789045224902</v>
       </c>
       <c r="C144" t="str">
-        <v>JOTA</v>
+        <v>latto</v>
       </c>
       <c r="D144" t="str">
-        <v>Into the Beach</v>
+        <v>Legacy</v>
       </c>
       <c r="E144" t="str">
         <v>EVENT</v>
@@ -8001,16 +8001,16 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>1789045150461-shz</v>
+        <v>1789045224902-dumau</v>
       </c>
       <c r="B145">
-        <v>1789045150461</v>
+        <v>1789045224902</v>
       </c>
       <c r="C145" t="str">
-        <v>shz</v>
+        <v>dumau</v>
       </c>
       <c r="D145" t="str">
-        <v>Into the Beach</v>
+        <v>Legacy</v>
       </c>
       <c r="E145" t="str">
         <v>EVENT</v>
@@ -8042,16 +8042,16 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>1789045118610-huncho</v>
+        <v>1789045150461-levi</v>
       </c>
       <c r="B146">
-        <v>1789045118610</v>
+        <v>1789045150461</v>
       </c>
       <c r="C146" t="str">
-        <v>huncho</v>
+        <v>levi</v>
       </c>
       <c r="D146" t="str">
-        <v>Take Flyte</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E146" t="str">
         <v>EVENT</v>
@@ -8083,16 +8083,16 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>1789045118610-Crisp</v>
+        <v>1789045150461-urban0</v>
       </c>
       <c r="B147">
-        <v>1789045118610</v>
+        <v>1789045150461</v>
       </c>
       <c r="C147" t="str">
-        <v>Crisp</v>
+        <v>urban0</v>
       </c>
       <c r="D147" t="str">
-        <v>Take Flyte</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E147" t="str">
         <v>EVENT</v>
@@ -8124,16 +8124,16 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>1789045118610-FxRE</v>
+        <v>1789045150461-t9rnay</v>
       </c>
       <c r="B148">
-        <v>1789045118610</v>
+        <v>1789045150461</v>
       </c>
       <c r="C148" t="str">
-        <v>FxRE</v>
+        <v>t9rnay</v>
       </c>
       <c r="D148" t="str">
-        <v>Take Flyte</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E148" t="str">
         <v>EVENT</v>
@@ -8165,16 +8165,16 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>1789045118610-Panic</v>
+        <v>1789045150461-JOTA</v>
       </c>
       <c r="B149">
-        <v>1789045118610</v>
+        <v>1789045150461</v>
       </c>
       <c r="C149" t="str">
-        <v>Panic</v>
+        <v>JOTA</v>
       </c>
       <c r="D149" t="str">
-        <v>Take Flyte</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E149" t="str">
         <v>EVENT</v>
@@ -8206,16 +8206,16 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>1789045118610-REKMEISTER</v>
+        <v>1789045150461-shz</v>
       </c>
       <c r="B150">
-        <v>1789045118610</v>
+        <v>1789045150461</v>
       </c>
       <c r="C150" t="str">
-        <v>REKMEISTER</v>
+        <v>shz</v>
       </c>
       <c r="D150" t="str">
-        <v>Take Flyte</v>
+        <v>Into the Beach</v>
       </c>
       <c r="E150" t="str">
         <v>EVENT</v>
@@ -8247,16 +8247,16 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>1784854079769-Benkai</v>
+        <v>1789045118610-huncho</v>
       </c>
       <c r="B151">
-        <v>1784854079769</v>
+        <v>1789045118610</v>
       </c>
       <c r="C151" t="str">
-        <v>Benkai</v>
+        <v>huncho</v>
       </c>
       <c r="D151" t="str">
-        <v>Entropiq</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E151" t="str">
         <v>EVENT</v>
@@ -8274,7 +8274,7 @@
         <v>America</v>
       </c>
       <c r="J151" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K151">
         <v>1</v>
@@ -8288,16 +8288,16 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>1784854079769-dea</v>
+        <v>1789045118610-Crisp</v>
       </c>
       <c r="B152">
-        <v>1784854079769</v>
+        <v>1789045118610</v>
       </c>
       <c r="C152" t="str">
-        <v>dea</v>
+        <v>Crisp</v>
       </c>
       <c r="D152" t="str">
-        <v>Entropiq</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E152" t="str">
         <v>EVENT</v>
@@ -8315,7 +8315,7 @@
         <v>America</v>
       </c>
       <c r="J152" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K152">
         <v>1</v>
@@ -8329,16 +8329,16 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>1784854079769-shane</v>
+        <v>1789045118610-FxRE</v>
       </c>
       <c r="B153">
-        <v>1784854079769</v>
+        <v>1789045118610</v>
       </c>
       <c r="C153" t="str">
-        <v>shane</v>
+        <v>FxRE</v>
       </c>
       <c r="D153" t="str">
-        <v>Entropiq</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E153" t="str">
         <v>EVENT</v>
@@ -8356,7 +8356,7 @@
         <v>America</v>
       </c>
       <c r="J153" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K153">
         <v>1</v>
@@ -8370,16 +8370,16 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>1784854079769-nosraC</v>
+        <v>1789045118610-Panic</v>
       </c>
       <c r="B154">
-        <v>1784854079769</v>
+        <v>1789045118610</v>
       </c>
       <c r="C154" t="str">
-        <v>nosraC</v>
+        <v>Panic</v>
       </c>
       <c r="D154" t="str">
-        <v>Entropiq</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E154" t="str">
         <v>EVENT</v>
@@ -8397,7 +8397,7 @@
         <v>America</v>
       </c>
       <c r="J154" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K154">
         <v>1</v>
@@ -8411,16 +8411,16 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>1784854079769-MarKE</v>
+        <v>1789045118610-REKMEISTER</v>
       </c>
       <c r="B155">
-        <v>1784854079769</v>
+        <v>1789045118610</v>
       </c>
       <c r="C155" t="str">
-        <v>MarKE</v>
+        <v>REKMEISTER</v>
       </c>
       <c r="D155" t="str">
-        <v>Entropiq</v>
+        <v>Take Flyte</v>
       </c>
       <c r="E155" t="str">
         <v>EVENT</v>
@@ -8438,7 +8438,7 @@
         <v>America</v>
       </c>
       <c r="J155" t="str">
-        <v>Third</v>
+        <v>Fourth</v>
       </c>
       <c r="K155">
         <v>1</v>
@@ -8452,16 +8452,16 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>1784854026526-ivz</v>
+        <v>1784854079769-Benkai</v>
       </c>
       <c r="B156">
-        <v>1784854026526</v>
+        <v>1784854079769</v>
       </c>
       <c r="C156" t="str">
-        <v>ivz</v>
+        <v>Benkai</v>
       </c>
       <c r="D156" t="str">
-        <v>AMKAL</v>
+        <v>Entropiq</v>
       </c>
       <c r="E156" t="str">
         <v>EVENT</v>
@@ -8479,7 +8479,7 @@
         <v>America</v>
       </c>
       <c r="J156" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K156">
         <v>1</v>
@@ -8493,16 +8493,16 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>1784854026526-abizz</v>
+        <v>1784854079769-dea</v>
       </c>
       <c r="B157">
-        <v>1784854026526</v>
+        <v>1784854079769</v>
       </c>
       <c r="C157" t="str">
-        <v>abizz</v>
+        <v>dea</v>
       </c>
       <c r="D157" t="str">
-        <v>AMKAL</v>
+        <v>Entropiq</v>
       </c>
       <c r="E157" t="str">
         <v>EVENT</v>
@@ -8520,7 +8520,7 @@
         <v>America</v>
       </c>
       <c r="J157" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K157">
         <v>1</v>
@@ -8534,16 +8534,16 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>1784854026526-nacho</v>
+        <v>1784854079769-shane</v>
       </c>
       <c r="B158">
-        <v>1784854026526</v>
+        <v>1784854079769</v>
       </c>
       <c r="C158" t="str">
-        <v>nacho</v>
+        <v>shane</v>
       </c>
       <c r="D158" t="str">
-        <v>AMKAL</v>
+        <v>Entropiq</v>
       </c>
       <c r="E158" t="str">
         <v>EVENT</v>
@@ -8561,7 +8561,7 @@
         <v>America</v>
       </c>
       <c r="J158" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K158">
         <v>1</v>
@@ -8575,16 +8575,16 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>1784854026526-BK1</v>
+        <v>1784854079769-nosraC</v>
       </c>
       <c r="B159">
-        <v>1784854026526</v>
+        <v>1784854079769</v>
       </c>
       <c r="C159" t="str">
-        <v>BK1</v>
+        <v>nosraC</v>
       </c>
       <c r="D159" t="str">
-        <v>AMKAL</v>
+        <v>Entropiq</v>
       </c>
       <c r="E159" t="str">
         <v>EVENT</v>
@@ -8602,7 +8602,7 @@
         <v>America</v>
       </c>
       <c r="J159" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K159">
         <v>1</v>
@@ -8616,16 +8616,16 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>1784854026526-next</v>
+        <v>1784854079769-MarKE</v>
       </c>
       <c r="B160">
-        <v>1784854026526</v>
+        <v>1784854079769</v>
       </c>
       <c r="C160" t="str">
-        <v>next</v>
+        <v>MarKE</v>
       </c>
       <c r="D160" t="str">
-        <v>AMKAL</v>
+        <v>Entropiq</v>
       </c>
       <c r="E160" t="str">
         <v>EVENT</v>
@@ -8643,7 +8643,7 @@
         <v>America</v>
       </c>
       <c r="J160" t="str">
-        <v>Second</v>
+        <v>Third</v>
       </c>
       <c r="K160">
         <v>1</v>
@@ -8657,16 +8657,16 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>1784848026994-molodoy</v>
+        <v>1784854026526-ivz</v>
       </c>
       <c r="B161">
-        <v>1784848026994</v>
+        <v>1784854026526</v>
       </c>
       <c r="C161" t="str">
-        <v>molodoy</v>
+        <v>ivz</v>
       </c>
       <c r="D161" t="str">
-        <v>FURIA</v>
+        <v>AMKAL</v>
       </c>
       <c r="E161" t="str">
         <v>EVENT</v>
@@ -8684,7 +8684,7 @@
         <v>America</v>
       </c>
       <c r="J161" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K161">
         <v>1</v>
@@ -8698,16 +8698,16 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>1784848026994-KSCERATO</v>
+        <v>1784854026526-abizz</v>
       </c>
       <c r="B162">
-        <v>1784848026994</v>
+        <v>1784854026526</v>
       </c>
       <c r="C162" t="str">
-        <v>KSCERATO</v>
+        <v>abizz</v>
       </c>
       <c r="D162" t="str">
-        <v>FURIA</v>
+        <v>AMKAL</v>
       </c>
       <c r="E162" t="str">
         <v>EVENT</v>
@@ -8725,7 +8725,7 @@
         <v>America</v>
       </c>
       <c r="J162" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K162">
         <v>1</v>
@@ -8739,16 +8739,16 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>1784848026994-YEKINDAR</v>
+        <v>1784854026526-nacho</v>
       </c>
       <c r="B163">
-        <v>1784848026994</v>
+        <v>1784854026526</v>
       </c>
       <c r="C163" t="str">
-        <v>YEKINDAR</v>
+        <v>nacho</v>
       </c>
       <c r="D163" t="str">
-        <v>FURIA</v>
+        <v>AMKAL</v>
       </c>
       <c r="E163" t="str">
         <v>EVENT</v>
@@ -8766,7 +8766,7 @@
         <v>America</v>
       </c>
       <c r="J163" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K163">
         <v>1</v>
@@ -8780,16 +8780,16 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>1784848026994-yuurih</v>
+        <v>1784854026526-BK1</v>
       </c>
       <c r="B164">
-        <v>1784848026994</v>
+        <v>1784854026526</v>
       </c>
       <c r="C164" t="str">
-        <v>yuurih</v>
+        <v>BK1</v>
       </c>
       <c r="D164" t="str">
-        <v>FURIA</v>
+        <v>AMKAL</v>
       </c>
       <c r="E164" t="str">
         <v>EVENT</v>
@@ -8807,7 +8807,7 @@
         <v>America</v>
       </c>
       <c r="J164" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K164">
         <v>1</v>
@@ -8821,16 +8821,16 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>1784848026994-FalleN</v>
+        <v>1784854026526-next</v>
       </c>
       <c r="B165">
-        <v>1784848026994</v>
+        <v>1784854026526</v>
       </c>
       <c r="C165" t="str">
-        <v>FalleN</v>
+        <v>next</v>
       </c>
       <c r="D165" t="str">
-        <v>FURIA</v>
+        <v>AMKAL</v>
       </c>
       <c r="E165" t="str">
         <v>EVENT</v>
@@ -8848,7 +8848,7 @@
         <v>America</v>
       </c>
       <c r="J165" t="str">
-        <v>Winner</v>
+        <v>Second</v>
       </c>
       <c r="K165">
         <v>1</v>
@@ -8862,34 +8862,34 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>1789044307262-sowalio</v>
+        <v>1784848026994-molodoy</v>
       </c>
       <c r="B166">
-        <v>1789044307262</v>
+        <v>1784848026994</v>
       </c>
       <c r="C166" t="str">
-        <v>sowalio</v>
+        <v>molodoy</v>
       </c>
       <c r="D166" t="str">
-        <v>Nemiga</v>
+        <v>FURIA</v>
       </c>
       <c r="E166" t="str">
         <v>EVENT</v>
       </c>
       <c r="F166" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G166">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H166" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I166" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J166" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K166">
         <v>1</v>
@@ -8903,34 +8903,34 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>1789044307262-khaN</v>
+        <v>1784848026994-KSCERATO</v>
       </c>
       <c r="B167">
-        <v>1789044307262</v>
+        <v>1784848026994</v>
       </c>
       <c r="C167" t="str">
-        <v>khaN</v>
+        <v>KSCERATO</v>
       </c>
       <c r="D167" t="str">
-        <v>Nemiga</v>
+        <v>FURIA</v>
       </c>
       <c r="E167" t="str">
         <v>EVENT</v>
       </c>
       <c r="F167" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G167">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H167" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I167" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J167" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K167">
         <v>1</v>
@@ -8944,34 +8944,34 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>1789044307262-riskyb0b</v>
+        <v>1784848026994-YEKINDAR</v>
       </c>
       <c r="B168">
-        <v>1789044307262</v>
+        <v>1784848026994</v>
       </c>
       <c r="C168" t="str">
-        <v>riskyb0b</v>
+        <v>YEKINDAR</v>
       </c>
       <c r="D168" t="str">
-        <v>Nemiga</v>
+        <v>FURIA</v>
       </c>
       <c r="E168" t="str">
         <v>EVENT</v>
       </c>
       <c r="F168" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G168">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H168" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I168" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J168" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K168">
         <v>1</v>
@@ -8985,34 +8985,34 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>1789044307262-1eeR</v>
+        <v>1784848026994-yuurih</v>
       </c>
       <c r="B169">
-        <v>1789044307262</v>
+        <v>1784848026994</v>
       </c>
       <c r="C169" t="str">
-        <v>1eeR</v>
+        <v>yuurih</v>
       </c>
       <c r="D169" t="str">
-        <v>Nemiga</v>
+        <v>FURIA</v>
       </c>
       <c r="E169" t="str">
         <v>EVENT</v>
       </c>
       <c r="F169" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G169">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H169" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I169" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J169" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K169">
         <v>1</v>
@@ -9026,34 +9026,34 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>1789044307262-Xant3r</v>
+        <v>1784848026994-FalleN</v>
       </c>
       <c r="B170">
-        <v>1789044307262</v>
+        <v>1784848026994</v>
       </c>
       <c r="C170" t="str">
-        <v>Xant3r</v>
+        <v>FalleN</v>
       </c>
       <c r="D170" t="str">
-        <v>Nemiga</v>
+        <v>FURIA</v>
       </c>
       <c r="E170" t="str">
         <v>EVENT</v>
       </c>
       <c r="F170" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G170">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H170" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I170" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J170" t="str">
-        <v>Fourth</v>
+        <v>Winner</v>
       </c>
       <c r="K170">
         <v>1</v>
@@ -9067,16 +9067,16 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>1789044244253-w0nderful</v>
+        <v>1789044307262-sowalio</v>
       </c>
       <c r="B171">
-        <v>1789044244253</v>
+        <v>1789044307262</v>
       </c>
       <c r="C171" t="str">
-        <v>w0nderful</v>
+        <v>sowalio</v>
       </c>
       <c r="D171" t="str">
-        <v>Natus Vincere</v>
+        <v>Nemiga</v>
       </c>
       <c r="E171" t="str">
         <v>EVENT</v>
@@ -9108,16 +9108,16 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>1789044244253-makazze</v>
+        <v>1789044307262-khaN</v>
       </c>
       <c r="B172">
-        <v>1789044244253</v>
+        <v>1789044307262</v>
       </c>
       <c r="C172" t="str">
-        <v>makazze</v>
+        <v>khaN</v>
       </c>
       <c r="D172" t="str">
-        <v>Natus Vincere</v>
+        <v>Nemiga</v>
       </c>
       <c r="E172" t="str">
         <v>EVENT</v>
@@ -9149,16 +9149,16 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>1789044244253-b1t</v>
+        <v>1789044307262-riskyb0b</v>
       </c>
       <c r="B173">
-        <v>1789044244253</v>
+        <v>1789044307262</v>
       </c>
       <c r="C173" t="str">
-        <v>b1t</v>
+        <v>riskyb0b</v>
       </c>
       <c r="D173" t="str">
-        <v>Natus Vincere</v>
+        <v>Nemiga</v>
       </c>
       <c r="E173" t="str">
         <v>EVENT</v>
@@ -9190,16 +9190,16 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>1789044244253-iM</v>
+        <v>1789044307262-1eeR</v>
       </c>
       <c r="B174">
-        <v>1789044244253</v>
+        <v>1789044307262</v>
       </c>
       <c r="C174" t="str">
-        <v>iM</v>
+        <v>1eeR</v>
       </c>
       <c r="D174" t="str">
-        <v>Natus Vincere</v>
+        <v>Nemiga</v>
       </c>
       <c r="E174" t="str">
         <v>EVENT</v>
@@ -9231,16 +9231,16 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>1789044244253-Aleksib</v>
+        <v>1789044307262-Xant3r</v>
       </c>
       <c r="B175">
-        <v>1789044244253</v>
+        <v>1789044307262</v>
       </c>
       <c r="C175" t="str">
-        <v>Aleksib</v>
+        <v>Xant3r</v>
       </c>
       <c r="D175" t="str">
-        <v>Natus Vincere</v>
+        <v>Nemiga</v>
       </c>
       <c r="E175" t="str">
         <v>EVENT</v>
@@ -9272,16 +9272,16 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>1789044197304-Dytor</v>
+        <v>1789044244253-w0nderful</v>
       </c>
       <c r="B176">
-        <v>1789044197304</v>
+        <v>1789044244253</v>
       </c>
       <c r="C176" t="str">
-        <v>Dytor</v>
+        <v>w0nderful</v>
       </c>
       <c r="D176" t="str">
-        <v>Copenhagen Flames</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E176" t="str">
         <v>EVENT</v>
@@ -9313,16 +9313,16 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>1789044197304-nbqq</v>
+        <v>1789044244253-makazze</v>
       </c>
       <c r="B177">
-        <v>1789044197304</v>
+        <v>1789044244253</v>
       </c>
       <c r="C177" t="str">
-        <v>nbqq</v>
+        <v>makazze</v>
       </c>
       <c r="D177" t="str">
-        <v>Copenhagen Flames</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E177" t="str">
         <v>EVENT</v>
@@ -9354,16 +9354,16 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>1789044197304-forsyy</v>
+        <v>1789044244253-b1t</v>
       </c>
       <c r="B178">
-        <v>1789044197304</v>
+        <v>1789044244253</v>
       </c>
       <c r="C178" t="str">
-        <v>forsyy</v>
+        <v>b1t</v>
       </c>
       <c r="D178" t="str">
-        <v>Copenhagen Flames</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E178" t="str">
         <v>EVENT</v>
@@ -9395,16 +9395,16 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>1789044197304-ROGA</v>
+        <v>1789044244253-iM</v>
       </c>
       <c r="B179">
-        <v>1789044197304</v>
+        <v>1789044244253</v>
       </c>
       <c r="C179" t="str">
-        <v>ROGA</v>
+        <v>iM</v>
       </c>
       <c r="D179" t="str">
-        <v>Copenhagen Flames</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E179" t="str">
         <v>EVENT</v>
@@ -9436,16 +9436,16 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>1789044197304-DANK1NG</v>
+        <v>1789044244253-Aleksib</v>
       </c>
       <c r="B180">
-        <v>1789044197304</v>
+        <v>1789044244253</v>
       </c>
       <c r="C180" t="str">
-        <v>DANK1NG</v>
+        <v>Aleksib</v>
       </c>
       <c r="D180" t="str">
-        <v>Copenhagen Flames</v>
+        <v>Natus Vincere</v>
       </c>
       <c r="E180" t="str">
         <v>EVENT</v>
@@ -9477,16 +9477,16 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>1789044064380-910</v>
+        <v>1789044197304-Dytor</v>
       </c>
       <c r="B181">
-        <v>1789044064380</v>
+        <v>1789044197304</v>
       </c>
       <c r="C181" t="str">
-        <v>910</v>
+        <v>Dytor</v>
       </c>
       <c r="D181" t="str">
-        <v>The MongolZ</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E181" t="str">
         <v>EVENT</v>
@@ -9518,16 +9518,16 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>1789044064380-mzinho</v>
+        <v>1789044197304-nbqq</v>
       </c>
       <c r="B182">
-        <v>1789044064380</v>
+        <v>1789044197304</v>
       </c>
       <c r="C182" t="str">
-        <v>mzinho</v>
+        <v>nbqq</v>
       </c>
       <c r="D182" t="str">
-        <v>The MongolZ</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E182" t="str">
         <v>EVENT</v>
@@ -9559,16 +9559,16 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>1789044064380-Senzu</v>
+        <v>1789044197304-forsyy</v>
       </c>
       <c r="B183">
-        <v>1789044064380</v>
+        <v>1789044197304</v>
       </c>
       <c r="C183" t="str">
-        <v>Senzu</v>
+        <v>forsyy</v>
       </c>
       <c r="D183" t="str">
-        <v>The MongolZ</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E183" t="str">
         <v>EVENT</v>
@@ -9600,16 +9600,16 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>1789044064380-Techno</v>
+        <v>1789044197304-ROGA</v>
       </c>
       <c r="B184">
-        <v>1789044064380</v>
+        <v>1789044197304</v>
       </c>
       <c r="C184" t="str">
-        <v>Techno</v>
+        <v>ROGA</v>
       </c>
       <c r="D184" t="str">
-        <v>The MongolZ</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E184" t="str">
         <v>EVENT</v>
@@ -9641,16 +9641,16 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>1789044064380-bLitz</v>
+        <v>1789044197304-DANK1NG</v>
       </c>
       <c r="B185">
-        <v>1789044064380</v>
+        <v>1789044197304</v>
       </c>
       <c r="C185" t="str">
-        <v>bLitz</v>
+        <v>DANK1NG</v>
       </c>
       <c r="D185" t="str">
-        <v>The MongolZ</v>
+        <v>Copenhagen Flames</v>
       </c>
       <c r="E185" t="str">
         <v>EVENT</v>
@@ -9682,16 +9682,16 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>1789043946191-ultimate</v>
+        <v>1789044064380-910</v>
       </c>
       <c r="B186">
-        <v>1789043946191</v>
+        <v>1789044064380</v>
       </c>
       <c r="C186" t="str">
-        <v>ultimate</v>
+        <v>910</v>
       </c>
       <c r="D186" t="str">
-        <v>Liquid</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E186" t="str">
         <v>EVENT</v>
@@ -9723,16 +9723,16 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>1789043946191-siuhy</v>
+        <v>1789044064380-mzinho</v>
       </c>
       <c r="B187">
-        <v>1789043946191</v>
+        <v>1789044064380</v>
       </c>
       <c r="C187" t="str">
-        <v>siuhy</v>
+        <v>mzinho</v>
       </c>
       <c r="D187" t="str">
-        <v>Liquid</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E187" t="str">
         <v>EVENT</v>
@@ -9764,16 +9764,16 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>1789043946191-EliGE</v>
+        <v>1789044064380-Senzu</v>
       </c>
       <c r="B188">
-        <v>1789043946191</v>
+        <v>1789044064380</v>
       </c>
       <c r="C188" t="str">
-        <v>EliGE</v>
+        <v>Senzu</v>
       </c>
       <c r="D188" t="str">
-        <v>Liquid</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E188" t="str">
         <v>EVENT</v>
@@ -9805,16 +9805,16 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>1789043946191-NertZ</v>
+        <v>1789044064380-Techno</v>
       </c>
       <c r="B189">
-        <v>1789043946191</v>
+        <v>1789044064380</v>
       </c>
       <c r="C189" t="str">
-        <v>NertZ</v>
+        <v>Techno</v>
       </c>
       <c r="D189" t="str">
-        <v>Liquid</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E189" t="str">
         <v>EVENT</v>
@@ -9846,16 +9846,16 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>1789043946191-NAF</v>
+        <v>1789044064380-bLitz</v>
       </c>
       <c r="B190">
-        <v>1789043946191</v>
+        <v>1789044064380</v>
       </c>
       <c r="C190" t="str">
-        <v>NAF</v>
+        <v>bLitz</v>
       </c>
       <c r="D190" t="str">
-        <v>Liquid</v>
+        <v>The MongolZ</v>
       </c>
       <c r="E190" t="str">
         <v>EVENT</v>
@@ -9887,16 +9887,16 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>1783531237020-mezii</v>
+        <v>1789043946191-ultimate</v>
       </c>
       <c r="B191">
-        <v>1783531237020</v>
+        <v>1789043946191</v>
       </c>
       <c r="C191" t="str">
-        <v>mezii</v>
+        <v>ultimate</v>
       </c>
       <c r="D191" t="str">
-        <v>Vitality</v>
+        <v>Liquid</v>
       </c>
       <c r="E191" t="str">
         <v>EVENT</v>
@@ -9914,7 +9914,7 @@
         <v/>
       </c>
       <c r="J191" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K191">
         <v>1</v>
@@ -9928,16 +9928,16 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>1783531237020-flameZ</v>
+        <v>1789043946191-siuhy</v>
       </c>
       <c r="B192">
-        <v>1783531237020</v>
+        <v>1789043946191</v>
       </c>
       <c r="C192" t="str">
-        <v>flameZ</v>
+        <v>siuhy</v>
       </c>
       <c r="D192" t="str">
-        <v>Vitality</v>
+        <v>Liquid</v>
       </c>
       <c r="E192" t="str">
         <v>EVENT</v>
@@ -9955,7 +9955,7 @@
         <v/>
       </c>
       <c r="J192" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K192">
         <v>1</v>
@@ -9969,16 +9969,16 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>1783531237020-ropz</v>
+        <v>1789043946191-EliGE</v>
       </c>
       <c r="B193">
-        <v>1783531237020</v>
+        <v>1789043946191</v>
       </c>
       <c r="C193" t="str">
-        <v>ropz</v>
+        <v>EliGE</v>
       </c>
       <c r="D193" t="str">
-        <v>Vitality</v>
+        <v>Liquid</v>
       </c>
       <c r="E193" t="str">
         <v>EVENT</v>
@@ -9996,7 +9996,7 @@
         <v/>
       </c>
       <c r="J193" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K193">
         <v>1</v>
@@ -10010,16 +10010,16 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>1783531237020-apEX</v>
+        <v>1789043946191-NertZ</v>
       </c>
       <c r="B194">
-        <v>1783531237020</v>
+        <v>1789043946191</v>
       </c>
       <c r="C194" t="str">
-        <v>apEX</v>
+        <v>NertZ</v>
       </c>
       <c r="D194" t="str">
-        <v>Vitality</v>
+        <v>Liquid</v>
       </c>
       <c r="E194" t="str">
         <v>EVENT</v>
@@ -10037,7 +10037,7 @@
         <v/>
       </c>
       <c r="J194" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K194">
         <v>1</v>
@@ -10051,16 +10051,16 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>1783531237020-ZywOo</v>
+        <v>1789043946191-NAF</v>
       </c>
       <c r="B195">
-        <v>1783531237020</v>
+        <v>1789043946191</v>
       </c>
       <c r="C195" t="str">
-        <v>ZywOo</v>
+        <v>NAF</v>
       </c>
       <c r="D195" t="str">
-        <v>Vitality</v>
+        <v>Liquid</v>
       </c>
       <c r="E195" t="str">
         <v>EVENT</v>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="J195" t="str">
-        <v>Second</v>
+        <v>Fourth</v>
       </c>
       <c r="K195">
         <v>1</v>
@@ -10092,16 +10092,16 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>1783531248336-kyousuke</v>
+        <v>1783531237020-mezii</v>
       </c>
       <c r="B196">
-        <v>1783531248336</v>
+        <v>1783531237020</v>
       </c>
       <c r="C196" t="str">
-        <v>kyousuke</v>
+        <v>mezii</v>
       </c>
       <c r="D196" t="str">
-        <v>Falcons</v>
+        <v>Vitality</v>
       </c>
       <c r="E196" t="str">
         <v>EVENT</v>
@@ -10119,7 +10119,7 @@
         <v/>
       </c>
       <c r="J196" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K196">
         <v>1</v>
@@ -10133,16 +10133,16 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>1783531248336-kyxsan</v>
+        <v>1783531237020-flameZ</v>
       </c>
       <c r="B197">
-        <v>1783531248336</v>
+        <v>1783531237020</v>
       </c>
       <c r="C197" t="str">
-        <v>kyxsan</v>
+        <v>flameZ</v>
       </c>
       <c r="D197" t="str">
-        <v>Falcons</v>
+        <v>Vitality</v>
       </c>
       <c r="E197" t="str">
         <v>EVENT</v>
@@ -10160,7 +10160,7 @@
         <v/>
       </c>
       <c r="J197" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K197">
         <v>1</v>
@@ -10174,16 +10174,16 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>1783531248336-NiKo</v>
+        <v>1783531237020-ropz</v>
       </c>
       <c r="B198">
-        <v>1783531248336</v>
+        <v>1783531237020</v>
       </c>
       <c r="C198" t="str">
-        <v>NiKo</v>
+        <v>ropz</v>
       </c>
       <c r="D198" t="str">
-        <v>Falcons</v>
+        <v>Vitality</v>
       </c>
       <c r="E198" t="str">
         <v>EVENT</v>
@@ -10201,7 +10201,7 @@
         <v/>
       </c>
       <c r="J198" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K198">
         <v>1</v>
@@ -10215,16 +10215,16 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>1783531248336-TeSeS</v>
+        <v>1783531237020-apEX</v>
       </c>
       <c r="B199">
-        <v>1783531248336</v>
+        <v>1783531237020</v>
       </c>
       <c r="C199" t="str">
-        <v>TeSeS</v>
+        <v>apEX</v>
       </c>
       <c r="D199" t="str">
-        <v>Falcons</v>
+        <v>Vitality</v>
       </c>
       <c r="E199" t="str">
         <v>EVENT</v>
@@ -10242,7 +10242,7 @@
         <v/>
       </c>
       <c r="J199" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K199">
         <v>1</v>
@@ -10256,16 +10256,16 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>1783531248336-m0NESY</v>
+        <v>1783531237020-ZywOo</v>
       </c>
       <c r="B200">
-        <v>1783531248336</v>
+        <v>1783531237020</v>
       </c>
       <c r="C200" t="str">
-        <v>m0NESY</v>
+        <v>ZywOo</v>
       </c>
       <c r="D200" t="str">
-        <v>Falcons</v>
+        <v>Vitality</v>
       </c>
       <c r="E200" t="str">
         <v>EVENT</v>
@@ -10283,7 +10283,7 @@
         <v/>
       </c>
       <c r="J200" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K200">
         <v>1</v>
@@ -10297,16 +10297,16 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>1789043725277-heroghoxxt</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
+        <v>1783531248336-kyousuke</v>
+      </c>
+      <c r="B201">
+        <v>1783531248336</v>
       </c>
       <c r="C201" t="str">
-        <v>heroghoxxt</v>
+        <v>kyousuke</v>
       </c>
       <c r="D201" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E201" t="str">
         <v>EVENT</v>
@@ -10324,7 +10324,7 @@
         <v/>
       </c>
       <c r="J201" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K201">
         <v>1</v>
@@ -10338,16 +10338,16 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>1789043725277-kilzys</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
+        <v>1783531248336-kyxsan</v>
+      </c>
+      <c r="B202">
+        <v>1783531248336</v>
       </c>
       <c r="C202" t="str">
-        <v>kilzys</v>
+        <v>kyxsan</v>
       </c>
       <c r="D202" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E202" t="str">
         <v>EVENT</v>
@@ -10365,7 +10365,7 @@
         <v/>
       </c>
       <c r="J202" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K202">
         <v>1</v>
@@ -10379,16 +10379,16 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>1783531219494-history</v>
+        <v>1783531248336-NiKo</v>
       </c>
       <c r="B203">
-        <v>1783531219494</v>
+        <v>1783531248336</v>
       </c>
       <c r="C203" t="str">
-        <v>history</v>
+        <v>NiKo</v>
       </c>
       <c r="D203" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E203" t="str">
         <v>EVENT</v>
@@ -10406,7 +10406,7 @@
         <v/>
       </c>
       <c r="J203" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K203">
         <v>1</v>
@@ -10420,16 +10420,16 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>1783531219494-SpavaQu</v>
+        <v>1783531248336-TeSeS</v>
       </c>
       <c r="B204">
-        <v>1783531219494</v>
+        <v>1783531248336</v>
       </c>
       <c r="C204" t="str">
-        <v>SpavaQu</v>
+        <v>TeSeS</v>
       </c>
       <c r="D204" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E204" t="str">
         <v>EVENT</v>
@@ -10447,7 +10447,7 @@
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K204">
         <v>1</v>
@@ -10461,16 +10461,16 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>1783531219494-Pelle</v>
+        <v>1783531248336-m0NESY</v>
       </c>
       <c r="B205">
-        <v>1783531219494</v>
+        <v>1783531248336</v>
       </c>
       <c r="C205" t="str">
-        <v>Pelle</v>
+        <v>m0NESY</v>
       </c>
       <c r="D205" t="str">
-        <v>Iluminar</v>
+        <v>Falcons</v>
       </c>
       <c r="E205" t="str">
         <v>EVENT</v>
@@ -10488,7 +10488,7 @@
         <v/>
       </c>
       <c r="J205" t="str">
-        <v>Winner</v>
+        <v>Third</v>
       </c>
       <c r="K205">
         <v>1</v>
@@ -10501,32 +10501,32 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206">
-        <v>1787472254648</v>
+      <c r="A206" t="str">
+        <v>1789043725277-heroghoxxt</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>REZ</v>
+        <v>heroghoxxt</v>
       </c>
       <c r="D206" t="str">
-        <v>Astana Dragons</v>
+        <v>Iluminar</v>
       </c>
       <c r="E206" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F206" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G206">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H206" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I206" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J206" t="str">
         <v>Winner</v>
@@ -10542,32 +10542,32 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207">
-        <v>1787472247600</v>
+      <c r="A207" t="str">
+        <v>1789043725277-kilzys</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>kr1vda</v>
+        <v>kilzys</v>
       </c>
       <c r="D207" t="str">
-        <v>Vox Eminor</v>
+        <v>Iluminar</v>
       </c>
       <c r="E207" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F207" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G207">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H207" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I207" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J207" t="str">
         <v>Winner</v>
@@ -10583,32 +10583,32 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208">
-        <v>1787472243903</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
+      <c r="A208" t="str">
+        <v>1783531219494-history</v>
+      </c>
+      <c r="B208">
+        <v>1783531219494</v>
       </c>
       <c r="C208" t="str">
-        <v>fear</v>
+        <v>history</v>
       </c>
       <c r="D208" t="str">
-        <v>Fnatic</v>
+        <v>Iluminar</v>
       </c>
       <c r="E208" t="str">
-        <v>VP</v>
+        <v>EVENT</v>
       </c>
       <c r="F208" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G208">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H208" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I208" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J208" t="str">
         <v>Winner</v>
@@ -10624,32 +10624,32 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209">
-        <v>1787472232104</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
+      <c r="A209" t="str">
+        <v>1783531219494-SpavaQu</v>
+      </c>
+      <c r="B209">
+        <v>1783531219494</v>
       </c>
       <c r="C209" t="str">
-        <v>KRIMZ</v>
+        <v>SpavaQu</v>
       </c>
       <c r="D209" t="str">
-        <v>Fnatic</v>
+        <v>Iluminar</v>
       </c>
       <c r="E209" t="str">
-        <v>EVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F209" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G209">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H209" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I209" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J209" t="str">
         <v>Winner</v>
@@ -10665,32 +10665,32 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210">
-        <v>1787472226864</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
+      <c r="A210" t="str">
+        <v>1783531219494-Pelle</v>
+      </c>
+      <c r="B210">
+        <v>1783531219494</v>
       </c>
       <c r="C210" t="str">
-        <v>blameF</v>
+        <v>Pelle</v>
       </c>
       <c r="D210" t="str">
-        <v>Fnatic</v>
+        <v>Iluminar</v>
       </c>
       <c r="E210" t="str">
-        <v>MVP</v>
+        <v>EVENT</v>
       </c>
       <c r="F210" t="str">
-        <v>Winamax Spanish Cirtuit  2026</v>
+        <v>DreamHack Winter 2026</v>
       </c>
       <c r="G210">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H210" t="str">
-        <v>Regional</v>
+        <v>Global</v>
       </c>
       <c r="I210" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="J210" t="str">
         <v>Winner</v>
@@ -10707,22 +10707,22 @@
     </row>
     <row r="211">
       <c r="A211">
-        <v>1784847962039</v>
+        <v>1787472254648</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>abizz</v>
+        <v>REZ</v>
       </c>
       <c r="D211" t="str">
-        <v>AMKAL</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="E211" t="str">
         <v>VP</v>
       </c>
       <c r="F211" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -10731,10 +10731,10 @@
         <v>Regional</v>
       </c>
       <c r="I211" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J211" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="K211">
         <v>1</v>
@@ -10748,22 +10748,22 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>1784847955956</v>
+        <v>1787472247600</v>
       </c>
       <c r="B212" t="str">
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>next</v>
+        <v>kr1vda</v>
       </c>
       <c r="D212" t="str">
-        <v>AMKAL</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="E212" t="str">
         <v>VP</v>
       </c>
       <c r="F212" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G212">
         <v>1</v>
@@ -10772,10 +10772,10 @@
         <v>Regional</v>
       </c>
       <c r="I212" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J212" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="K212">
         <v>1</v>
@@ -10789,22 +10789,22 @@
     </row>
     <row r="213">
       <c r="A213">
-        <v>1784847948890</v>
+        <v>1787472243903</v>
       </c>
       <c r="B213" t="str">
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>yuurih</v>
+        <v>fear</v>
       </c>
       <c r="D213" t="str">
-        <v>FURIA</v>
+        <v>Fnatic</v>
       </c>
       <c r="E213" t="str">
         <v>VP</v>
       </c>
       <c r="F213" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G213">
         <v>1</v>
@@ -10813,7 +10813,7 @@
         <v>Regional</v>
       </c>
       <c r="I213" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J213" t="str">
         <v>Winner</v>
@@ -10830,22 +10830,22 @@
     </row>
     <row r="214">
       <c r="A214">
-        <v>1784847943609</v>
+        <v>1787472232104</v>
       </c>
       <c r="B214" t="str">
         <v/>
       </c>
       <c r="C214" t="str">
-        <v>KSCERATO</v>
+        <v>KRIMZ</v>
       </c>
       <c r="D214" t="str">
-        <v>FURIA</v>
+        <v>Fnatic</v>
       </c>
       <c r="E214" t="str">
         <v>EVP</v>
       </c>
       <c r="F214" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G214">
         <v>1</v>
@@ -10854,7 +10854,7 @@
         <v>Regional</v>
       </c>
       <c r="I214" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J214" t="str">
         <v>Winner</v>
@@ -10871,22 +10871,22 @@
     </row>
     <row r="215">
       <c r="A215">
-        <v>1784847935905</v>
+        <v>1787472226864</v>
       </c>
       <c r="B215" t="str">
         <v/>
       </c>
       <c r="C215" t="str">
-        <v>molodoy</v>
+        <v>blameF</v>
       </c>
       <c r="D215" t="str">
-        <v>FURIA</v>
+        <v>Fnatic</v>
       </c>
       <c r="E215" t="str">
         <v>MVP</v>
       </c>
       <c r="F215" t="str">
-        <v>FiReLEAGUE Buenos Aires 2026</v>
+        <v>Winamax Spanish Cirtuit  2026</v>
       </c>
       <c r="G215">
         <v>1</v>
@@ -10895,7 +10895,7 @@
         <v>Regional</v>
       </c>
       <c r="I215" t="str">
-        <v>America</v>
+        <v>Europe</v>
       </c>
       <c r="J215" t="str">
         <v>Winner</v>
@@ -10912,34 +10912,34 @@
     </row>
     <row r="216">
       <c r="A216">
-        <v>1783531290361</v>
+        <v>1784847962039</v>
       </c>
       <c r="B216" t="str">
         <v/>
       </c>
       <c r="C216" t="str">
-        <v>m0NESY</v>
+        <v>abizz</v>
       </c>
       <c r="D216" t="str">
-        <v>Falcons</v>
+        <v>AMKAL</v>
       </c>
       <c r="E216" t="str">
         <v>VP</v>
       </c>
       <c r="F216" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G216">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H216" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I216" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J216" t="str">
-        <v>Third</v>
+        <v>Second</v>
       </c>
       <c r="K216">
         <v>1</v>
@@ -10953,31 +10953,31 @@
     </row>
     <row r="217">
       <c r="A217">
-        <v>1783531284605</v>
+        <v>1784847955956</v>
       </c>
       <c r="B217" t="str">
         <v/>
       </c>
       <c r="C217" t="str">
-        <v>ropz</v>
+        <v>next</v>
       </c>
       <c r="D217" t="str">
-        <v>Vitality</v>
+        <v>AMKAL</v>
       </c>
       <c r="E217" t="str">
         <v>VP</v>
       </c>
       <c r="F217" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G217">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H217" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I217" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J217" t="str">
         <v>Second</v>
@@ -10994,34 +10994,34 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>1783531278450</v>
+        <v>1784847948890</v>
       </c>
       <c r="B218" t="str">
         <v/>
       </c>
       <c r="C218" t="str">
-        <v>ZywOo</v>
+        <v>yuurih</v>
       </c>
       <c r="D218" t="str">
-        <v>Vitality</v>
+        <v>FURIA</v>
       </c>
       <c r="E218" t="str">
-        <v>EVP</v>
+        <v>VP</v>
       </c>
       <c r="F218" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G218">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H218" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I218" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J218" t="str">
-        <v>Second</v>
+        <v>Winner</v>
       </c>
       <c r="K218">
         <v>1</v>
@@ -11035,31 +11035,31 @@
     </row>
     <row r="219">
       <c r="A219">
-        <v>1783531271104</v>
+        <v>1784847943609</v>
       </c>
       <c r="B219" t="str">
         <v/>
       </c>
       <c r="C219" t="str">
-        <v>heroghoxxt</v>
+        <v>KSCERATO</v>
       </c>
       <c r="D219" t="str">
-        <v>Iluminar</v>
+        <v>FURIA</v>
       </c>
       <c r="E219" t="str">
-        <v>VP</v>
+        <v>EVP</v>
       </c>
       <c r="F219" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G219">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H219" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I219" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J219" t="str">
         <v>Winner</v>
@@ -11076,31 +11076,31 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>1783531262507</v>
+        <v>1784847935905</v>
       </c>
       <c r="B220" t="str">
         <v/>
       </c>
       <c r="C220" t="str">
-        <v>kilzys</v>
+        <v>molodoy</v>
       </c>
       <c r="D220" t="str">
-        <v>Iluminar</v>
+        <v>FURIA</v>
       </c>
       <c r="E220" t="str">
         <v>MVP</v>
       </c>
       <c r="F220" t="str">
-        <v>DreamHack Winter 2026</v>
+        <v>FiReLEAGUE Buenos Aires 2026</v>
       </c>
       <c r="G220">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H220" t="str">
-        <v>Global</v>
+        <v>Regional</v>
       </c>
       <c r="I220" t="str">
-        <v/>
+        <v>America</v>
       </c>
       <c r="J220" t="str">
         <v>Winner</v>
@@ -11115,9 +11115,214 @@
         <v/>
       </c>
     </row>
+    <row r="221">
+      <c r="A221">
+        <v>1783531290361</v>
+      </c>
+      <c r="B221" t="str">
+        <v/>
+      </c>
+      <c r="C221" t="str">
+        <v>m0NESY</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Falcons</v>
+      </c>
+      <c r="E221" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F221" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G221">
+        <v>5</v>
+      </c>
+      <c r="H221" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I221" t="str">
+        <v/>
+      </c>
+      <c r="J221" t="str">
+        <v>Third</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221" t="str">
+        <v/>
+      </c>
+      <c r="M221" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>1783531284605</v>
+      </c>
+      <c r="B222" t="str">
+        <v/>
+      </c>
+      <c r="C222" t="str">
+        <v>ropz</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E222" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F222" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G222">
+        <v>5</v>
+      </c>
+      <c r="H222" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I222" t="str">
+        <v/>
+      </c>
+      <c r="J222" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
+      </c>
+      <c r="L222" t="str">
+        <v/>
+      </c>
+      <c r="M222" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>1783531278450</v>
+      </c>
+      <c r="B223" t="str">
+        <v/>
+      </c>
+      <c r="C223" t="str">
+        <v>ZywOo</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Vitality</v>
+      </c>
+      <c r="E223" t="str">
+        <v>EVP</v>
+      </c>
+      <c r="F223" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G223">
+        <v>5</v>
+      </c>
+      <c r="H223" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I223" t="str">
+        <v/>
+      </c>
+      <c r="J223" t="str">
+        <v>Second</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+      <c r="L223" t="str">
+        <v/>
+      </c>
+      <c r="M223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>1783531271104</v>
+      </c>
+      <c r="B224" t="str">
+        <v/>
+      </c>
+      <c r="C224" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E224" t="str">
+        <v>VP</v>
+      </c>
+      <c r="F224" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G224">
+        <v>5</v>
+      </c>
+      <c r="H224" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I224" t="str">
+        <v/>
+      </c>
+      <c r="J224" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="L224" t="str">
+        <v/>
+      </c>
+      <c r="M224" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>1783531262507</v>
+      </c>
+      <c r="B225" t="str">
+        <v/>
+      </c>
+      <c r="C225" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="E225" t="str">
+        <v>MVP</v>
+      </c>
+      <c r="F225" t="str">
+        <v>DreamHack Winter 2026</v>
+      </c>
+      <c r="G225">
+        <v>5</v>
+      </c>
+      <c r="H225" t="str">
+        <v>Global</v>
+      </c>
+      <c r="I225" t="str">
+        <v/>
+      </c>
+      <c r="J225" t="str">
+        <v>Winner</v>
+      </c>
+      <c r="K225">
+        <v>1</v>
+      </c>
+      <c r="L225" t="str">
+        <v/>
+      </c>
+      <c r="M225" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M220"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M225"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/file/history_updated.xlsx
+++ b/file/history_updated.xlsx
@@ -11329,7 +11329,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11359,137 +11359,137 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1788874820852</v>
+        <v>1790815097907</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="str">
-        <v>FA SIGNING</v>
+        <v>PROMOTED</v>
       </c>
       <c r="D2" t="str">
-        <v>Perfecto</v>
+        <v>kl1m</v>
       </c>
       <c r="E2" t="str">
-        <v>Free Agency</v>
+        <v>Envy</v>
       </c>
       <c r="F2" t="str">
-        <v>BC.Game</v>
+        <v>Envy</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="str">
-        <v>joined as Bench</v>
+        <v>promoted to starter</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1788874765369</v>
+        <v>1790815092655</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>FA SIGNING</v>
+        <v>RELEASED</v>
       </c>
       <c r="D3" t="str">
-        <v>kl1m</v>
+        <v>PTC</v>
       </c>
       <c r="E3" t="str">
+        <v>Envy</v>
+      </c>
+      <c r="F3" t="str">
         <v>Free Agency</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Envy</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="str">
-        <v>joined as Bench</v>
+        <v>released to market for free</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1787536348426</v>
+        <v>1790815054169</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="str">
-        <v>RELEASED</v>
+        <v>PROMOTED</v>
       </c>
       <c r="D4" t="str">
-        <v>fer</v>
+        <v>Perfecto</v>
       </c>
       <c r="E4" t="str">
-        <v>Lux Tenebris</v>
+        <v>BC.Game</v>
       </c>
       <c r="F4" t="str">
-        <v>Free Agency</v>
+        <v>BC.Game</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="str">
-        <v>released to market for free</v>
+        <v>promoted to starter</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>1785396043745</v>
+        <v>1790815033506</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="str">
-        <v>PROMOTED</v>
+        <v>RELEASED</v>
       </c>
       <c r="D5" t="str">
-        <v>boltz</v>
+        <v>Valiance</v>
       </c>
       <c r="E5" t="str">
-        <v>Lux Tenebris</v>
+        <v>BC.Game</v>
       </c>
       <c r="F5" t="str">
-        <v>Lux Tenebris</v>
+        <v>Free Agency</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="str">
-        <v>promoted to starter</v>
+        <v>released to market for free</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1785396042996</v>
+        <v>1788874820852</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>BENCHED</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D6" t="str">
-        <v>fer</v>
+        <v>Perfecto</v>
       </c>
       <c r="E6" t="str">
-        <v>Lux Tenebris</v>
+        <v>Free Agency</v>
       </c>
       <c r="F6" t="str">
-        <v>Lux Tenebris</v>
+        <v>BC.Game</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="str">
-        <v>moved to bench</v>
+        <v>joined as Bench</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>1785396011356</v>
+        <v>1788874765369</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -11498,13 +11498,13 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D7" t="str">
-        <v>boltz</v>
+        <v>kl1m</v>
       </c>
       <c r="E7" t="str">
         <v>Free Agency</v>
       </c>
       <c r="F7" t="str">
-        <v>Lux Tenebris</v>
+        <v>Envy</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -11515,111 +11515,111 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>1783532394458</v>
+        <v>1787536348426</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="str">
-        <v>FA SIGNING</v>
+        <v>RELEASED</v>
       </c>
       <c r="D8" t="str">
-        <v>diskyb0b</v>
+        <v>fer</v>
       </c>
       <c r="E8" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="F8" t="str">
         <v>Free Agency</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Kappa Bar</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="str">
-        <v>joined as Starter</v>
+        <v>released to market for free</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>1783532378345</v>
+        <v>1785396043745</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="str">
-        <v>TRANSFER</v>
+        <v>PROMOTED</v>
       </c>
       <c r="D9" t="str">
-        <v>Gizmy</v>
+        <v>boltz</v>
       </c>
       <c r="E9" t="str">
-        <v>Kappa Bar</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="F9" t="str">
-        <v>Iluminar</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>promoted to starter</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>1783532335269</v>
+        <v>1785396042996</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>FA SIGNING</v>
+        <v>BENCHED</v>
       </c>
       <c r="D10" t="str">
-        <v>hades</v>
+        <v>fer</v>
       </c>
       <c r="E10" t="str">
-        <v>Free Agency</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="F10" t="str">
-        <v>Mythic</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="str">
-        <v>joined as Starter</v>
+        <v>moved to bench</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>1783532286477</v>
+        <v>1785396011356</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D11" t="str">
-        <v>fl0m</v>
+        <v>boltz</v>
       </c>
       <c r="E11" t="str">
-        <v>Mythic</v>
+        <v>Free Agency</v>
       </c>
       <c r="F11" t="str">
-        <v>Iluminar</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Bench</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>1783531772696</v>
+        <v>1783532394458</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -11628,13 +11628,13 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D12" t="str">
-        <v>taco</v>
+        <v>diskyb0b</v>
       </c>
       <c r="E12" t="str">
         <v>Free Agency</v>
       </c>
       <c r="F12" t="str">
-        <v>Lux Tenebris</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -11645,33 +11645,33 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>1783531758984</v>
+        <v>1783532378345</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="str">
-        <v>FA SIGNING</v>
+        <v>TRANSFER</v>
       </c>
       <c r="D13" t="str">
-        <v>fer</v>
+        <v>Gizmy</v>
       </c>
       <c r="E13" t="str">
-        <v>Free Agency</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="F13" t="str">
-        <v>Lux Tenebris</v>
+        <v>Iluminar</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="str">
-        <v>joined as Starter</v>
+        <v>CLAUSE DEAL · joined as Starter</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>1783531616692</v>
+        <v>1783532335269</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -11680,13 +11680,13 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D14" t="str">
-        <v>kyourezz</v>
+        <v>hades</v>
       </c>
       <c r="E14" t="str">
         <v>Free Agency</v>
       </c>
       <c r="F14" t="str">
-        <v>Lux Tenebris</v>
+        <v>Mythic</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -11697,7 +11697,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>1783531586211</v>
+        <v>1783532286477</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -11706,16 +11706,16 @@
         <v>TRANSFER</v>
       </c>
       <c r="D15" t="str">
-        <v>heroghoxxt</v>
+        <v>fl0m</v>
       </c>
       <c r="E15" t="str">
+        <v>Mythic</v>
+      </c>
+      <c r="F15" t="str">
         <v>Iluminar</v>
       </c>
-      <c r="F15" t="str">
-        <v>Lux Tenebris</v>
-      </c>
       <c r="G15">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="H15" t="str">
         <v>CLAUSE DEAL · joined as Starter</v>
@@ -11723,33 +11723,33 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>1783531583393</v>
+        <v>1783531772696</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="str">
-        <v>TRANSFER</v>
+        <v>FA SIGNING</v>
       </c>
       <c r="D16" t="str">
-        <v>kilzys</v>
+        <v>taco</v>
       </c>
       <c r="E16" t="str">
-        <v>Iluminar</v>
+        <v>Free Agency</v>
       </c>
       <c r="F16" t="str">
         <v>Lux Tenebris</v>
       </c>
       <c r="G16">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="H16" t="str">
-        <v>CLAUSE DEAL · joined as Starter</v>
+        <v>joined as Starter</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>1783473413103</v>
+        <v>1783531758984</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -11758,7 +11758,7 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D17" t="str">
-        <v>taco</v>
+        <v>fer</v>
       </c>
       <c r="E17" t="str">
         <v>Free Agency</v>
@@ -11775,7 +11775,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>1783473388452</v>
+        <v>1783531616692</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -11784,7 +11784,7 @@
         <v>FA SIGNING</v>
       </c>
       <c r="D18" t="str">
-        <v>fer</v>
+        <v>kyourezz</v>
       </c>
       <c r="E18" t="str">
         <v>Free Agency</v>
@@ -11799,16 +11799,120 @@
         <v>joined as Starter</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19">
+        <v>1783531586211</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>TRANSFER</v>
+      </c>
+      <c r="D19" t="str">
+        <v>heroghoxxt</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G19">
+        <v>40000</v>
+      </c>
+      <c r="H19" t="str">
+        <v>CLAUSE DEAL · joined as Starter</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>1783531583393</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>TRANSFER</v>
+      </c>
+      <c r="D20" t="str">
+        <v>kilzys</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Iluminar</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G20">
+        <v>50000</v>
+      </c>
+      <c r="H20" t="str">
+        <v>CLAUSE DEAL · joined as Starter</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>1783473413103</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D21" t="str">
+        <v>taco</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>1783473388452</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>FA SIGNING</v>
+      </c>
+      <c r="D22" t="str">
+        <v>fer</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Free Agency</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="str">
+        <v>joined as Starter</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11835,68 +11939,68 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1788874820765</v>
+        <v>1790815092391</v>
       </c>
       <c r="B2" t="str">
-        <v>Perfecto</v>
+        <v>PTC</v>
       </c>
       <c r="C2" t="str">
-        <v>BC.Game</v>
+        <v>—</v>
       </c>
       <c r="D2" t="str">
-        <v>FREE AGENCY</v>
+        <v>Envy</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>✅ FA SIGNING</v>
+        <v>✅ RELEASED (FREE)</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1788874765189</v>
+        <v>1790815033249</v>
       </c>
       <c r="B3" t="str">
-        <v>kl1m</v>
+        <v>Valiance</v>
       </c>
       <c r="C3" t="str">
-        <v>Envy</v>
+        <v>—</v>
       </c>
       <c r="D3" t="str">
-        <v>FREE AGENCY</v>
+        <v>BC.Game</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>✅ FA SIGNING</v>
+        <v>✅ RELEASED (FREE)</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1787536347803</v>
+        <v>1788874820765</v>
       </c>
       <c r="B4" t="str">
-        <v>fer</v>
+        <v>Perfecto</v>
       </c>
       <c r="C4" t="str">
-        <v>—</v>
+        <v>BC.Game</v>
       </c>
       <c r="D4" t="str">
-        <v>Lux Tenebris</v>
+        <v>FREE AGENCY</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>✅ RELEASED (FREE)</v>
+        <v>✅ FA SIGNING</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -11904,13 +12008,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1785396010605</v>
+        <v>1788874765189</v>
       </c>
       <c r="B5" t="str">
-        <v>boltz</v>
+        <v>kl1m</v>
       </c>
       <c r="C5" t="str">
-        <v>Lux Tenebris</v>
+        <v>Envy</v>
       </c>
       <c r="D5" t="str">
         <v>FREE AGENCY</v>
@@ -11925,9 +12029,55 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>1787536347803</v>
+      </c>
+      <c r="B6" t="str">
+        <v>fer</v>
+      </c>
+      <c r="C6" t="str">
+        <v>—</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="str">
+        <v>✅ RELEASED (FREE)</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1785396010605</v>
+      </c>
+      <c r="B7" t="str">
+        <v>boltz</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Lux Tenebris</v>
+      </c>
+      <c r="D7" t="str">
+        <v>FREE AGENCY</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="str">
+        <v>✅ FA SIGNING</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11943,7 +12093,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
